--- a/file/history.xlsx
+++ b/file/history.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/faa3f9bfbb5dc780/Documentos/GitHub/ck-tools/file/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\joao.abraga\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="563" documentId="13_ncr:1_{AB7ADBC0-0AFC-4EB5-BDC6-F57936754D64}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{875A5B4F-0713-4E80-888F-0BBE7E743135}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{77347E75-C064-47B0-B07A-BDBB4F745A11}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2520" yWindow="4185" windowWidth="21600" windowHeight="11295" xr2:uid="{39BF18F1-6CA4-42F4-B020-2D59954264FB}"/>
+    <workbookView xWindow="4890" yWindow="3630" windowWidth="21600" windowHeight="11295" xr2:uid="{39BF18F1-6CA4-42F4-B020-2D59954264FB}"/>
   </bookViews>
   <sheets>
     <sheet name="main" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2786" uniqueCount="268">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2876" uniqueCount="268">
   <si>
     <t>Team 1</t>
   </si>
@@ -966,7 +966,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema do Office">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -12498,148 +12498,364 @@
       </c>
     </row>
     <row r="558" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A558" s="11"/>
-      <c r="B558" s="11"/>
-      <c r="C558" s="11"/>
-      <c r="D558" s="11"/>
-      <c r="E558" s="11"/>
-      <c r="F558" s="11"/>
+      <c r="A558" s="5" t="s">
+        <v>136</v>
+      </c>
+      <c r="B558" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="C558" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="D558" s="5" t="s">
+        <v>151</v>
+      </c>
+      <c r="E558" s="5" t="s">
+        <v>266</v>
+      </c>
+      <c r="F558" s="8">
+        <v>46246</v>
+      </c>
     </row>
     <row r="559" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A559" s="11"/>
-      <c r="B559" s="11"/>
-      <c r="C559" s="11"/>
-      <c r="D559" s="11"/>
-      <c r="E559" s="11"/>
-      <c r="F559" s="11"/>
+      <c r="A559" s="5" t="s">
+        <v>136</v>
+      </c>
+      <c r="B559" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="C559" s="5" t="s">
+        <v>162</v>
+      </c>
+      <c r="D559" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="E559" s="5" t="s">
+        <v>266</v>
+      </c>
+      <c r="F559" s="8">
+        <v>46246</v>
+      </c>
     </row>
     <row r="560" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A560" s="11"/>
-      <c r="B560" s="11"/>
-      <c r="C560" s="11"/>
-      <c r="D560" s="11"/>
-      <c r="E560" s="11"/>
-      <c r="F560" s="11"/>
+      <c r="A560" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="B560" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="C560" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="D560" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="E560" s="4" t="s">
+        <v>266</v>
+      </c>
+      <c r="F560" s="9">
+        <v>46246</v>
+      </c>
     </row>
     <row r="561" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A561" s="11"/>
-      <c r="B561" s="11"/>
-      <c r="C561" s="11"/>
-      <c r="D561" s="11"/>
-      <c r="E561" s="11"/>
-      <c r="F561" s="11"/>
+      <c r="A561" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="B561" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="C561" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="D561" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="E561" s="4" t="s">
+        <v>266</v>
+      </c>
+      <c r="F561" s="9">
+        <v>46246</v>
+      </c>
     </row>
     <row r="562" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A562" s="11"/>
-      <c r="B562" s="11"/>
-      <c r="C562" s="11"/>
-      <c r="D562" s="11"/>
-      <c r="E562" s="11"/>
-      <c r="F562" s="11"/>
+      <c r="A562" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="B562" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="C562" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="D562" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="E562" s="4" t="s">
+        <v>266</v>
+      </c>
+      <c r="F562" s="9">
+        <v>46246</v>
+      </c>
     </row>
     <row r="563" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A563" s="11"/>
-      <c r="B563" s="11"/>
-      <c r="C563" s="11"/>
-      <c r="D563" s="11"/>
-      <c r="E563" s="11"/>
-      <c r="F563" s="11"/>
+      <c r="A563" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="B563" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="C563" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="D563" s="5" t="s">
+        <v>101</v>
+      </c>
+      <c r="E563" s="5" t="s">
+        <v>266</v>
+      </c>
+      <c r="F563" s="8">
+        <v>46246</v>
+      </c>
     </row>
     <row r="564" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A564" s="11"/>
-      <c r="B564" s="11"/>
-      <c r="C564" s="11"/>
-      <c r="D564" s="11"/>
-      <c r="E564" s="11"/>
-      <c r="F564" s="11"/>
+      <c r="A564" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="B564" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="C564" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D564" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="E564" s="5" t="s">
+        <v>266</v>
+      </c>
+      <c r="F564" s="8">
+        <v>46246</v>
+      </c>
     </row>
     <row r="565" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A565" s="11"/>
-      <c r="B565" s="11"/>
-      <c r="C565" s="11"/>
-      <c r="D565" s="11"/>
-      <c r="E565" s="11"/>
-      <c r="F565" s="11"/>
+      <c r="A565" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="B565" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="C565" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="D565" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="E565" s="5" t="s">
+        <v>266</v>
+      </c>
+      <c r="F565" s="8">
+        <v>46246</v>
+      </c>
     </row>
     <row r="566" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A566" s="11"/>
-      <c r="B566" s="11"/>
-      <c r="C566" s="11"/>
-      <c r="D566" s="11"/>
-      <c r="E566" s="11"/>
-      <c r="F566" s="11"/>
+      <c r="A566" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="B566" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="C566" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="D566" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="E566" s="4" t="s">
+        <v>266</v>
+      </c>
+      <c r="F566" s="9">
+        <v>46246</v>
+      </c>
     </row>
     <row r="567" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A567" s="11"/>
-      <c r="B567" s="11"/>
-      <c r="C567" s="11"/>
-      <c r="D567" s="11"/>
-      <c r="E567" s="11"/>
-      <c r="F567" s="11"/>
+      <c r="A567" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="B567" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="C567" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="D567" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="E567" s="4" t="s">
+        <v>266</v>
+      </c>
+      <c r="F567" s="9">
+        <v>46246</v>
+      </c>
     </row>
     <row r="568" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A568" s="11"/>
-      <c r="B568" s="11"/>
-      <c r="C568" s="11"/>
-      <c r="D568" s="11"/>
-      <c r="E568" s="11"/>
-      <c r="F568" s="11"/>
+      <c r="A568" s="5" t="s">
+        <v>104</v>
+      </c>
+      <c r="B568" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="C568" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="D568" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="E568" s="5" t="s">
+        <v>266</v>
+      </c>
+      <c r="F568" s="8">
+        <v>46247</v>
+      </c>
     </row>
     <row r="569" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A569" s="11"/>
-      <c r="B569" s="11"/>
-      <c r="C569" s="11"/>
-      <c r="D569" s="11"/>
-      <c r="E569" s="11"/>
-      <c r="F569" s="11"/>
+      <c r="A569" s="5" t="s">
+        <v>104</v>
+      </c>
+      <c r="B569" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="C569" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D569" s="5" t="s">
+        <v>150</v>
+      </c>
+      <c r="E569" s="5" t="s">
+        <v>266</v>
+      </c>
+      <c r="F569" s="8">
+        <v>46247</v>
+      </c>
     </row>
     <row r="570" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A570" s="11"/>
-      <c r="B570" s="11"/>
-      <c r="C570" s="11"/>
-      <c r="D570" s="11"/>
-      <c r="E570" s="11"/>
-      <c r="F570" s="11"/>
+      <c r="A570" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="B570" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="C570" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="D570" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="E570" s="4" t="s">
+        <v>266</v>
+      </c>
+      <c r="F570" s="9">
+        <v>46247</v>
+      </c>
     </row>
     <row r="571" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A571" s="11"/>
-      <c r="B571" s="11"/>
-      <c r="C571" s="11"/>
-      <c r="D571" s="11"/>
-      <c r="E571" s="11"/>
-      <c r="F571" s="11"/>
+      <c r="A571" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="B571" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="C571" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="D571" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="E571" s="4" t="s">
+        <v>266</v>
+      </c>
+      <c r="F571" s="9">
+        <v>46247</v>
+      </c>
     </row>
     <row r="572" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A572" s="11"/>
-      <c r="B572" s="11"/>
-      <c r="C572" s="11"/>
-      <c r="D572" s="11"/>
-      <c r="E572" s="11"/>
-      <c r="F572" s="11"/>
+      <c r="A572" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="B572" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="C572" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D572" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="E572" s="5" t="s">
+        <v>266</v>
+      </c>
+      <c r="F572" s="8">
+        <v>46247</v>
+      </c>
     </row>
     <row r="573" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A573" s="11"/>
-      <c r="B573" s="11"/>
-      <c r="C573" s="11"/>
-      <c r="D573" s="11"/>
-      <c r="E573" s="11"/>
-      <c r="F573" s="11"/>
+      <c r="A573" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="B573" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="C573" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="D573" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="E573" s="5" t="s">
+        <v>266</v>
+      </c>
+      <c r="F573" s="8">
+        <v>46247</v>
+      </c>
     </row>
     <row r="574" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A574" s="11"/>
-      <c r="B574" s="11"/>
-      <c r="C574" s="11"/>
-      <c r="D574" s="11"/>
-      <c r="E574" s="11"/>
-      <c r="F574" s="11"/>
+      <c r="A574" s="4" t="s">
+        <v>267</v>
+      </c>
+      <c r="B574" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="C574" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="D574" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="E574" s="4" t="s">
+        <v>266</v>
+      </c>
+      <c r="F574" s="9">
+        <v>46247</v>
+      </c>
     </row>
     <row r="575" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A575" s="11"/>
-      <c r="B575" s="11"/>
-      <c r="C575" s="11"/>
-      <c r="D575" s="11"/>
-      <c r="E575" s="11"/>
-      <c r="F575" s="11"/>
+      <c r="A575" s="4" t="s">
+        <v>267</v>
+      </c>
+      <c r="B575" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="C575" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="D575" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="E575" s="4" t="s">
+        <v>266</v>
+      </c>
+      <c r="F575" s="9">
+        <v>46247</v>
+      </c>
     </row>
     <row r="576" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A576" s="11"/>

--- a/file/history.xlsx
+++ b/file/history.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\joao.abraga\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\joao.abraga\Downloads\ck-tools-main\file\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{77347E75-C064-47B0-B07A-BDBB4F745A11}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4873FE19-206B-4C4D-A9D7-3715FBDACD71}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4890" yWindow="3630" windowWidth="21600" windowHeight="11295" xr2:uid="{39BF18F1-6CA4-42F4-B020-2D59954264FB}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{39BF18F1-6CA4-42F4-B020-2D59954264FB}"/>
   </bookViews>
   <sheets>
     <sheet name="main" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2876" uniqueCount="268">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2877" uniqueCount="213">
   <si>
     <t>Team 1</t>
   </si>
@@ -665,181 +665,16 @@
     <t>Vox Eminor</t>
   </si>
   <si>
-    <t>Winamax Spanish Cirtuit 2027</t>
-  </si>
-  <si>
-    <t>Winamax Spanish Cirtuit 2028</t>
-  </si>
-  <si>
-    <t>Winamax Spanish Cirtuit 2029</t>
-  </si>
-  <si>
-    <t>Winamax Spanish Cirtuit 2030</t>
-  </si>
-  <si>
-    <t>Winamax Spanish Cirtuit 2031</t>
-  </si>
-  <si>
-    <t>Winamax Spanish Cirtuit 2032</t>
-  </si>
-  <si>
-    <t>Winamax Spanish Cirtuit 2033</t>
-  </si>
-  <si>
-    <t>Winamax Spanish Cirtuit 2034</t>
-  </si>
-  <si>
-    <t>Winamax Spanish Cirtuit 2035</t>
-  </si>
-  <si>
-    <t>Winamax Spanish Cirtuit 2036</t>
-  </si>
-  <si>
-    <t>Winamax Spanish Cirtuit 2037</t>
-  </si>
-  <si>
-    <t>Winamax Spanish Cirtuit 2038</t>
-  </si>
-  <si>
-    <t>Winamax Spanish Cirtuit 2039</t>
-  </si>
-  <si>
-    <t>Winamax Spanish Cirtuit 2040</t>
-  </si>
-  <si>
-    <t>Winamax Spanish Cirtuit 2041</t>
-  </si>
-  <si>
-    <t>Winamax Spanish Cirtuit 2042</t>
-  </si>
-  <si>
-    <t>Winamax Spanish Cirtuit 2043</t>
-  </si>
-  <si>
-    <t>Winamax Spanish Cirtuit 2044</t>
-  </si>
-  <si>
-    <t>Winamax Spanish Cirtuit 2045</t>
-  </si>
-  <si>
-    <t>Winamax Spanish Cirtuit 2046</t>
-  </si>
-  <si>
-    <t>Winamax Spanish Cirtuit 2047</t>
-  </si>
-  <si>
-    <t>Winamax Spanish Cirtuit 2048</t>
-  </si>
-  <si>
-    <t>Winamax Spanish Cirtuit 2049</t>
-  </si>
-  <si>
-    <t>Winamax Spanish Cirtuit 2050</t>
-  </si>
-  <si>
-    <t>Winamax Spanish Cirtuit 2051</t>
-  </si>
-  <si>
-    <t>Winamax Spanish Cirtuit 2052</t>
-  </si>
-  <si>
-    <t>Winamax Spanish Cirtuit 2053</t>
-  </si>
-  <si>
-    <t>Winamax Spanish Cirtuit 2054</t>
-  </si>
-  <si>
-    <t>Winamax Spanish Cirtuit 2055</t>
-  </si>
-  <si>
-    <t>Winamax Spanish Cirtuit 2056</t>
-  </si>
-  <si>
-    <t>Winamax Spanish Cirtuit 2057</t>
-  </si>
-  <si>
-    <t>Winamax Spanish Cirtuit 2058</t>
-  </si>
-  <si>
-    <t>Winamax Spanish Cirtuit 2059</t>
-  </si>
-  <si>
-    <t>Winamax Spanish Cirtuit 2060</t>
-  </si>
-  <si>
-    <t>Winamax Spanish Cirtuit 2061</t>
-  </si>
-  <si>
-    <t>Winamax Spanish Cirtuit 2062</t>
-  </si>
-  <si>
-    <t>Winamax Spanish Cirtuit 2063</t>
-  </si>
-  <si>
-    <t>Winamax Spanish Cirtuit 2064</t>
-  </si>
-  <si>
     <t>13x</t>
   </si>
   <si>
-    <t>Winamax Spanish Cirtuit 2065</t>
-  </si>
-  <si>
-    <t>Winamax Spanish Cirtuit 2066</t>
-  </si>
-  <si>
-    <t>Winamax Spanish Cirtuit 2067</t>
-  </si>
-  <si>
-    <t>Winamax Spanish Cirtuit 2068</t>
-  </si>
-  <si>
-    <t>Winamax Spanish Cirtuit 2069</t>
-  </si>
-  <si>
-    <t>Winamax Spanish Cirtuit 2070</t>
-  </si>
-  <si>
-    <t>Winamax Spanish Cirtuit 2071</t>
-  </si>
-  <si>
-    <t>Winamax Spanish Cirtuit 2072</t>
-  </si>
-  <si>
-    <t>Winamax Spanish Cirtuit 2073</t>
-  </si>
-  <si>
-    <t>Winamax Spanish Cirtuit 2074</t>
-  </si>
-  <si>
-    <t>Winamax Spanish Cirtuit 2075</t>
-  </si>
-  <si>
-    <t>Winamax Spanish Cirtuit 2076</t>
-  </si>
-  <si>
-    <t>Winamax Spanish Cirtuit 2077</t>
-  </si>
-  <si>
-    <t>Winamax Spanish Cirtuit 2078</t>
-  </si>
-  <si>
-    <t>Winamax Spanish Cirtuit 2079</t>
-  </si>
-  <si>
-    <t>Winamax Spanish Cirtuit 2080</t>
-  </si>
-  <si>
-    <t>Winamax Spanish Cirtuit 2081</t>
-  </si>
-  <si>
-    <t>Winamax Spanish Cirtuit 2082</t>
-  </si>
-  <si>
     <t>BLAST Premier 2026 Seoul</t>
   </si>
   <si>
     <t>Lux Tenebris</t>
+  </si>
+  <si>
+    <t>Details</t>
   </si>
 </sst>
 </file>
@@ -1282,18 +1117,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ECD49EDF-97AD-42E2-9203-75390A90C7F2}">
-  <dimension ref="A1:H606"/>
+  <dimension ref="A1:I606"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="25.42578125" style="1" customWidth="1"/>
     <col min="2" max="2" width="26.42578125" style="1" customWidth="1"/>
     <col min="3" max="3" width="16.5703125" style="1" customWidth="1"/>
     <col min="4" max="4" width="12.5703125" style="1" customWidth="1"/>
-    <col min="5" max="5" width="39.7109375" style="1" customWidth="1"/>
-    <col min="6" max="6" width="12.42578125" style="1" customWidth="1"/>
+    <col min="5" max="6" width="39.7109375" style="1" customWidth="1"/>
+    <col min="7" max="7" width="12.42578125" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1310,10 +1145,13 @@
         <v>4</v>
       </c>
       <c r="F1" s="2" t="s">
+        <v>212</v>
+      </c>
+      <c r="G1" s="2" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
         <v>6</v>
       </c>
@@ -1329,11 +1167,12 @@
       <c r="E2" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F2" s="6">
+      <c r="F2" s="3"/>
+      <c r="G2" s="6">
         <v>46023</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>11</v>
       </c>
@@ -1349,11 +1188,11 @@
       <c r="E3" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="F3" s="7">
+      <c r="G3" s="7">
         <v>46023</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
         <v>14</v>
       </c>
@@ -1369,11 +1208,12 @@
       <c r="E4" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F4" s="6">
+      <c r="F4" s="3"/>
+      <c r="G4" s="6">
         <v>46023</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>18</v>
       </c>
@@ -1389,11 +1229,11 @@
       <c r="E5" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="F5" s="7">
+      <c r="G5" s="7">
         <v>46023</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
         <v>20</v>
       </c>
@@ -1409,11 +1249,12 @@
       <c r="E6" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F6" s="6">
+      <c r="F6" s="3"/>
+      <c r="G6" s="6">
         <v>46023</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>24</v>
       </c>
@@ -1429,11 +1270,11 @@
       <c r="E7" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="F7" s="7">
+      <c r="G7" s="7">
         <v>46023</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
         <v>27</v>
       </c>
@@ -1449,11 +1290,12 @@
       <c r="E8" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F8" s="6">
+      <c r="F8" s="3"/>
+      <c r="G8" s="6">
         <v>46023</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>30</v>
       </c>
@@ -1469,11 +1311,11 @@
       <c r="E9" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="F9" s="7">
+      <c r="G9" s="7">
         <v>46023</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
         <v>33</v>
       </c>
@@ -1489,11 +1331,12 @@
       <c r="E10" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F10" s="6">
+      <c r="F10" s="3"/>
+      <c r="G10" s="6">
         <v>46024</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
         <v>36</v>
       </c>
@@ -1509,11 +1352,11 @@
       <c r="E11" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="F11" s="7">
+      <c r="G11" s="7">
         <v>46024</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
         <v>39</v>
       </c>
@@ -1529,11 +1372,12 @@
       <c r="E12" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F12" s="6">
+      <c r="F12" s="3"/>
+      <c r="G12" s="6">
         <v>46024</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
         <v>42</v>
       </c>
@@ -1549,11 +1393,11 @@
       <c r="E13" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="F13" s="7">
+      <c r="G13" s="7">
         <v>46024</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
         <v>45</v>
       </c>
@@ -1569,11 +1413,12 @@
       <c r="E14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F14" s="6">
+      <c r="F14" s="3"/>
+      <c r="G14" s="6">
         <v>46024</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
         <v>48</v>
       </c>
@@ -1589,11 +1434,11 @@
       <c r="E15" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="F15" s="7">
+      <c r="G15" s="7">
         <v>46024</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
         <v>52</v>
       </c>
@@ -1609,11 +1454,12 @@
       <c r="E16" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F16" s="6">
+      <c r="F16" s="3"/>
+      <c r="G16" s="6">
         <v>46024</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
         <v>56</v>
       </c>
@@ -1629,11 +1475,11 @@
       <c r="E17" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="F17" s="7">
+      <c r="G17" s="7">
         <v>46024</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
         <v>59</v>
       </c>
@@ -1649,11 +1495,12 @@
       <c r="E18" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F18" s="6">
+      <c r="F18" s="3"/>
+      <c r="G18" s="6">
         <v>46025</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
         <v>62</v>
       </c>
@@ -1669,11 +1516,11 @@
       <c r="E19" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="F19" s="7">
+      <c r="G19" s="7">
         <v>46025</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
         <v>65</v>
       </c>
@@ -1689,11 +1536,12 @@
       <c r="E20" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F20" s="6">
+      <c r="F20" s="3"/>
+      <c r="G20" s="6">
         <v>46025</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
         <v>67</v>
       </c>
@@ -1709,11 +1557,11 @@
       <c r="E21" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="F21" s="7">
+      <c r="G21" s="7">
         <v>46025</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
         <v>69</v>
       </c>
@@ -1729,11 +1577,12 @@
       <c r="E22" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F22" s="6">
+      <c r="F22" s="3"/>
+      <c r="G22" s="6">
         <v>46025</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
         <v>71</v>
       </c>
@@ -1749,11 +1598,11 @@
       <c r="E23" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="F23" s="7">
+      <c r="G23" s="7">
         <v>46025</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24" s="3" t="s">
         <v>74</v>
       </c>
@@ -1769,11 +1618,12 @@
       <c r="E24" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F24" s="6">
+      <c r="F24" s="3"/>
+      <c r="G24" s="6">
         <v>46025</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
         <v>77</v>
       </c>
@@ -1789,11 +1639,11 @@
       <c r="E25" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="F25" s="7">
+      <c r="G25" s="7">
         <v>46025</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A26" s="3" t="s">
         <v>79</v>
       </c>
@@ -1809,11 +1659,12 @@
       <c r="E26" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F26" s="6">
+      <c r="F26" s="3"/>
+      <c r="G26" s="6">
         <v>46026</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
         <v>81</v>
       </c>
@@ -1829,11 +1680,11 @@
       <c r="E27" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="F27" s="7">
+      <c r="G27" s="7">
         <v>46026</v>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A28" s="3" t="s">
         <v>83</v>
       </c>
@@ -1849,11 +1700,12 @@
       <c r="E28" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F28" s="6">
+      <c r="F28" s="3"/>
+      <c r="G28" s="6">
         <v>46026</v>
       </c>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
         <v>86</v>
       </c>
@@ -1869,11 +1721,11 @@
       <c r="E29" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="F29" s="7">
+      <c r="G29" s="7">
         <v>46026</v>
       </c>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A30" s="3" t="s">
         <v>88</v>
       </c>
@@ -1889,11 +1741,12 @@
       <c r="E30" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F30" s="6">
+      <c r="F30" s="3"/>
+      <c r="G30" s="6">
         <v>46026</v>
       </c>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
         <v>91</v>
       </c>
@@ -1909,11 +1762,11 @@
       <c r="E31" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="F31" s="7">
+      <c r="G31" s="7">
         <v>46026</v>
       </c>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A32" s="3" t="s">
         <v>93</v>
       </c>
@@ -1929,11 +1782,12 @@
       <c r="E32" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F32" s="6">
+      <c r="F32" s="3"/>
+      <c r="G32" s="6">
         <v>46026</v>
       </c>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
         <v>95</v>
       </c>
@@ -1949,11 +1803,11 @@
       <c r="E33" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="F33" s="7">
+      <c r="G33" s="7">
         <v>46026</v>
       </c>
     </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A34" s="3" t="s">
         <v>97</v>
       </c>
@@ -1969,11 +1823,12 @@
       <c r="E34" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F34" s="6">
+      <c r="F34" s="3"/>
+      <c r="G34" s="6">
         <v>46027</v>
       </c>
     </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
         <v>99</v>
       </c>
@@ -1989,11 +1844,11 @@
       <c r="E35" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="F35" s="7">
+      <c r="G35" s="7">
         <v>46027</v>
       </c>
     </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A36" s="3" t="s">
         <v>102</v>
       </c>
@@ -2009,11 +1864,12 @@
       <c r="E36" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F36" s="6">
+      <c r="F36" s="3"/>
+      <c r="G36" s="6">
         <v>46027</v>
       </c>
     </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
         <v>104</v>
       </c>
@@ -2029,11 +1885,11 @@
       <c r="E37" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="F37" s="7">
+      <c r="G37" s="7">
         <v>46027</v>
       </c>
     </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A38" s="3" t="s">
         <v>107</v>
       </c>
@@ -2049,11 +1905,12 @@
       <c r="E38" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F38" s="6">
+      <c r="F38" s="3"/>
+      <c r="G38" s="6">
         <v>46027</v>
       </c>
     </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
         <v>109</v>
       </c>
@@ -2069,11 +1926,11 @@
       <c r="E39" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="F39" s="7">
+      <c r="G39" s="7">
         <v>46027</v>
       </c>
     </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A40" s="3" t="s">
         <v>111</v>
       </c>
@@ -2089,11 +1946,12 @@
       <c r="E40" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F40" s="6">
+      <c r="F40" s="3"/>
+      <c r="G40" s="6">
         <v>46027</v>
       </c>
     </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
         <v>113</v>
       </c>
@@ -2109,11 +1967,11 @@
       <c r="E41" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="F41" s="7">
+      <c r="G41" s="7">
         <v>46027</v>
       </c>
     </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A42" s="3" t="s">
         <v>115</v>
       </c>
@@ -2129,11 +1987,12 @@
       <c r="E42" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F42" s="6">
+      <c r="F42" s="3"/>
+      <c r="G42" s="6">
         <v>46028</v>
       </c>
     </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
         <v>117</v>
       </c>
@@ -2149,11 +2008,11 @@
       <c r="E43" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="F43" s="7">
+      <c r="G43" s="7">
         <v>46028</v>
       </c>
     </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A44" s="3" t="s">
         <v>119</v>
       </c>
@@ -2169,11 +2028,12 @@
       <c r="E44" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F44" s="6">
+      <c r="F44" s="3"/>
+      <c r="G44" s="6">
         <v>46028</v>
       </c>
     </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
         <v>121</v>
       </c>
@@ -2189,11 +2049,11 @@
       <c r="E45" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="F45" s="7">
+      <c r="G45" s="7">
         <v>46028</v>
       </c>
     </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A46" s="3" t="s">
         <v>124</v>
       </c>
@@ -2209,11 +2069,12 @@
       <c r="E46" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F46" s="6">
+      <c r="F46" s="3"/>
+      <c r="G46" s="6">
         <v>46028</v>
       </c>
     </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A47" s="1" t="s">
         <v>126</v>
       </c>
@@ -2229,11 +2090,11 @@
       <c r="E47" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="F47" s="7">
+      <c r="G47" s="7">
         <v>46028</v>
       </c>
     </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A48" s="3" t="s">
         <v>128</v>
       </c>
@@ -2249,11 +2110,12 @@
       <c r="E48" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F48" s="6">
+      <c r="F48" s="3"/>
+      <c r="G48" s="6">
         <v>46028</v>
       </c>
     </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A49" s="1" t="s">
         <v>130</v>
       </c>
@@ -2269,11 +2131,11 @@
       <c r="E49" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="F49" s="7">
+      <c r="G49" s="7">
         <v>46028</v>
       </c>
     </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A50" s="3" t="s">
         <v>132</v>
       </c>
@@ -2289,11 +2151,12 @@
       <c r="E50" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F50" s="6">
+      <c r="F50" s="3"/>
+      <c r="G50" s="6">
         <v>46029</v>
       </c>
     </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A51" s="1" t="s">
         <v>135</v>
       </c>
@@ -2309,11 +2172,11 @@
       <c r="E51" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="F51" s="7">
+      <c r="G51" s="7">
         <v>46029</v>
       </c>
     </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A52" s="3" t="s">
         <v>137</v>
       </c>
@@ -2329,11 +2192,12 @@
       <c r="E52" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F52" s="6">
+      <c r="F52" s="3"/>
+      <c r="G52" s="6">
         <v>46029</v>
       </c>
     </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A53" s="1" t="s">
         <v>139</v>
       </c>
@@ -2349,11 +2213,11 @@
       <c r="E53" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="F53" s="7">
+      <c r="G53" s="7">
         <v>46029</v>
       </c>
     </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A54" s="3" t="s">
         <v>141</v>
       </c>
@@ -2369,11 +2233,12 @@
       <c r="E54" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F54" s="6">
+      <c r="F54" s="3"/>
+      <c r="G54" s="6">
         <v>46029</v>
       </c>
     </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A55" s="1" t="s">
         <v>143</v>
       </c>
@@ -2389,11 +2254,11 @@
       <c r="E55" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="F55" s="7">
+      <c r="G55" s="7">
         <v>46029</v>
       </c>
     </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A56" s="3" t="s">
         <v>145</v>
       </c>
@@ -2409,11 +2274,12 @@
       <c r="E56" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F56" s="6">
+      <c r="F56" s="3"/>
+      <c r="G56" s="6">
         <v>46029</v>
       </c>
     </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A57" s="1" t="s">
         <v>147</v>
       </c>
@@ -2429,11 +2295,11 @@
       <c r="E57" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="F57" s="7">
+      <c r="G57" s="7">
         <v>46029</v>
       </c>
     </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A58" s="3" t="s">
         <v>14</v>
       </c>
@@ -2449,11 +2315,12 @@
       <c r="E58" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F58" s="6">
+      <c r="F58" s="3"/>
+      <c r="G58" s="6">
         <v>46030</v>
       </c>
     </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A59" s="3" t="s">
         <v>14</v>
       </c>
@@ -2469,11 +2336,12 @@
       <c r="E59" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F59" s="6">
+      <c r="F59" s="3"/>
+      <c r="G59" s="6">
         <v>46030</v>
       </c>
     </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A60" s="1" t="s">
         <v>36</v>
       </c>
@@ -2489,11 +2357,11 @@
       <c r="E60" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="F60" s="7">
+      <c r="G60" s="7">
         <v>46030</v>
       </c>
     </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A61" s="1" t="s">
         <v>36</v>
       </c>
@@ -2509,11 +2377,11 @@
       <c r="E61" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="F61" s="7">
+      <c r="G61" s="7">
         <v>46030</v>
       </c>
     </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A62" s="1" t="s">
         <v>36</v>
       </c>
@@ -2529,11 +2397,11 @@
       <c r="E62" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="F62" s="7">
+      <c r="G62" s="7">
         <v>46030</v>
       </c>
     </row>
-    <row r="63" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A63" s="3" t="s">
         <v>6</v>
       </c>
@@ -2549,11 +2417,12 @@
       <c r="E63" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F63" s="6">
+      <c r="F63" s="3"/>
+      <c r="G63" s="6">
         <v>46030</v>
       </c>
     </row>
-    <row r="64" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A64" s="3" t="s">
         <v>6</v>
       </c>
@@ -2569,11 +2438,12 @@
       <c r="E64" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F64" s="6">
+      <c r="F64" s="3"/>
+      <c r="G64" s="6">
         <v>46030</v>
       </c>
     </row>
-    <row r="65" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A65" s="1" t="s">
         <v>25</v>
       </c>
@@ -2589,11 +2459,11 @@
       <c r="E65" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="F65" s="7">
+      <c r="G65" s="7">
         <v>46030</v>
       </c>
     </row>
-    <row r="66" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A66" s="1" t="s">
         <v>25</v>
       </c>
@@ -2609,11 +2479,11 @@
       <c r="E66" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="F66" s="7">
+      <c r="G66" s="7">
         <v>46030</v>
       </c>
     </row>
-    <row r="67" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A67" s="1" t="s">
         <v>25</v>
       </c>
@@ -2629,11 +2499,11 @@
       <c r="E67" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="F67" s="7">
+      <c r="G67" s="7">
         <v>46030</v>
       </c>
     </row>
-    <row r="68" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A68" s="3" t="s">
         <v>14</v>
       </c>
@@ -2649,11 +2519,12 @@
       <c r="E68" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F68" s="6">
+      <c r="F68" s="3"/>
+      <c r="G68" s="6">
         <v>46031</v>
       </c>
     </row>
-    <row r="69" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A69" s="3" t="s">
         <v>14</v>
       </c>
@@ -2669,11 +2540,12 @@
       <c r="E69" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F69" s="6">
+      <c r="F69" s="3"/>
+      <c r="G69" s="6">
         <v>46031</v>
       </c>
     </row>
-    <row r="70" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A70" s="3" t="s">
         <v>14</v>
       </c>
@@ -2689,11 +2561,12 @@
       <c r="E70" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F70" s="6">
+      <c r="F70" s="3"/>
+      <c r="G70" s="6">
         <v>46031</v>
       </c>
     </row>
-    <row r="71" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A71" s="1" t="s">
         <v>6</v>
       </c>
@@ -2709,11 +2582,11 @@
       <c r="E71" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="F71" s="7">
+      <c r="G71" s="7">
         <v>46031</v>
       </c>
     </row>
-    <row r="72" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A72" s="1" t="s">
         <v>6</v>
       </c>
@@ -2729,11 +2602,11 @@
       <c r="E72" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="F72" s="7">
+      <c r="G72" s="7">
         <v>46031</v>
       </c>
     </row>
-    <row r="73" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A73" s="1" t="s">
         <v>6</v>
       </c>
@@ -2749,11 +2622,11 @@
       <c r="E73" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="F73" s="7">
+      <c r="G73" s="7">
         <v>46031</v>
       </c>
     </row>
-    <row r="74" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A74" s="3" t="s">
         <v>46</v>
       </c>
@@ -2769,11 +2642,12 @@
       <c r="E74" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F74" s="6">
+      <c r="F74" s="3"/>
+      <c r="G74" s="6">
         <v>46031</v>
       </c>
     </row>
-    <row r="75" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A75" s="3" t="s">
         <v>46</v>
       </c>
@@ -2789,11 +2663,12 @@
       <c r="E75" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F75" s="6">
+      <c r="F75" s="3"/>
+      <c r="G75" s="6">
         <v>46031</v>
       </c>
     </row>
-    <row r="76" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A76" s="1" t="s">
         <v>53</v>
       </c>
@@ -2809,11 +2684,11 @@
       <c r="E76" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="F76" s="7">
+      <c r="G76" s="7">
         <v>46031</v>
       </c>
     </row>
-    <row r="77" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A77" s="1" t="s">
         <v>53</v>
       </c>
@@ -2829,11 +2704,11 @@
       <c r="E77" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="F77" s="7">
+      <c r="G77" s="7">
         <v>46031</v>
       </c>
     </row>
-    <row r="78" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A78" s="3" t="s">
         <v>6</v>
       </c>
@@ -2849,11 +2724,12 @@
       <c r="E78" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F78" s="6">
+      <c r="F78" s="3"/>
+      <c r="G78" s="6">
         <v>46032</v>
       </c>
     </row>
-    <row r="79" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A79" s="3" t="s">
         <v>6</v>
       </c>
@@ -2869,11 +2745,12 @@
       <c r="E79" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F79" s="6">
+      <c r="F79" s="3"/>
+      <c r="G79" s="6">
         <v>46032</v>
       </c>
     </row>
-    <row r="80" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A80" s="1" t="s">
         <v>14</v>
       </c>
@@ -2889,11 +2766,11 @@
       <c r="E80" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="F80" s="7">
+      <c r="G80" s="7">
         <v>46032</v>
       </c>
     </row>
-    <row r="81" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A81" s="1" t="s">
         <v>14</v>
       </c>
@@ -2909,11 +2786,11 @@
       <c r="E81" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="F81" s="7">
+      <c r="G81" s="7">
         <v>46032</v>
       </c>
     </row>
-    <row r="82" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A82" s="3" t="s">
         <v>36</v>
       </c>
@@ -2929,11 +2806,12 @@
       <c r="E82" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F82" s="6">
+      <c r="F82" s="3"/>
+      <c r="G82" s="6">
         <v>46032</v>
       </c>
     </row>
-    <row r="83" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A83" s="3" t="s">
         <v>36</v>
       </c>
@@ -2949,11 +2827,12 @@
       <c r="E83" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F83" s="6">
+      <c r="F83" s="3"/>
+      <c r="G83" s="6">
         <v>46032</v>
       </c>
     </row>
-    <row r="84" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A84" s="1" t="s">
         <v>53</v>
       </c>
@@ -2969,11 +2848,11 @@
       <c r="E84" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="F84" s="7">
+      <c r="G84" s="7">
         <v>46032</v>
       </c>
     </row>
-    <row r="85" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A85" s="1" t="s">
         <v>53</v>
       </c>
@@ -2989,11 +2868,11 @@
       <c r="E85" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="F85" s="7">
+      <c r="G85" s="7">
         <v>46032</v>
       </c>
     </row>
-    <row r="86" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A86" s="3" t="s">
         <v>20</v>
       </c>
@@ -3009,11 +2888,12 @@
       <c r="E86" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F86" s="6">
+      <c r="F86" s="3"/>
+      <c r="G86" s="6">
         <v>46033</v>
       </c>
     </row>
-    <row r="87" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A87" s="3" t="s">
         <v>20</v>
       </c>
@@ -3029,11 +2909,12 @@
       <c r="E87" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F87" s="6">
+      <c r="F87" s="3"/>
+      <c r="G87" s="6">
         <v>46033</v>
       </c>
     </row>
-    <row r="88" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A88" s="3" t="s">
         <v>20</v>
       </c>
@@ -3049,11 +2930,12 @@
       <c r="E88" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F88" s="6">
+      <c r="F88" s="3"/>
+      <c r="G88" s="6">
         <v>46033</v>
       </c>
     </row>
-    <row r="89" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A89" s="1" t="s">
         <v>34</v>
       </c>
@@ -3069,11 +2951,11 @@
       <c r="E89" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="F89" s="7">
+      <c r="G89" s="7">
         <v>46033</v>
       </c>
     </row>
-    <row r="90" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A90" s="1" t="s">
         <v>34</v>
       </c>
@@ -3089,11 +2971,11 @@
       <c r="E90" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="F90" s="7">
+      <c r="G90" s="7">
         <v>46033</v>
       </c>
     </row>
-    <row r="91" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A91" s="1" t="s">
         <v>34</v>
       </c>
@@ -3109,11 +2991,11 @@
       <c r="E91" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="F91" s="7">
+      <c r="G91" s="7">
         <v>46033</v>
       </c>
     </row>
-    <row r="92" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A92" s="3" t="s">
         <v>40</v>
       </c>
@@ -3129,11 +3011,12 @@
       <c r="E92" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F92" s="6">
+      <c r="F92" s="3"/>
+      <c r="G92" s="6">
         <v>46033</v>
       </c>
     </row>
-    <row r="93" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A93" s="3" t="s">
         <v>40</v>
       </c>
@@ -3149,11 +3032,12 @@
       <c r="E93" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F93" s="6">
+      <c r="F93" s="3"/>
+      <c r="G93" s="6">
         <v>46033</v>
       </c>
     </row>
-    <row r="94" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A94" s="1" t="s">
         <v>42</v>
       </c>
@@ -3169,11 +3053,11 @@
       <c r="E94" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="F94" s="7">
+      <c r="G94" s="7">
         <v>46033</v>
       </c>
     </row>
-    <row r="95" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A95" s="1" t="s">
         <v>42</v>
       </c>
@@ -3189,11 +3073,11 @@
       <c r="E95" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="F95" s="7">
+      <c r="G95" s="7">
         <v>46033</v>
       </c>
     </row>
-    <row r="96" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A96" s="1" t="s">
         <v>42</v>
       </c>
@@ -3209,11 +3093,11 @@
       <c r="E96" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="F96" s="7">
+      <c r="G96" s="7">
         <v>46033</v>
       </c>
     </row>
-    <row r="97" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A97" s="3" t="s">
         <v>20</v>
       </c>
@@ -3229,11 +3113,12 @@
       <c r="E97" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F97" s="6">
+      <c r="F97" s="3"/>
+      <c r="G97" s="6">
         <v>46033</v>
       </c>
     </row>
-    <row r="98" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A98" s="3" t="s">
         <v>20</v>
       </c>
@@ -3249,11 +3134,12 @@
       <c r="E98" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F98" s="6">
+      <c r="F98" s="3"/>
+      <c r="G98" s="6">
         <v>46033</v>
       </c>
     </row>
-    <row r="99" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A99" s="3" t="s">
         <v>20</v>
       </c>
@@ -3269,11 +3155,12 @@
       <c r="E99" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F99" s="6">
+      <c r="F99" s="3"/>
+      <c r="G99" s="6">
         <v>46033</v>
       </c>
     </row>
-    <row r="100" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A100" s="1" t="s">
         <v>31</v>
       </c>
@@ -3289,11 +3176,11 @@
       <c r="E100" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="F100" s="7">
+      <c r="G100" s="7">
         <v>46033</v>
       </c>
     </row>
-    <row r="101" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A101" s="1" t="s">
         <v>31</v>
       </c>
@@ -3309,11 +3196,11 @@
       <c r="E101" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="F101" s="7">
+      <c r="G101" s="7">
         <v>46033</v>
       </c>
     </row>
-    <row r="102" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A102" s="3" t="s">
         <v>57</v>
       </c>
@@ -3329,11 +3216,12 @@
       <c r="E102" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F102" s="6">
+      <c r="F102" s="3"/>
+      <c r="G102" s="6">
         <v>46034</v>
       </c>
     </row>
-    <row r="103" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A103" s="3" t="s">
         <v>57</v>
       </c>
@@ -3349,11 +3237,12 @@
       <c r="E103" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F103" s="6">
+      <c r="F103" s="3"/>
+      <c r="G103" s="6">
         <v>46034</v>
       </c>
     </row>
-    <row r="104" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A104" s="1" t="s">
         <v>40</v>
       </c>
@@ -3369,11 +3258,11 @@
       <c r="E104" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="F104" s="7">
+      <c r="G104" s="7">
         <v>46034</v>
       </c>
     </row>
-    <row r="105" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A105" s="1" t="s">
         <v>40</v>
       </c>
@@ -3389,11 +3278,11 @@
       <c r="E105" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="F105" s="7">
+      <c r="G105" s="7">
         <v>46034</v>
       </c>
     </row>
-    <row r="106" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A106" s="1" t="s">
         <v>40</v>
       </c>
@@ -3409,11 +3298,11 @@
       <c r="E106" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="F106" s="7">
+      <c r="G106" s="7">
         <v>46034</v>
       </c>
     </row>
-    <row r="107" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A107" s="3" t="s">
         <v>42</v>
       </c>
@@ -3429,11 +3318,12 @@
       <c r="E107" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F107" s="6">
+      <c r="F107" s="3"/>
+      <c r="G107" s="6">
         <v>46034</v>
       </c>
     </row>
-    <row r="108" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A108" s="3" t="s">
         <v>42</v>
       </c>
@@ -3449,11 +3339,12 @@
       <c r="E108" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F108" s="6">
+      <c r="F108" s="3"/>
+      <c r="G108" s="6">
         <v>46034</v>
       </c>
     </row>
-    <row r="109" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A109" s="1" t="s">
         <v>20</v>
       </c>
@@ -3469,11 +3360,11 @@
       <c r="E109" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="F109" s="7">
+      <c r="G109" s="7">
         <v>46034</v>
       </c>
     </row>
-    <row r="110" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A110" s="1" t="s">
         <v>20</v>
       </c>
@@ -3489,11 +3380,11 @@
       <c r="E110" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="F110" s="7">
+      <c r="G110" s="7">
         <v>46034</v>
       </c>
     </row>
-    <row r="111" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A111" s="1" t="s">
         <v>20</v>
       </c>
@@ -3509,11 +3400,11 @@
       <c r="E111" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="F111" s="7">
+      <c r="G111" s="7">
         <v>46034</v>
       </c>
     </row>
-    <row r="112" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A112" s="3" t="s">
         <v>34</v>
       </c>
@@ -3529,11 +3420,12 @@
       <c r="E112" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F112" s="6">
+      <c r="F112" s="3"/>
+      <c r="G112" s="6">
         <v>46034</v>
       </c>
     </row>
-    <row r="113" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A113" s="3" t="s">
         <v>34</v>
       </c>
@@ -3549,11 +3441,12 @@
       <c r="E113" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F113" s="6">
+      <c r="F113" s="3"/>
+      <c r="G113" s="6">
         <v>46034</v>
       </c>
     </row>
-    <row r="114" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A114" s="1" t="s">
         <v>27</v>
       </c>
@@ -3569,11 +3462,11 @@
       <c r="E114" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="F114" s="7">
+      <c r="G114" s="7">
         <v>46034</v>
       </c>
     </row>
-    <row r="115" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A115" s="1" t="s">
         <v>27</v>
       </c>
@@ -3589,11 +3482,11 @@
       <c r="E115" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="F115" s="7">
+      <c r="G115" s="7">
         <v>46034</v>
       </c>
     </row>
-    <row r="116" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A116" s="3" t="s">
         <v>71</v>
       </c>
@@ -3609,11 +3502,12 @@
       <c r="E116" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F116" s="6">
+      <c r="F116" s="3"/>
+      <c r="G116" s="6">
         <v>46035</v>
       </c>
     </row>
-    <row r="117" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A117" s="3" t="s">
         <v>71</v>
       </c>
@@ -3629,11 +3523,12 @@
       <c r="E117" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F117" s="6">
+      <c r="F117" s="3"/>
+      <c r="G117" s="6">
         <v>46035</v>
       </c>
     </row>
-    <row r="118" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A118" s="3" t="s">
         <v>71</v>
       </c>
@@ -3649,11 +3544,12 @@
       <c r="E118" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F118" s="6">
+      <c r="F118" s="3"/>
+      <c r="G118" s="6">
         <v>46035</v>
       </c>
     </row>
-    <row r="119" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A119" s="1" t="s">
         <v>59</v>
       </c>
@@ -3669,11 +3565,11 @@
       <c r="E119" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="F119" s="7">
+      <c r="G119" s="7">
         <v>46035</v>
       </c>
     </row>
-    <row r="120" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A120" s="1" t="s">
         <v>59</v>
       </c>
@@ -3689,11 +3585,11 @@
       <c r="E120" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="F120" s="7">
+      <c r="G120" s="7">
         <v>46035</v>
       </c>
     </row>
-    <row r="121" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A121" s="3" t="s">
         <v>74</v>
       </c>
@@ -3709,11 +3605,12 @@
       <c r="E121" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F121" s="6">
+      <c r="F121" s="3"/>
+      <c r="G121" s="6">
         <v>46035</v>
       </c>
     </row>
-    <row r="122" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A122" s="3" t="s">
         <v>74</v>
       </c>
@@ -3729,11 +3626,12 @@
       <c r="E122" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F122" s="6">
+      <c r="F122" s="3"/>
+      <c r="G122" s="6">
         <v>46035</v>
       </c>
     </row>
-    <row r="123" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A123" s="1" t="s">
         <v>89</v>
       </c>
@@ -3749,11 +3647,11 @@
       <c r="E123" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="F123" s="7">
+      <c r="G123" s="7">
         <v>46035</v>
       </c>
     </row>
-    <row r="124" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A124" s="1" t="s">
         <v>89</v>
       </c>
@@ -3769,11 +3667,11 @@
       <c r="E124" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="F124" s="7">
+      <c r="G124" s="7">
         <v>46035</v>
       </c>
     </row>
-    <row r="125" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A125" s="3" t="s">
         <v>63</v>
       </c>
@@ -3789,11 +3687,12 @@
       <c r="E125" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F125" s="6">
+      <c r="F125" s="3"/>
+      <c r="G125" s="6">
         <v>46035</v>
       </c>
     </row>
-    <row r="126" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A126" s="3" t="s">
         <v>63</v>
       </c>
@@ -3809,11 +3708,12 @@
       <c r="E126" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F126" s="6">
+      <c r="F126" s="3"/>
+      <c r="G126" s="6">
         <v>46035</v>
       </c>
     </row>
-    <row r="127" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A127" s="1" t="s">
         <v>93</v>
       </c>
@@ -3829,11 +3729,11 @@
       <c r="E127" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="F127" s="7">
+      <c r="G127" s="7">
         <v>46036</v>
       </c>
     </row>
-    <row r="128" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A128" s="1" t="s">
         <v>93</v>
       </c>
@@ -3849,11 +3749,11 @@
       <c r="E128" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="F128" s="7">
+      <c r="G128" s="7">
         <v>46036</v>
       </c>
     </row>
-    <row r="129" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A129" s="1" t="s">
         <v>93</v>
       </c>
@@ -3869,11 +3769,11 @@
       <c r="E129" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="F129" s="7">
+      <c r="G129" s="7">
         <v>46036</v>
       </c>
     </row>
-    <row r="130" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A130" s="3" t="s">
         <v>69</v>
       </c>
@@ -3889,11 +3789,12 @@
       <c r="E130" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F130" s="6">
+      <c r="F130" s="3"/>
+      <c r="G130" s="6">
         <v>46036</v>
       </c>
     </row>
-    <row r="131" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A131" s="3" t="s">
         <v>69</v>
       </c>
@@ -3909,11 +3810,12 @@
       <c r="E131" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F131" s="6">
+      <c r="F131" s="3"/>
+      <c r="G131" s="6">
         <v>46036</v>
       </c>
     </row>
-    <row r="132" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A132" s="1" t="s">
         <v>71</v>
       </c>
@@ -3929,11 +3831,11 @@
       <c r="E132" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="F132" s="7">
+      <c r="G132" s="7">
         <v>46036</v>
       </c>
     </row>
-    <row r="133" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A133" s="1" t="s">
         <v>71</v>
       </c>
@@ -3949,11 +3851,11 @@
       <c r="E133" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="F133" s="7">
+      <c r="G133" s="7">
         <v>46036</v>
       </c>
     </row>
-    <row r="134" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A134" s="3" t="s">
         <v>89</v>
       </c>
@@ -3969,11 +3871,12 @@
       <c r="E134" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F134" s="6">
+      <c r="F134" s="3"/>
+      <c r="G134" s="6">
         <v>46036</v>
       </c>
     </row>
-    <row r="135" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A135" s="3" t="s">
         <v>89</v>
       </c>
@@ -3989,11 +3892,12 @@
       <c r="E135" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F135" s="6">
+      <c r="F135" s="3"/>
+      <c r="G135" s="6">
         <v>46036</v>
       </c>
     </row>
-    <row r="136" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A136" s="3" t="s">
         <v>89</v>
       </c>
@@ -4009,11 +3913,12 @@
       <c r="E136" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F136" s="6">
+      <c r="F136" s="3"/>
+      <c r="G136" s="6">
         <v>46036</v>
       </c>
     </row>
-    <row r="137" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A137" s="3" t="s">
         <v>89</v>
       </c>
@@ -4029,11 +3934,12 @@
       <c r="E137" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F137" s="6">
+      <c r="F137" s="3"/>
+      <c r="G137" s="6">
         <v>46036</v>
       </c>
     </row>
-    <row r="138" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A138" s="1" t="s">
         <v>80</v>
       </c>
@@ -4049,11 +3955,11 @@
       <c r="E138" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="F138" s="7">
+      <c r="G138" s="7">
         <v>46036</v>
       </c>
     </row>
-    <row r="139" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A139" s="1" t="s">
         <v>80</v>
       </c>
@@ -4069,11 +3975,11 @@
       <c r="E139" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="F139" s="7">
+      <c r="G139" s="7">
         <v>46036</v>
       </c>
     </row>
-    <row r="140" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A140" s="3" t="s">
         <v>69</v>
       </c>
@@ -4089,11 +3995,12 @@
       <c r="E140" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F140" s="6">
+      <c r="F140" s="3"/>
+      <c r="G140" s="6">
         <v>46037</v>
       </c>
     </row>
-    <row r="141" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A141" s="3" t="s">
         <v>69</v>
       </c>
@@ -4109,11 +4016,12 @@
       <c r="E141" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F141" s="6">
+      <c r="F141" s="3"/>
+      <c r="G141" s="6">
         <v>46037</v>
       </c>
     </row>
-    <row r="142" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A142" s="1" t="s">
         <v>80</v>
       </c>
@@ -4129,11 +4037,11 @@
       <c r="E142" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="F142" s="7">
+      <c r="G142" s="7">
         <v>46037</v>
       </c>
     </row>
-    <row r="143" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A143" s="1" t="s">
         <v>80</v>
       </c>
@@ -4149,11 +4057,11 @@
       <c r="E143" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="F143" s="7">
+      <c r="G143" s="7">
         <v>46037</v>
       </c>
     </row>
-    <row r="144" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A144" s="3" t="s">
         <v>96</v>
       </c>
@@ -4169,11 +4077,12 @@
       <c r="E144" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F144" s="6">
+      <c r="F144" s="3"/>
+      <c r="G144" s="6">
         <v>46037</v>
       </c>
     </row>
-    <row r="145" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A145" s="3" t="s">
         <v>96</v>
       </c>
@@ -4189,11 +4098,12 @@
       <c r="E145" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F145" s="6">
+      <c r="F145" s="3"/>
+      <c r="G145" s="6">
         <v>46037</v>
       </c>
     </row>
-    <row r="146" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A146" s="3" t="s">
         <v>96</v>
       </c>
@@ -4209,11 +4119,12 @@
       <c r="E146" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F146" s="6">
+      <c r="F146" s="3"/>
+      <c r="G146" s="6">
         <v>46037</v>
       </c>
     </row>
-    <row r="147" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A147" s="1" t="s">
         <v>91</v>
       </c>
@@ -4229,11 +4140,11 @@
       <c r="E147" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="F147" s="7">
+      <c r="G147" s="7">
         <v>46037</v>
       </c>
     </row>
-    <row r="148" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A148" s="1" t="s">
         <v>91</v>
       </c>
@@ -4249,11 +4160,11 @@
       <c r="E148" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="F148" s="7">
+      <c r="G148" s="7">
         <v>46037</v>
       </c>
     </row>
-    <row r="149" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A149" s="3" t="s">
         <v>65</v>
       </c>
@@ -4269,11 +4180,12 @@
       <c r="E149" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F149" s="6">
+      <c r="F149" s="3"/>
+      <c r="G149" s="6">
         <v>46038</v>
       </c>
     </row>
-    <row r="150" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A150" s="3" t="s">
         <v>65</v>
       </c>
@@ -4289,11 +4201,12 @@
       <c r="E150" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F150" s="6">
+      <c r="F150" s="3"/>
+      <c r="G150" s="6">
         <v>46038</v>
       </c>
     </row>
-    <row r="151" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A151" s="3" t="s">
         <v>65</v>
       </c>
@@ -4309,11 +4222,12 @@
       <c r="E151" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F151" s="6">
+      <c r="F151" s="3"/>
+      <c r="G151" s="6">
         <v>46038</v>
       </c>
     </row>
-    <row r="152" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A152" s="1" t="s">
         <v>78</v>
       </c>
@@ -4329,11 +4243,11 @@
       <c r="E152" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="F152" s="7">
+      <c r="G152" s="7">
         <v>46038</v>
       </c>
     </row>
-    <row r="153" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A153" s="1" t="s">
         <v>78</v>
       </c>
@@ -4349,11 +4263,11 @@
       <c r="E153" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="F153" s="7">
+      <c r="G153" s="7">
         <v>46038</v>
       </c>
     </row>
-    <row r="154" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A154" s="1" t="s">
         <v>78</v>
       </c>
@@ -4369,11 +4283,11 @@
       <c r="E154" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="F154" s="7">
+      <c r="G154" s="7">
         <v>46038</v>
       </c>
     </row>
-    <row r="155" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A155" s="3" t="s">
         <v>91</v>
       </c>
@@ -4389,11 +4303,12 @@
       <c r="E155" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F155" s="6">
+      <c r="F155" s="3"/>
+      <c r="G155" s="6">
         <v>46038</v>
       </c>
     </row>
-    <row r="156" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A156" s="3" t="s">
         <v>91</v>
       </c>
@@ -4409,11 +4324,12 @@
       <c r="E156" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F156" s="6">
+      <c r="F156" s="3"/>
+      <c r="G156" s="6">
         <v>46038</v>
       </c>
     </row>
-    <row r="157" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A157" s="3" t="s">
         <v>86</v>
       </c>
@@ -4429,11 +4345,11 @@
       <c r="E157" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="F157" s="7">
+      <c r="G157" s="7">
         <v>46038</v>
       </c>
     </row>
-    <row r="158" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A158" s="1" t="s">
         <v>86</v>
       </c>
@@ -4449,11 +4365,11 @@
       <c r="E158" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="F158" s="7">
+      <c r="G158" s="7">
         <v>46038</v>
       </c>
     </row>
-    <row r="159" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A159" s="1" t="s">
         <v>86</v>
       </c>
@@ -4469,11 +4385,11 @@
       <c r="E159" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="F159" s="7">
+      <c r="G159" s="7">
         <v>46038</v>
       </c>
     </row>
-    <row r="160" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A160" s="3" t="s">
         <v>84</v>
       </c>
@@ -4489,11 +4405,12 @@
       <c r="E160" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F160" s="6">
+      <c r="F160" s="3"/>
+      <c r="G160" s="6">
         <v>46038</v>
       </c>
     </row>
-    <row r="161" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A161" s="3" t="s">
         <v>84</v>
       </c>
@@ -4509,11 +4426,12 @@
       <c r="E161" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F161" s="6">
+      <c r="F161" s="3"/>
+      <c r="G161" s="6">
         <v>46038</v>
       </c>
     </row>
-    <row r="162" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A162" s="1" t="s">
         <v>96</v>
       </c>
@@ -4529,11 +4447,11 @@
       <c r="E162" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="F162" s="7">
+      <c r="G162" s="7">
         <v>46039</v>
       </c>
     </row>
-    <row r="163" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A163" s="1" t="s">
         <v>96</v>
       </c>
@@ -4549,11 +4467,11 @@
       <c r="E163" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="F163" s="7">
+      <c r="G163" s="7">
         <v>46039</v>
       </c>
     </row>
-    <row r="164" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A164" s="1" t="s">
         <v>96</v>
       </c>
@@ -4569,11 +4487,11 @@
       <c r="E164" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="F164" s="7">
+      <c r="G164" s="7">
         <v>46039</v>
       </c>
     </row>
-    <row r="165" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A165" s="3" t="s">
         <v>65</v>
       </c>
@@ -4589,11 +4507,12 @@
       <c r="E165" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F165" s="6">
+      <c r="F165" s="3"/>
+      <c r="G165" s="6">
         <v>46039</v>
       </c>
     </row>
-    <row r="166" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A166" s="3" t="s">
         <v>65</v>
       </c>
@@ -4609,11 +4528,12 @@
       <c r="E166" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F166" s="6">
+      <c r="F166" s="3"/>
+      <c r="G166" s="6">
         <v>46039</v>
       </c>
     </row>
-    <row r="167" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A167" s="1" t="s">
         <v>78</v>
       </c>
@@ -4629,11 +4549,11 @@
       <c r="E167" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="F167" s="7">
+      <c r="G167" s="7">
         <v>46040</v>
       </c>
     </row>
-    <row r="168" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A168" s="1" t="s">
         <v>78</v>
       </c>
@@ -4649,11 +4569,11 @@
       <c r="E168" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="F168" s="7">
+      <c r="G168" s="7">
         <v>46040</v>
       </c>
     </row>
-    <row r="169" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A169" s="3" t="s">
         <v>96</v>
       </c>
@@ -4669,11 +4589,12 @@
       <c r="E169" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F169" s="6">
+      <c r="F169" s="3"/>
+      <c r="G169" s="6">
         <v>46040</v>
       </c>
     </row>
-    <row r="170" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A170" s="3" t="s">
         <v>96</v>
       </c>
@@ -4689,11 +4610,12 @@
       <c r="E170" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F170" s="6">
+      <c r="F170" s="3"/>
+      <c r="G170" s="6">
         <v>46040</v>
       </c>
     </row>
-    <row r="171" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A171" s="3" t="s">
         <v>96</v>
       </c>
@@ -4709,11 +4631,12 @@
       <c r="E171" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F171" s="6">
+      <c r="F171" s="3"/>
+      <c r="G171" s="6">
         <v>46040</v>
       </c>
     </row>
-    <row r="172" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A172" s="1" t="s">
         <v>103</v>
       </c>
@@ -4729,11 +4652,11 @@
       <c r="E172" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="F172" s="7">
+      <c r="G172" s="7">
         <v>46041</v>
       </c>
     </row>
-    <row r="173" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A173" s="1" t="s">
         <v>103</v>
       </c>
@@ -4749,11 +4672,11 @@
       <c r="E173" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="F173" s="7">
+      <c r="G173" s="7">
         <v>46041</v>
       </c>
     </row>
-    <row r="174" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A174" s="1" t="s">
         <v>103</v>
       </c>
@@ -4769,11 +4692,11 @@
       <c r="E174" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="F174" s="7">
+      <c r="G174" s="7">
         <v>46041</v>
       </c>
     </row>
-    <row r="175" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A175" s="3" t="s">
         <v>147</v>
       </c>
@@ -4789,11 +4712,12 @@
       <c r="E175" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F175" s="6">
+      <c r="F175" s="3"/>
+      <c r="G175" s="6">
         <v>46041</v>
       </c>
     </row>
-    <row r="176" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A176" s="3" t="s">
         <v>147</v>
       </c>
@@ -4809,11 +4733,12 @@
       <c r="E176" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F176" s="6">
+      <c r="F176" s="3"/>
+      <c r="G176" s="6">
         <v>46041</v>
       </c>
     </row>
-    <row r="177" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A177" s="1" t="s">
         <v>133</v>
       </c>
@@ -4829,11 +4754,11 @@
       <c r="E177" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="F177" s="7">
+      <c r="G177" s="7">
         <v>46041</v>
       </c>
     </row>
-    <row r="178" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A178" s="1" t="s">
         <v>133</v>
       </c>
@@ -4849,11 +4774,11 @@
       <c r="E178" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="F178" s="7">
+      <c r="G178" s="7">
         <v>46041</v>
       </c>
     </row>
-    <row r="179" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A179" s="1" t="s">
         <v>133</v>
       </c>
@@ -4869,11 +4794,11 @@
       <c r="E179" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="F179" s="7">
+      <c r="G179" s="7">
         <v>46041</v>
       </c>
     </row>
-    <row r="180" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A180" s="3" t="s">
         <v>127</v>
       </c>
@@ -4889,11 +4814,12 @@
       <c r="E180" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F180" s="6">
+      <c r="F180" s="3"/>
+      <c r="G180" s="6">
         <v>46041</v>
       </c>
     </row>
-    <row r="181" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A181" s="3" t="s">
         <v>127</v>
       </c>
@@ -4909,11 +4835,12 @@
       <c r="E181" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F181" s="6">
+      <c r="F181" s="3"/>
+      <c r="G181" s="6">
         <v>46041</v>
       </c>
     </row>
-    <row r="182" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A182" s="1" t="s">
         <v>147</v>
       </c>
@@ -4929,11 +4856,11 @@
       <c r="E182" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="F182" s="7">
+      <c r="G182" s="7">
         <v>46042</v>
       </c>
     </row>
-    <row r="183" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A183" s="1" t="s">
         <v>147</v>
       </c>
@@ -4949,11 +4876,11 @@
       <c r="E183" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="F183" s="7">
+      <c r="G183" s="7">
         <v>46042</v>
       </c>
     </row>
-    <row r="184" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A184" s="1" t="s">
         <v>147</v>
       </c>
@@ -4969,11 +4896,11 @@
       <c r="E184" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="F184" s="7">
+      <c r="G184" s="7">
         <v>46042</v>
       </c>
     </row>
-    <row r="185" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A185" s="3" t="s">
         <v>133</v>
       </c>
@@ -4989,11 +4916,12 @@
       <c r="E185" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F185" s="6">
+      <c r="F185" s="3"/>
+      <c r="G185" s="6">
         <v>46042</v>
       </c>
     </row>
-    <row r="186" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A186" s="3" t="s">
         <v>133</v>
       </c>
@@ -5009,11 +4937,12 @@
       <c r="E186" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F186" s="6">
+      <c r="F186" s="3"/>
+      <c r="G186" s="6">
         <v>46042</v>
       </c>
     </row>
-    <row r="187" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A187" s="1" t="s">
         <v>103</v>
       </c>
@@ -5029,11 +4958,11 @@
       <c r="E187" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="F187" s="7">
+      <c r="G187" s="7">
         <v>46042</v>
       </c>
     </row>
-    <row r="188" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A188" s="1" t="s">
         <v>103</v>
       </c>
@@ -5049,11 +4978,11 @@
       <c r="E188" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="F188" s="7">
+      <c r="G188" s="7">
         <v>46042</v>
       </c>
     </row>
-    <row r="189" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A189" s="1" t="s">
         <v>103</v>
       </c>
@@ -5069,11 +4998,11 @@
       <c r="E189" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="F189" s="7">
+      <c r="G189" s="7">
         <v>46042</v>
       </c>
     </row>
-    <row r="190" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A190" s="3" t="s">
         <v>136</v>
       </c>
@@ -5089,11 +5018,12 @@
       <c r="E190" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F190" s="6">
+      <c r="F190" s="3"/>
+      <c r="G190" s="6">
         <v>46042</v>
       </c>
     </row>
-    <row r="191" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A191" s="3" t="s">
         <v>136</v>
       </c>
@@ -5109,11 +5039,12 @@
       <c r="E191" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F191" s="6">
+      <c r="F191" s="3"/>
+      <c r="G191" s="6">
         <v>46042</v>
       </c>
     </row>
-    <row r="192" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A192" s="1" t="s">
         <v>103</v>
       </c>
@@ -5129,11 +5060,11 @@
       <c r="E192" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="F192" s="7">
+      <c r="G192" s="7">
         <v>46043</v>
       </c>
     </row>
-    <row r="193" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A193" s="1" t="s">
         <v>103</v>
       </c>
@@ -5149,11 +5080,11 @@
       <c r="E193" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="F193" s="7">
+      <c r="G193" s="7">
         <v>46043</v>
       </c>
     </row>
-    <row r="194" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A194" s="3" t="s">
         <v>147</v>
       </c>
@@ -5169,11 +5100,12 @@
       <c r="E194" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F194" s="6">
+      <c r="F194" s="3"/>
+      <c r="G194" s="6">
         <v>46043</v>
       </c>
     </row>
-    <row r="195" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A195" s="3" t="s">
         <v>147</v>
       </c>
@@ -5189,11 +5121,12 @@
       <c r="E195" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F195" s="6">
+      <c r="F195" s="3"/>
+      <c r="G195" s="6">
         <v>46043</v>
       </c>
     </row>
-    <row r="196" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A196" s="3" t="s">
         <v>147</v>
       </c>
@@ -5209,11 +5142,12 @@
       <c r="E196" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F196" s="6">
+      <c r="F196" s="3"/>
+      <c r="G196" s="6">
         <v>46043</v>
       </c>
     </row>
-    <row r="197" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A197" s="1" t="s">
         <v>129</v>
       </c>
@@ -5229,11 +5163,11 @@
       <c r="E197" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="F197" s="7">
+      <c r="G197" s="7">
         <v>46043</v>
       </c>
     </row>
-    <row r="198" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A198" s="1" t="s">
         <v>129</v>
       </c>
@@ -5249,11 +5183,11 @@
       <c r="E198" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="F198" s="7">
+      <c r="G198" s="7">
         <v>46043</v>
       </c>
     </row>
-    <row r="199" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A199" s="1" t="s">
         <v>129</v>
       </c>
@@ -5269,11 +5203,11 @@
       <c r="E199" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="F199" s="7">
+      <c r="G199" s="7">
         <v>46043</v>
       </c>
     </row>
-    <row r="200" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A200" s="3" t="s">
         <v>103</v>
       </c>
@@ -5289,11 +5223,12 @@
       <c r="E200" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F200" s="6">
+      <c r="F200" s="3"/>
+      <c r="G200" s="6">
         <v>46043</v>
       </c>
     </row>
-    <row r="201" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A201" s="3" t="s">
         <v>103</v>
       </c>
@@ -5309,11 +5244,12 @@
       <c r="E201" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F201" s="6">
+      <c r="F201" s="3"/>
+      <c r="G201" s="6">
         <v>46043</v>
       </c>
     </row>
-    <row r="202" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A202" s="3" t="s">
         <v>103</v>
       </c>
@@ -5329,11 +5265,12 @@
       <c r="E202" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F202" s="6">
+      <c r="F202" s="3"/>
+      <c r="G202" s="6">
         <v>46043</v>
       </c>
     </row>
-    <row r="203" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A203" s="1" t="s">
         <v>112</v>
       </c>
@@ -5349,11 +5286,11 @@
       <c r="E203" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="F203" s="7">
+      <c r="G203" s="7">
         <v>46044</v>
       </c>
     </row>
-    <row r="204" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A204" s="1" t="s">
         <v>112</v>
       </c>
@@ -5369,11 +5306,11 @@
       <c r="E204" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="F204" s="7">
+      <c r="G204" s="7">
         <v>46044</v>
       </c>
     </row>
-    <row r="205" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A205" s="1" t="s">
         <v>112</v>
       </c>
@@ -5389,11 +5326,11 @@
       <c r="E205" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="F205" s="7">
+      <c r="G205" s="7">
         <v>46044</v>
       </c>
     </row>
-    <row r="206" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A206" s="3" t="s">
         <v>105</v>
       </c>
@@ -5409,11 +5346,12 @@
       <c r="E206" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F206" s="6">
+      <c r="F206" s="3"/>
+      <c r="G206" s="6">
         <v>46044</v>
       </c>
     </row>
-    <row r="207" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A207" s="3" t="s">
         <v>105</v>
       </c>
@@ -5429,11 +5367,12 @@
       <c r="E207" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F207" s="6">
+      <c r="F207" s="3"/>
+      <c r="G207" s="6">
         <v>46044</v>
       </c>
     </row>
-    <row r="208" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A208" s="1" t="s">
         <v>97</v>
       </c>
@@ -5449,11 +5388,11 @@
       <c r="E208" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="F208" s="7">
+      <c r="G208" s="7">
         <v>46044</v>
       </c>
     </row>
-    <row r="209" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A209" s="1" t="s">
         <v>97</v>
       </c>
@@ -5469,11 +5408,11 @@
       <c r="E209" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="F209" s="7">
+      <c r="G209" s="7">
         <v>46044</v>
       </c>
     </row>
-    <row r="210" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A210" s="1" t="s">
         <v>97</v>
       </c>
@@ -5489,11 +5428,11 @@
       <c r="E210" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="F210" s="7">
+      <c r="G210" s="7">
         <v>46044</v>
       </c>
     </row>
-    <row r="211" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A211" s="3" t="s">
         <v>143</v>
       </c>
@@ -5509,11 +5448,12 @@
       <c r="E211" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F211" s="6">
+      <c r="F211" s="3"/>
+      <c r="G211" s="6">
         <v>46044</v>
       </c>
     </row>
-    <row r="212" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A212" s="3" t="s">
         <v>143</v>
       </c>
@@ -5529,11 +5469,12 @@
       <c r="E212" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F212" s="6">
+      <c r="F212" s="3"/>
+      <c r="G212" s="6">
         <v>46044</v>
       </c>
     </row>
-    <row r="213" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A213" s="1" t="s">
         <v>100</v>
       </c>
@@ -5549,11 +5490,11 @@
       <c r="E213" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="F213" s="7">
+      <c r="G213" s="7">
         <v>46044</v>
       </c>
     </row>
-    <row r="214" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A214" s="1" t="s">
         <v>100</v>
       </c>
@@ -5569,11 +5510,11 @@
       <c r="E214" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="F214" s="7">
+      <c r="G214" s="7">
         <v>46044</v>
       </c>
     </row>
-    <row r="215" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A215" s="3" t="s">
         <v>141</v>
       </c>
@@ -5589,11 +5530,12 @@
       <c r="E215" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F215" s="6">
+      <c r="F215" s="3"/>
+      <c r="G215" s="6">
         <v>46044</v>
       </c>
     </row>
-    <row r="216" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A216" s="3" t="s">
         <v>141</v>
       </c>
@@ -5609,11 +5551,12 @@
       <c r="E216" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F216" s="6">
+      <c r="F216" s="3"/>
+      <c r="G216" s="6">
         <v>46044</v>
       </c>
     </row>
-    <row r="217" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A217" s="1" t="s">
         <v>112</v>
       </c>
@@ -5629,11 +5572,11 @@
       <c r="E217" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="F217" s="7">
+      <c r="G217" s="7">
         <v>46045</v>
       </c>
     </row>
-    <row r="218" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A218" s="1" t="s">
         <v>112</v>
       </c>
@@ -5649,11 +5592,11 @@
       <c r="E218" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="F218" s="7">
+      <c r="G218" s="7">
         <v>46045</v>
       </c>
     </row>
-    <row r="219" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A219" s="1" t="s">
         <v>112</v>
       </c>
@@ -5669,11 +5612,11 @@
       <c r="E219" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="F219" s="7">
+      <c r="G219" s="7">
         <v>46045</v>
       </c>
     </row>
-    <row r="220" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A220" s="3" t="s">
         <v>97</v>
       </c>
@@ -5689,11 +5632,12 @@
       <c r="E220" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F220" s="6">
+      <c r="F220" s="3"/>
+      <c r="G220" s="6">
         <v>46045</v>
       </c>
     </row>
-    <row r="221" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A221" s="3" t="s">
         <v>97</v>
       </c>
@@ -5709,11 +5653,12 @@
       <c r="E221" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F221" s="6">
+      <c r="F221" s="3"/>
+      <c r="G221" s="6">
         <v>46045</v>
       </c>
     </row>
-    <row r="222" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A222" s="1" t="s">
         <v>97</v>
       </c>
@@ -5729,11 +5674,11 @@
       <c r="E222" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="F222" s="7">
+      <c r="G222" s="7">
         <v>46045</v>
       </c>
     </row>
-    <row r="223" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A223" s="1" t="s">
         <v>97</v>
       </c>
@@ -5749,11 +5694,11 @@
       <c r="E223" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="F223" s="7">
+      <c r="G223" s="7">
         <v>46045</v>
       </c>
     </row>
-    <row r="224" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A224" s="1" t="s">
         <v>97</v>
       </c>
@@ -5769,11 +5714,11 @@
       <c r="E224" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="F224" s="7">
+      <c r="G224" s="7">
         <v>46045</v>
       </c>
     </row>
-    <row r="225" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A225" s="3" t="s">
         <v>112</v>
       </c>
@@ -5789,11 +5734,12 @@
       <c r="E225" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F225" s="6">
+      <c r="F225" s="3"/>
+      <c r="G225" s="6">
         <v>46045</v>
       </c>
     </row>
-    <row r="226" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A226" s="3" t="s">
         <v>112</v>
       </c>
@@ -5809,11 +5755,12 @@
       <c r="E226" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F226" s="6">
+      <c r="F226" s="3"/>
+      <c r="G226" s="6">
         <v>46045</v>
       </c>
     </row>
-    <row r="227" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A227" s="1" t="s">
         <v>105</v>
       </c>
@@ -5829,11 +5776,11 @@
       <c r="E227" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="F227" s="7">
+      <c r="G227" s="7">
         <v>46046</v>
       </c>
     </row>
-    <row r="228" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A228" s="1" t="s">
         <v>105</v>
       </c>
@@ -5849,11 +5796,11 @@
       <c r="E228" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="F228" s="7">
+      <c r="G228" s="7">
         <v>46046</v>
       </c>
     </row>
-    <row r="229" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A229" s="3" t="s">
         <v>100</v>
       </c>
@@ -5869,11 +5816,12 @@
       <c r="E229" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F229" s="6">
+      <c r="F229" s="3"/>
+      <c r="G229" s="6">
         <v>46046</v>
       </c>
     </row>
-    <row r="230" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A230" s="3" t="s">
         <v>100</v>
       </c>
@@ -5889,11 +5837,12 @@
       <c r="E230" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F230" s="6">
+      <c r="F230" s="3"/>
+      <c r="G230" s="6">
         <v>46046</v>
       </c>
     </row>
-    <row r="231" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A231" s="1" t="s">
         <v>139</v>
       </c>
@@ -5909,11 +5858,11 @@
       <c r="E231" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="F231" s="7">
+      <c r="G231" s="7">
         <v>46046</v>
       </c>
     </row>
-    <row r="232" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A232" s="1" t="s">
         <v>139</v>
       </c>
@@ -5929,11 +5878,11 @@
       <c r="E232" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="F232" s="7">
+      <c r="G232" s="7">
         <v>46046</v>
       </c>
     </row>
-    <row r="233" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A233" s="3" t="s">
         <v>124</v>
       </c>
@@ -5949,11 +5898,12 @@
       <c r="E233" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F233" s="6">
+      <c r="F233" s="3"/>
+      <c r="G233" s="6">
         <v>46046</v>
       </c>
     </row>
-    <row r="234" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A234" s="3" t="s">
         <v>124</v>
       </c>
@@ -5969,11 +5919,12 @@
       <c r="E234" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F234" s="6">
+      <c r="F234" s="3"/>
+      <c r="G234" s="6">
         <v>46046</v>
       </c>
     </row>
-    <row r="235" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A235" s="3" t="s">
         <v>124</v>
       </c>
@@ -5989,11 +5940,12 @@
       <c r="E235" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F235" s="6">
+      <c r="F235" s="3"/>
+      <c r="G235" s="6">
         <v>46046</v>
       </c>
     </row>
-    <row r="236" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A236" s="1" t="s">
         <v>138</v>
       </c>
@@ -6009,11 +5961,11 @@
       <c r="E236" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="F236" s="7">
+      <c r="G236" s="7">
         <v>46046</v>
       </c>
     </row>
-    <row r="237" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A237" s="1" t="s">
         <v>138</v>
       </c>
@@ -6029,11 +5981,11 @@
       <c r="E237" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="F237" s="7">
+      <c r="G237" s="7">
         <v>46046</v>
       </c>
     </row>
-    <row r="238" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A238" s="3" t="s">
         <v>119</v>
       </c>
@@ -6049,11 +6001,12 @@
       <c r="E238" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F238" s="6">
+      <c r="F238" s="3"/>
+      <c r="G238" s="6">
         <v>46046</v>
       </c>
     </row>
-    <row r="239" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A239" s="3" t="s">
         <v>119</v>
       </c>
@@ -6069,11 +6022,12 @@
       <c r="E239" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F239" s="6">
+      <c r="F239" s="3"/>
+      <c r="G239" s="6">
         <v>46046</v>
       </c>
     </row>
-    <row r="240" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A240" s="3" t="s">
         <v>119</v>
       </c>
@@ -6089,11 +6043,12 @@
       <c r="E240" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F240" s="6">
+      <c r="F240" s="3"/>
+      <c r="G240" s="6">
         <v>46046</v>
       </c>
     </row>
-    <row r="241" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A241" s="1" t="s">
         <v>139</v>
       </c>
@@ -6109,11 +6064,11 @@
       <c r="E241" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="F241" s="7">
+      <c r="G241" s="7">
         <v>46047</v>
       </c>
     </row>
-    <row r="242" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A242" s="1" t="s">
         <v>139</v>
       </c>
@@ -6129,11 +6084,11 @@
       <c r="E242" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="F242" s="7">
+      <c r="G242" s="7">
         <v>46047</v>
       </c>
     </row>
-    <row r="243" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A243" s="3" t="s">
         <v>108</v>
       </c>
@@ -6149,11 +6104,12 @@
       <c r="E243" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F243" s="6">
+      <c r="F243" s="3"/>
+      <c r="G243" s="6">
         <v>46047</v>
       </c>
     </row>
-    <row r="244" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A244" s="3" t="s">
         <v>108</v>
       </c>
@@ -6169,11 +6125,12 @@
       <c r="E244" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F244" s="6">
+      <c r="F244" s="3"/>
+      <c r="G244" s="6">
         <v>46047</v>
       </c>
     </row>
-    <row r="245" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A245" s="3" t="s">
         <v>108</v>
       </c>
@@ -6189,11 +6146,12 @@
       <c r="E245" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F245" s="6">
+      <c r="F245" s="3"/>
+      <c r="G245" s="6">
         <v>46047</v>
       </c>
     </row>
-    <row r="246" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A246" s="1" t="s">
         <v>118</v>
       </c>
@@ -6209,11 +6167,11 @@
       <c r="E246" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="F246" s="7">
+      <c r="G246" s="7">
         <v>46047</v>
       </c>
     </row>
-    <row r="247" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A247" s="1" t="s">
         <v>118</v>
       </c>
@@ -6229,11 +6187,11 @@
       <c r="E247" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="F247" s="7">
+      <c r="G247" s="7">
         <v>46047</v>
       </c>
     </row>
-    <row r="248" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A248" s="1" t="s">
         <v>118</v>
       </c>
@@ -6249,11 +6207,11 @@
       <c r="E248" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="F248" s="7">
+      <c r="G248" s="7">
         <v>46047</v>
       </c>
     </row>
-    <row r="249" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A249" s="3" t="s">
         <v>138</v>
       </c>
@@ -6269,11 +6227,12 @@
       <c r="E249" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F249" s="6">
+      <c r="F249" s="3"/>
+      <c r="G249" s="6">
         <v>46047</v>
       </c>
     </row>
-    <row r="250" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A250" s="3" t="s">
         <v>138</v>
       </c>
@@ -6289,11 +6248,12 @@
       <c r="E250" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F250" s="6">
+      <c r="F250" s="3"/>
+      <c r="G250" s="6">
         <v>46047</v>
       </c>
     </row>
-    <row r="251" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A251" s="3" t="s">
         <v>138</v>
       </c>
@@ -6309,11 +6269,12 @@
       <c r="E251" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F251" s="6">
+      <c r="F251" s="3"/>
+      <c r="G251" s="6">
         <v>46047</v>
       </c>
     </row>
-    <row r="252" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A252" s="1" t="s">
         <v>139</v>
       </c>
@@ -6329,11 +6290,11 @@
       <c r="E252" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="F252" s="7">
+      <c r="G252" s="7">
         <v>46047</v>
       </c>
     </row>
-    <row r="253" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A253" s="1" t="s">
         <v>139</v>
       </c>
@@ -6349,11 +6310,11 @@
       <c r="E253" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="F253" s="7">
+      <c r="G253" s="7">
         <v>46047</v>
       </c>
     </row>
-    <row r="254" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A254" s="1" t="s">
         <v>139</v>
       </c>
@@ -6369,11 +6330,11 @@
       <c r="E254" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="F254" s="7">
+      <c r="G254" s="7">
         <v>46047</v>
       </c>
     </row>
-    <row r="255" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A255" s="3" t="s">
         <v>109</v>
       </c>
@@ -6389,11 +6350,12 @@
       <c r="E255" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F255" s="6">
+      <c r="F255" s="3"/>
+      <c r="G255" s="6">
         <v>46047</v>
       </c>
     </row>
-    <row r="256" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A256" s="3" t="s">
         <v>109</v>
       </c>
@@ -6409,11 +6371,12 @@
       <c r="E256" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F256" s="6">
+      <c r="F256" s="3"/>
+      <c r="G256" s="6">
         <v>46047</v>
       </c>
     </row>
-    <row r="257" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A257" s="3" t="s">
         <v>109</v>
       </c>
@@ -6429,11 +6392,12 @@
       <c r="E257" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F257" s="6">
+      <c r="F257" s="3"/>
+      <c r="G257" s="6">
         <v>46047</v>
       </c>
     </row>
-    <row r="258" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A258" s="1" t="s">
         <v>118</v>
       </c>
@@ -6449,11 +6413,11 @@
       <c r="E258" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="F258" s="7">
+      <c r="G258" s="7">
         <v>46048</v>
       </c>
     </row>
-    <row r="259" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A259" s="1" t="s">
         <v>118</v>
       </c>
@@ -6469,11 +6433,11 @@
       <c r="E259" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="F259" s="7">
+      <c r="G259" s="7">
         <v>46048</v>
       </c>
     </row>
-    <row r="260" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A260" s="3" t="s">
         <v>138</v>
       </c>
@@ -6489,11 +6453,12 @@
       <c r="E260" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F260" s="6">
+      <c r="F260" s="3"/>
+      <c r="G260" s="6">
         <v>46048</v>
       </c>
     </row>
-    <row r="261" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A261" s="3" t="s">
         <v>138</v>
       </c>
@@ -6509,11 +6474,12 @@
       <c r="E261" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F261" s="6">
+      <c r="F261" s="3"/>
+      <c r="G261" s="6">
         <v>46048</v>
       </c>
     </row>
-    <row r="262" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A262" s="1" t="s">
         <v>145</v>
       </c>
@@ -6529,11 +6495,11 @@
       <c r="E262" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="F262" s="7">
+      <c r="G262" s="7">
         <v>46049</v>
       </c>
     </row>
-    <row r="263" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A263" s="1" t="s">
         <v>145</v>
       </c>
@@ -6549,11 +6515,11 @@
       <c r="E263" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="F263" s="7">
+      <c r="G263" s="7">
         <v>46049</v>
       </c>
     </row>
-    <row r="264" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A264" s="3" t="s">
         <v>83</v>
       </c>
@@ -6569,11 +6535,12 @@
       <c r="E264" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F264" s="6">
+      <c r="F264" s="3"/>
+      <c r="G264" s="6">
         <v>46049</v>
       </c>
     </row>
-    <row r="265" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A265" s="3" t="s">
         <v>83</v>
       </c>
@@ -6589,11 +6556,12 @@
       <c r="E265" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F265" s="6">
+      <c r="F265" s="3"/>
+      <c r="G265" s="6">
         <v>46049</v>
       </c>
     </row>
-    <row r="266" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A266" s="1" t="s">
         <v>92</v>
       </c>
@@ -6609,11 +6577,11 @@
       <c r="E266" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="F266" s="7">
+      <c r="G266" s="7">
         <v>46049</v>
       </c>
     </row>
-    <row r="267" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A267" s="1" t="s">
         <v>92</v>
       </c>
@@ -6629,11 +6597,11 @@
       <c r="E267" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="F267" s="7">
+      <c r="G267" s="7">
         <v>46049</v>
       </c>
     </row>
-    <row r="268" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A268" s="1" t="s">
         <v>92</v>
       </c>
@@ -6649,11 +6617,11 @@
       <c r="E268" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="F268" s="7">
+      <c r="G268" s="7">
         <v>46049</v>
       </c>
     </row>
-    <row r="269" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A269" s="3" t="s">
         <v>66</v>
       </c>
@@ -6669,11 +6637,12 @@
       <c r="E269" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F269" s="6">
+      <c r="F269" s="3"/>
+      <c r="G269" s="6">
         <v>46049</v>
       </c>
     </row>
-    <row r="270" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A270" s="3" t="s">
         <v>66</v>
       </c>
@@ -6689,11 +6658,12 @@
       <c r="E270" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F270" s="6">
+      <c r="F270" s="3"/>
+      <c r="G270" s="6">
         <v>46049</v>
       </c>
     </row>
-    <row r="271" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A271" s="1" t="s">
         <v>94</v>
       </c>
@@ -6709,11 +6679,11 @@
       <c r="E271" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="F271" s="7">
+      <c r="G271" s="7">
         <v>46050</v>
       </c>
     </row>
-    <row r="272" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A272" s="1" t="s">
         <v>94</v>
       </c>
@@ -6729,11 +6699,11 @@
       <c r="E272" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="F272" s="7">
+      <c r="G272" s="7">
         <v>46050</v>
       </c>
     </row>
-    <row r="273" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A273" s="1" t="s">
         <v>94</v>
       </c>
@@ -6749,11 +6719,11 @@
       <c r="E273" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="F273" s="7">
+      <c r="G273" s="7">
         <v>46050</v>
       </c>
     </row>
-    <row r="274" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A274" s="3" t="s">
         <v>92</v>
       </c>
@@ -6769,11 +6739,12 @@
       <c r="E274" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F274" s="6">
+      <c r="F274" s="3"/>
+      <c r="G274" s="6">
         <v>46050</v>
       </c>
     </row>
-    <row r="275" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A275" s="3" t="s">
         <v>92</v>
       </c>
@@ -6789,11 +6760,12 @@
       <c r="E275" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F275" s="6">
+      <c r="F275" s="3"/>
+      <c r="G275" s="6">
         <v>46050</v>
       </c>
     </row>
-    <row r="276" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A276" s="3" t="s">
         <v>92</v>
       </c>
@@ -6809,11 +6781,12 @@
       <c r="E276" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F276" s="6">
+      <c r="F276" s="3"/>
+      <c r="G276" s="6">
         <v>46050</v>
       </c>
     </row>
-    <row r="277" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A277" s="1" t="s">
         <v>94</v>
       </c>
@@ -6829,11 +6802,11 @@
       <c r="E277" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="F277" s="7">
+      <c r="G277" s="7">
         <v>46050</v>
       </c>
     </row>
-    <row r="278" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A278" s="1" t="s">
         <v>94</v>
       </c>
@@ -6849,11 +6822,11 @@
       <c r="E278" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="F278" s="7">
+      <c r="G278" s="7">
         <v>46050</v>
       </c>
     </row>
-    <row r="279" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="279" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A279" s="3" t="s">
         <v>65</v>
       </c>
@@ -6869,11 +6842,12 @@
       <c r="E279" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F279" s="6">
+      <c r="F279" s="3"/>
+      <c r="G279" s="6">
         <v>46051</v>
       </c>
     </row>
-    <row r="280" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="280" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A280" s="3" t="s">
         <v>65</v>
       </c>
@@ -6889,11 +6863,12 @@
       <c r="E280" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F280" s="6">
+      <c r="F280" s="3"/>
+      <c r="G280" s="6">
         <v>46051</v>
       </c>
     </row>
-    <row r="281" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="281" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A281" s="1" t="s">
         <v>59</v>
       </c>
@@ -6909,11 +6884,11 @@
       <c r="E281" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="F281" s="7">
+      <c r="G281" s="7">
         <v>46051</v>
       </c>
     </row>
-    <row r="282" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="282" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A282" s="1" t="s">
         <v>59</v>
       </c>
@@ -6929,11 +6904,11 @@
       <c r="E282" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="F282" s="7">
+      <c r="G282" s="7">
         <v>46051</v>
       </c>
     </row>
-    <row r="283" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A283" s="3" t="s">
         <v>103</v>
       </c>
@@ -6949,11 +6924,12 @@
       <c r="E283" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F283" s="6">
+      <c r="F283" s="3"/>
+      <c r="G283" s="6">
         <v>46051</v>
       </c>
     </row>
-    <row r="284" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="284" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A284" s="3" t="s">
         <v>103</v>
       </c>
@@ -6969,11 +6945,12 @@
       <c r="E284" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F284" s="6">
+      <c r="F284" s="3"/>
+      <c r="G284" s="6">
         <v>46051</v>
       </c>
     </row>
-    <row r="285" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="285" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A285" s="3" t="s">
         <v>103</v>
       </c>
@@ -6989,11 +6966,12 @@
       <c r="E285" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F285" s="6">
+      <c r="F285" s="3"/>
+      <c r="G285" s="6">
         <v>46051</v>
       </c>
     </row>
-    <row r="286" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="286" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A286" s="1" t="s">
         <v>138</v>
       </c>
@@ -7009,11 +6987,11 @@
       <c r="E286" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="F286" s="7">
+      <c r="G286" s="7">
         <v>46051</v>
       </c>
     </row>
-    <row r="287" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="287" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A287" s="1" t="s">
         <v>138</v>
       </c>
@@ -7029,11 +7007,11 @@
       <c r="E287" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="F287" s="7">
+      <c r="G287" s="7">
         <v>46051</v>
       </c>
     </row>
-    <row r="288" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="288" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A288" s="1" t="s">
         <v>138</v>
       </c>
@@ -7049,11 +7027,11 @@
       <c r="E288" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="F288" s="7">
+      <c r="G288" s="7">
         <v>46051</v>
       </c>
     </row>
-    <row r="289" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="289" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A289" s="3" t="s">
         <v>65</v>
       </c>
@@ -7069,11 +7047,12 @@
       <c r="E289" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F289" s="6">
+      <c r="F289" s="3"/>
+      <c r="G289" s="6">
         <v>46052</v>
       </c>
     </row>
-    <row r="290" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="290" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A290" s="3" t="s">
         <v>65</v>
       </c>
@@ -7089,11 +7068,12 @@
       <c r="E290" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F290" s="6">
+      <c r="F290" s="3"/>
+      <c r="G290" s="6">
         <v>46052</v>
       </c>
     </row>
-    <row r="291" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="291" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A291" s="1" t="s">
         <v>103</v>
       </c>
@@ -7109,11 +7089,11 @@
       <c r="E291" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="F291" s="7">
+      <c r="G291" s="7">
         <v>46052</v>
       </c>
     </row>
-    <row r="292" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="292" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A292" s="1" t="s">
         <v>103</v>
       </c>
@@ -7129,11 +7109,11 @@
       <c r="E292" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="F292" s="7">
+      <c r="G292" s="7">
         <v>46052</v>
       </c>
     </row>
-    <row r="293" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="293" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A293" s="1" t="s">
         <v>103</v>
       </c>
@@ -7149,11 +7129,11 @@
       <c r="E293" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="F293" s="7">
+      <c r="G293" s="7">
         <v>46052</v>
       </c>
     </row>
-    <row r="294" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="294" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A294" s="3" t="s">
         <v>31</v>
       </c>
@@ -7169,11 +7149,12 @@
       <c r="E294" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F294" s="6">
+      <c r="F294" s="3"/>
+      <c r="G294" s="6">
         <v>46053</v>
       </c>
     </row>
-    <row r="295" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="295" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A295" s="1" t="s">
         <v>96</v>
       </c>
@@ -7189,11 +7170,11 @@
       <c r="E295" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="F295" s="7">
+      <c r="G295" s="7">
         <v>46053</v>
       </c>
     </row>
-    <row r="296" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="296" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A296" s="3" t="s">
         <v>100</v>
       </c>
@@ -7209,11 +7190,12 @@
       <c r="E296" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F296" s="6">
+      <c r="F296" s="3"/>
+      <c r="G296" s="6">
         <v>46053</v>
       </c>
     </row>
-    <row r="297" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="297" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A297" s="1" t="s">
         <v>20</v>
       </c>
@@ -7229,11 +7211,11 @@
       <c r="E297" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="F297" s="7">
+      <c r="G297" s="7">
         <v>46053</v>
       </c>
     </row>
-    <row r="298" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="298" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A298" s="3" t="s">
         <v>109</v>
       </c>
@@ -7249,11 +7231,12 @@
       <c r="E298" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F298" s="6">
+      <c r="F298" s="3"/>
+      <c r="G298" s="6">
         <v>46053</v>
       </c>
     </row>
-    <row r="299" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="299" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A299" s="1" t="s">
         <v>129</v>
       </c>
@@ -7269,11 +7252,11 @@
       <c r="E299" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="F299" s="7">
+      <c r="G299" s="7">
         <v>46053</v>
       </c>
     </row>
-    <row r="300" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="300" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A300" s="3" t="s">
         <v>93</v>
       </c>
@@ -7289,11 +7272,12 @@
       <c r="E300" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F300" s="6">
+      <c r="F300" s="3"/>
+      <c r="G300" s="6">
         <v>46053</v>
       </c>
     </row>
-    <row r="301" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="301" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A301" s="1" t="s">
         <v>14</v>
       </c>
@@ -7309,11 +7293,11 @@
       <c r="E301" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="F301" s="7">
+      <c r="G301" s="7">
         <v>46053</v>
       </c>
     </row>
-    <row r="302" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="302" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A302" s="3" t="s">
         <v>147</v>
       </c>
@@ -7329,11 +7313,12 @@
       <c r="E302" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F302" s="6">
+      <c r="F302" s="3"/>
+      <c r="G302" s="6">
         <v>46054</v>
       </c>
     </row>
-    <row r="303" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="303" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A303" s="1" t="s">
         <v>96</v>
       </c>
@@ -7349,11 +7334,11 @@
       <c r="E303" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="F303" s="7">
+      <c r="G303" s="7">
         <v>46054</v>
       </c>
     </row>
-    <row r="304" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="304" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A304" s="3" t="s">
         <v>20</v>
       </c>
@@ -7369,11 +7354,12 @@
       <c r="E304" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F304" s="6">
+      <c r="F304" s="3"/>
+      <c r="G304" s="6">
         <v>46054</v>
       </c>
     </row>
-    <row r="305" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="305" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A305" s="1" t="s">
         <v>31</v>
       </c>
@@ -7389,11 +7375,11 @@
       <c r="E305" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="F305" s="7">
+      <c r="G305" s="7">
         <v>46054</v>
       </c>
     </row>
-    <row r="306" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="306" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A306" s="3" t="s">
         <v>78</v>
       </c>
@@ -7409,11 +7395,12 @@
       <c r="E306" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F306" s="6">
+      <c r="F306" s="3"/>
+      <c r="G306" s="6">
         <v>46054</v>
       </c>
     </row>
-    <row r="307" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="307" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A307" s="1" t="s">
         <v>14</v>
       </c>
@@ -7429,11 +7416,11 @@
       <c r="E307" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="F307" s="7">
+      <c r="G307" s="7">
         <v>46054</v>
       </c>
     </row>
-    <row r="308" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="308" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A308" s="3" t="s">
         <v>36</v>
       </c>
@@ -7449,11 +7436,12 @@
       <c r="E308" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F308" s="6">
+      <c r="F308" s="3"/>
+      <c r="G308" s="6">
         <v>46054</v>
       </c>
     </row>
-    <row r="309" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="309" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A309" s="1" t="s">
         <v>109</v>
       </c>
@@ -7469,11 +7457,11 @@
       <c r="E309" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="F309" s="7">
+      <c r="G309" s="7">
         <v>46054</v>
       </c>
     </row>
-    <row r="310" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="310" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A310" s="3" t="s">
         <v>20</v>
       </c>
@@ -7489,11 +7477,12 @@
       <c r="E310" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F310" s="6">
+      <c r="F310" s="3"/>
+      <c r="G310" s="6">
         <v>46055</v>
       </c>
     </row>
-    <row r="311" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="311" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A311" s="3" t="s">
         <v>20</v>
       </c>
@@ -7509,11 +7498,12 @@
       <c r="E311" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F311" s="6">
+      <c r="F311" s="3"/>
+      <c r="G311" s="6">
         <v>46055</v>
       </c>
     </row>
-    <row r="312" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="312" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A312" s="1" t="s">
         <v>100</v>
       </c>
@@ -7529,11 +7519,11 @@
       <c r="E312" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="F312" s="7">
+      <c r="G312" s="7">
         <v>46055</v>
       </c>
     </row>
-    <row r="313" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="313" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A313" s="1" t="s">
         <v>100</v>
       </c>
@@ -7549,11 +7539,11 @@
       <c r="E313" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="F313" s="7">
+      <c r="G313" s="7">
         <v>46055</v>
       </c>
     </row>
-    <row r="314" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="314" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A314" s="1" t="s">
         <v>100</v>
       </c>
@@ -7569,11 +7559,11 @@
       <c r="E314" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="F314" s="7">
+      <c r="G314" s="7">
         <v>46055</v>
       </c>
     </row>
-    <row r="315" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="315" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A315" s="3" t="s">
         <v>93</v>
       </c>
@@ -7589,11 +7579,12 @@
       <c r="E315" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F315" s="6">
+      <c r="F315" s="3"/>
+      <c r="G315" s="6">
         <v>46055</v>
       </c>
     </row>
-    <row r="316" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="316" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A316" s="1" t="s">
         <v>78</v>
       </c>
@@ -7609,11 +7600,11 @@
       <c r="E316" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="F316" s="7">
+      <c r="G316" s="7">
         <v>46055</v>
       </c>
     </row>
-    <row r="317" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="317" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A317" s="3" t="s">
         <v>147</v>
       </c>
@@ -7629,11 +7620,12 @@
       <c r="E317" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F317" s="6">
+      <c r="F317" s="3"/>
+      <c r="G317" s="6">
         <v>46055</v>
       </c>
     </row>
-    <row r="318" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="318" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A318" s="1" t="s">
         <v>96</v>
       </c>
@@ -7649,11 +7641,11 @@
       <c r="E318" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="F318" s="7">
+      <c r="G318" s="7">
         <v>46055</v>
       </c>
     </row>
-    <row r="319" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="319" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A319" s="3" t="s">
         <v>103</v>
       </c>
@@ -7669,11 +7661,12 @@
       <c r="E319" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F319" s="6">
+      <c r="F319" s="3"/>
+      <c r="G319" s="6">
         <v>46056</v>
       </c>
     </row>
-    <row r="320" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="320" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A320" s="3" t="s">
         <v>103</v>
       </c>
@@ -7689,11 +7682,12 @@
       <c r="E320" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F320" s="6">
+      <c r="F320" s="3"/>
+      <c r="G320" s="6">
         <v>46056</v>
       </c>
     </row>
-    <row r="321" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="321" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A321" s="1" t="s">
         <v>80</v>
       </c>
@@ -7709,11 +7703,11 @@
       <c r="E321" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="F321" s="7">
+      <c r="G321" s="7">
         <v>46056</v>
       </c>
     </row>
-    <row r="322" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="322" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A322" s="1" t="s">
         <v>80</v>
       </c>
@@ -7729,11 +7723,11 @@
       <c r="E322" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="F322" s="7">
+      <c r="G322" s="7">
         <v>46056</v>
       </c>
     </row>
-    <row r="323" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="323" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A323" s="1" t="s">
         <v>80</v>
       </c>
@@ -7749,11 +7743,11 @@
       <c r="E323" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="F323" s="7">
+      <c r="G323" s="7">
         <v>46056</v>
       </c>
     </row>
-    <row r="324" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="324" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A324" s="3" t="s">
         <v>147</v>
       </c>
@@ -7769,11 +7763,12 @@
       <c r="E324" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F324" s="6">
+      <c r="F324" s="3"/>
+      <c r="G324" s="6">
         <v>46057</v>
       </c>
     </row>
-    <row r="325" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="325" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A325" s="3" t="s">
         <v>147</v>
       </c>
@@ -7789,11 +7784,12 @@
       <c r="E325" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F325" s="6">
+      <c r="F325" s="3"/>
+      <c r="G325" s="6">
         <v>46057</v>
       </c>
     </row>
-    <row r="326" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="326" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A326" s="3" t="s">
         <v>147</v>
       </c>
@@ -7809,11 +7805,12 @@
       <c r="E326" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F326" s="6">
+      <c r="F326" s="3"/>
+      <c r="G326" s="6">
         <v>46057</v>
       </c>
     </row>
-    <row r="327" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="327" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A327" s="1" t="s">
         <v>31</v>
       </c>
@@ -7829,11 +7826,11 @@
       <c r="E327" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="F327" s="7">
+      <c r="G327" s="7">
         <v>46057</v>
       </c>
     </row>
-    <row r="328" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="328" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A328" s="1" t="s">
         <v>31</v>
       </c>
@@ -7849,11 +7846,11 @@
       <c r="E328" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="F328" s="7">
+      <c r="G328" s="7">
         <v>46057</v>
       </c>
     </row>
-    <row r="329" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="329" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A329" s="3" t="s">
         <v>36</v>
       </c>
@@ -7869,11 +7866,12 @@
       <c r="E329" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F329" s="6">
+      <c r="F329" s="3"/>
+      <c r="G329" s="6">
         <v>46057</v>
       </c>
     </row>
-    <row r="330" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="330" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A330" s="3" t="s">
         <v>36</v>
       </c>
@@ -7889,11 +7887,12 @@
       <c r="E330" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F330" s="6">
+      <c r="F330" s="3"/>
+      <c r="G330" s="6">
         <v>46057</v>
       </c>
     </row>
-    <row r="331" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="331" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A331" s="1" t="s">
         <v>93</v>
       </c>
@@ -7909,11 +7908,11 @@
       <c r="E331" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="F331" s="7">
+      <c r="G331" s="7">
         <v>46058</v>
       </c>
     </row>
-    <row r="332" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="332" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A332" s="1" t="s">
         <v>93</v>
       </c>
@@ -7929,11 +7928,11 @@
       <c r="E332" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="F332" s="7">
+      <c r="G332" s="7">
         <v>46058</v>
       </c>
     </row>
-    <row r="333" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="333" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A333" s="1" t="s">
         <v>93</v>
       </c>
@@ -7949,11 +7948,11 @@
       <c r="E333" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="F333" s="7">
+      <c r="G333" s="7">
         <v>46058</v>
       </c>
     </row>
-    <row r="334" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="334" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A334" s="3" t="s">
         <v>121</v>
       </c>
@@ -7969,11 +7968,12 @@
       <c r="E334" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F334" s="6">
+      <c r="F334" s="3"/>
+      <c r="G334" s="6">
         <v>46058</v>
       </c>
     </row>
-    <row r="335" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="335" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A335" s="3" t="s">
         <v>121</v>
       </c>
@@ -7989,11 +7989,12 @@
       <c r="E335" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F335" s="6">
+      <c r="F335" s="3"/>
+      <c r="G335" s="6">
         <v>46058</v>
       </c>
     </row>
-    <row r="336" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="336" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A336" s="1" t="s">
         <v>129</v>
       </c>
@@ -8009,11 +8010,11 @@
       <c r="E336" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="F336" s="7">
+      <c r="G336" s="7">
         <v>46058</v>
       </c>
     </row>
-    <row r="337" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="337" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A337" s="1" t="s">
         <v>129</v>
       </c>
@@ -8029,11 +8030,11 @@
       <c r="E337" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="F337" s="7">
+      <c r="G337" s="7">
         <v>46058</v>
       </c>
     </row>
-    <row r="338" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="338" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A338" s="1" t="s">
         <v>129</v>
       </c>
@@ -8049,11 +8050,11 @@
       <c r="E338" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="F338" s="7">
+      <c r="G338" s="7">
         <v>46058</v>
       </c>
     </row>
-    <row r="339" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="339" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A339" s="3" t="s">
         <v>31</v>
       </c>
@@ -8069,11 +8070,12 @@
       <c r="E339" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F339" s="6">
+      <c r="F339" s="3"/>
+      <c r="G339" s="6">
         <v>46059</v>
       </c>
     </row>
-    <row r="340" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="340" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A340" s="3" t="s">
         <v>31</v>
       </c>
@@ -8089,11 +8091,12 @@
       <c r="E340" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F340" s="6">
+      <c r="F340" s="3"/>
+      <c r="G340" s="6">
         <v>46059</v>
       </c>
     </row>
-    <row r="341" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="341" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A341" s="3" t="s">
         <v>31</v>
       </c>
@@ -8109,11 +8112,12 @@
       <c r="E341" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F341" s="6">
+      <c r="F341" s="3"/>
+      <c r="G341" s="6">
         <v>46059</v>
       </c>
     </row>
-    <row r="342" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="342" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A342" s="1" t="s">
         <v>78</v>
       </c>
@@ -8129,11 +8133,11 @@
       <c r="E342" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="F342" s="7">
+      <c r="G342" s="7">
         <v>46059</v>
       </c>
     </row>
-    <row r="343" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="343" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A343" s="1" t="s">
         <v>78</v>
       </c>
@@ -8149,11 +8153,11 @@
       <c r="E343" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="F343" s="7">
+      <c r="G343" s="7">
         <v>46059</v>
       </c>
     </row>
-    <row r="344" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="344" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A344" s="3" t="s">
         <v>36</v>
       </c>
@@ -8169,11 +8173,12 @@
       <c r="E344" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F344" s="6">
+      <c r="F344" s="3"/>
+      <c r="G344" s="6">
         <v>46059</v>
       </c>
     </row>
-    <row r="345" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="345" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A345" s="3" t="s">
         <v>36</v>
       </c>
@@ -8189,11 +8194,12 @@
       <c r="E345" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F345" s="6">
+      <c r="F345" s="3"/>
+      <c r="G345" s="6">
         <v>46059</v>
       </c>
     </row>
-    <row r="346" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="346" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A346" s="3" t="s">
         <v>36</v>
       </c>
@@ -8209,11 +8215,12 @@
       <c r="E346" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F346" s="6">
+      <c r="F346" s="3"/>
+      <c r="G346" s="6">
         <v>46059</v>
       </c>
     </row>
-    <row r="347" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="347" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A347" s="1" t="s">
         <v>34</v>
       </c>
@@ -8229,11 +8236,11 @@
       <c r="E347" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="F347" s="7">
+      <c r="G347" s="7">
         <v>46069</v>
       </c>
     </row>
-    <row r="348" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="348" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A348" s="3" t="s">
         <v>105</v>
       </c>
@@ -8249,11 +8256,12 @@
       <c r="E348" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F348" s="6">
+      <c r="F348" s="3"/>
+      <c r="G348" s="6">
         <v>46069</v>
       </c>
     </row>
-    <row r="349" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="349" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A349" s="1" t="s">
         <v>67</v>
       </c>
@@ -8269,11 +8277,11 @@
       <c r="E349" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="F349" s="7">
+      <c r="G349" s="7">
         <v>46069</v>
       </c>
     </row>
-    <row r="350" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="350" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A350" s="3" t="s">
         <v>118</v>
       </c>
@@ -8289,11 +8297,12 @@
       <c r="E350" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F350" s="6">
+      <c r="F350" s="3"/>
+      <c r="G350" s="6">
         <v>46069</v>
       </c>
     </row>
-    <row r="351" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="351" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A351" s="1" t="s">
         <v>69</v>
       </c>
@@ -8309,11 +8318,11 @@
       <c r="E351" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="F351" s="7">
+      <c r="G351" s="7">
         <v>46069</v>
       </c>
     </row>
-    <row r="352" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="352" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A352" s="3" t="s">
         <v>130</v>
       </c>
@@ -8329,11 +8338,12 @@
       <c r="E352" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F352" s="6">
+      <c r="F352" s="3"/>
+      <c r="G352" s="6">
         <v>46069</v>
       </c>
     </row>
-    <row r="353" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="353" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A353" s="1" t="s">
         <v>94</v>
       </c>
@@ -8349,11 +8359,11 @@
       <c r="E353" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="F353" s="7">
+      <c r="G353" s="7">
         <v>46069</v>
       </c>
     </row>
-    <row r="354" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="354" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A354" s="3" t="s">
         <v>25</v>
       </c>
@@ -8369,11 +8379,12 @@
       <c r="E354" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F354" s="6">
+      <c r="F354" s="3"/>
+      <c r="G354" s="6">
         <v>46069</v>
       </c>
     </row>
-    <row r="355" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="355" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A355" s="1" t="s">
         <v>34</v>
       </c>
@@ -8389,11 +8400,11 @@
       <c r="E355" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="F355" s="7">
+      <c r="G355" s="7">
         <v>46070</v>
       </c>
     </row>
-    <row r="356" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="356" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A356" s="3" t="s">
         <v>69</v>
       </c>
@@ -8409,11 +8420,12 @@
       <c r="E356" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F356" s="6">
+      <c r="F356" s="3"/>
+      <c r="G356" s="6">
         <v>46070</v>
       </c>
     </row>
-    <row r="357" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="357" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A357" s="1" t="s">
         <v>105</v>
       </c>
@@ -8429,11 +8441,11 @@
       <c r="E357" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="F357" s="7">
+      <c r="G357" s="7">
         <v>46070</v>
       </c>
     </row>
-    <row r="358" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="358" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A358" s="3" t="s">
         <v>25</v>
       </c>
@@ -8449,11 +8461,12 @@
       <c r="E358" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F358" s="6">
+      <c r="F358" s="3"/>
+      <c r="G358" s="6">
         <v>46070</v>
       </c>
     </row>
-    <row r="359" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="359" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A359" s="1" t="s">
         <v>100</v>
       </c>
@@ -8469,11 +8482,11 @@
       <c r="E359" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="F359" s="7">
+      <c r="G359" s="7">
         <v>46081</v>
       </c>
     </row>
-    <row r="360" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="360" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A360" s="3" t="s">
         <v>65</v>
       </c>
@@ -8489,11 +8502,12 @@
       <c r="E360" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F360" s="6">
+      <c r="F360" s="3"/>
+      <c r="G360" s="6">
         <v>46081</v>
       </c>
     </row>
-    <row r="361" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="361" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A361" s="1" t="s">
         <v>118</v>
       </c>
@@ -8509,11 +8523,11 @@
       <c r="E361" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="F361" s="7">
+      <c r="G361" s="7">
         <v>46081</v>
       </c>
     </row>
-    <row r="362" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="362" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A362" s="3" t="s">
         <v>129</v>
       </c>
@@ -8529,11 +8543,12 @@
       <c r="E362" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F362" s="6">
+      <c r="F362" s="3"/>
+      <c r="G362" s="6">
         <v>46081</v>
       </c>
     </row>
-    <row r="363" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="363" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A363" s="1" t="s">
         <v>147</v>
       </c>
@@ -8549,11 +8564,11 @@
       <c r="E363" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="F363" s="7">
+      <c r="G363" s="7">
         <v>46091</v>
       </c>
     </row>
-    <row r="364" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="364" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A364" s="1" t="s">
         <v>147</v>
       </c>
@@ -8569,11 +8584,11 @@
       <c r="E364" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="F364" s="7">
+      <c r="G364" s="7">
         <v>46091</v>
       </c>
     </row>
-    <row r="365" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="365" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A365" s="3" t="s">
         <v>25</v>
       </c>
@@ -8589,11 +8604,12 @@
       <c r="E365" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F365" s="6">
+      <c r="F365" s="3"/>
+      <c r="G365" s="6">
         <v>46091</v>
       </c>
     </row>
-    <row r="366" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="366" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A366" s="3" t="s">
         <v>25</v>
       </c>
@@ -8609,11 +8625,12 @@
       <c r="E366" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F366" s="6">
+      <c r="F366" s="3"/>
+      <c r="G366" s="6">
         <v>46091</v>
       </c>
     </row>
-    <row r="367" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="367" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A367" s="1" t="s">
         <v>67</v>
       </c>
@@ -8629,11 +8646,11 @@
       <c r="E367" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="F367" s="7">
+      <c r="G367" s="7">
         <v>46101</v>
       </c>
     </row>
-    <row r="368" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="368" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A368" s="3" t="s">
         <v>130</v>
       </c>
@@ -8649,11 +8666,12 @@
       <c r="E368" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F368" s="6">
+      <c r="F368" s="3"/>
+      <c r="G368" s="6">
         <v>46101</v>
       </c>
     </row>
-    <row r="369" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="369" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A369" s="1" t="s">
         <v>94</v>
       </c>
@@ -8669,11 +8687,11 @@
       <c r="E369" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="F369" s="7">
+      <c r="G369" s="7">
         <v>46101</v>
       </c>
     </row>
-    <row r="370" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="370" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A370" s="3" t="s">
         <v>20</v>
       </c>
@@ -8689,11 +8707,12 @@
       <c r="E370" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F370" s="6">
+      <c r="F370" s="3"/>
+      <c r="G370" s="6">
         <v>46101</v>
       </c>
     </row>
-    <row r="371" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="371" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A371" s="1" t="s">
         <v>118</v>
       </c>
@@ -8709,11 +8728,11 @@
       <c r="E371" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="F371" s="7">
+      <c r="G371" s="7">
         <v>46102</v>
       </c>
     </row>
-    <row r="372" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="372" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A372" s="1" t="s">
         <v>118</v>
       </c>
@@ -8729,11 +8748,11 @@
       <c r="E372" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="F372" s="7">
+      <c r="G372" s="7">
         <v>46102</v>
       </c>
     </row>
-    <row r="373" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="373" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A373" s="3" t="s">
         <v>129</v>
       </c>
@@ -8749,11 +8768,12 @@
       <c r="E373" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F373" s="6">
+      <c r="F373" s="3"/>
+      <c r="G373" s="6">
         <v>46102</v>
       </c>
     </row>
-    <row r="374" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="374" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A374" s="3" t="s">
         <v>129</v>
       </c>
@@ -8769,11 +8789,12 @@
       <c r="E374" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F374" s="6">
+      <c r="F374" s="3"/>
+      <c r="G374" s="6">
         <v>46102</v>
       </c>
     </row>
-    <row r="375" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="375" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A375" s="5" t="s">
         <v>129</v>
       </c>
@@ -8789,11 +8810,12 @@
       <c r="E375" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="F375" s="8">
+      <c r="F375" s="5"/>
+      <c r="G375" s="8">
         <v>46102</v>
       </c>
     </row>
-    <row r="376" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="376" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A376" s="4" t="s">
         <v>20</v>
       </c>
@@ -8809,11 +8831,12 @@
       <c r="E376" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="F376" s="9">
+      <c r="F376" s="4"/>
+      <c r="G376" s="9">
         <v>46143</v>
       </c>
     </row>
-    <row r="377" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="377" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A377" s="4" t="s">
         <v>20</v>
       </c>
@@ -8829,11 +8852,12 @@
       <c r="E377" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="F377" s="9">
+      <c r="F377" s="4"/>
+      <c r="G377" s="9">
         <v>46143</v>
       </c>
     </row>
-    <row r="378" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="378" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A378" s="4" t="s">
         <v>20</v>
       </c>
@@ -8849,11 +8873,12 @@
       <c r="E378" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="F378" s="9">
+      <c r="F378" s="4"/>
+      <c r="G378" s="9">
         <v>46143</v>
       </c>
     </row>
-    <row r="379" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="379" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A379" s="5" t="s">
         <v>34</v>
       </c>
@@ -8869,11 +8894,12 @@
       <c r="E379" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="F379" s="8">
+      <c r="F379" s="5"/>
+      <c r="G379" s="8">
         <v>46143</v>
       </c>
     </row>
-    <row r="380" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="380" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A380" s="5" t="s">
         <v>34</v>
       </c>
@@ -8889,11 +8915,12 @@
       <c r="E380" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="F380" s="8">
+      <c r="F380" s="5"/>
+      <c r="G380" s="8">
         <v>46143</v>
       </c>
     </row>
-    <row r="381" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="381" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A381" s="5" t="s">
         <v>34</v>
       </c>
@@ -8909,11 +8936,12 @@
       <c r="E381" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="F381" s="8">
+      <c r="F381" s="5"/>
+      <c r="G381" s="8">
         <v>46143</v>
       </c>
     </row>
-    <row r="382" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="382" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A382" s="4" t="s">
         <v>69</v>
       </c>
@@ -8929,11 +8957,12 @@
       <c r="E382" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="F382" s="9">
+      <c r="F382" s="4"/>
+      <c r="G382" s="9">
         <v>46143</v>
       </c>
     </row>
-    <row r="383" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="383" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A383" s="4" t="s">
         <v>69</v>
       </c>
@@ -8949,11 +8978,12 @@
       <c r="E383" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="F383" s="9">
+      <c r="F383" s="4"/>
+      <c r="G383" s="9">
         <v>46143</v>
       </c>
     </row>
-    <row r="384" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="384" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A384" s="5" t="s">
         <v>78</v>
       </c>
@@ -8969,11 +8999,12 @@
       <c r="E384" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="F384" s="8">
+      <c r="F384" s="5"/>
+      <c r="G384" s="8">
         <v>46143</v>
       </c>
     </row>
-    <row r="385" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="385" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A385" s="5" t="s">
         <v>78</v>
       </c>
@@ -8989,11 +9020,12 @@
       <c r="E385" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="F385" s="8">
+      <c r="F385" s="5"/>
+      <c r="G385" s="8">
         <v>46143</v>
       </c>
     </row>
-    <row r="386" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="386" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A386" s="5" t="s">
         <v>78</v>
       </c>
@@ -9009,11 +9041,12 @@
       <c r="E386" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="F386" s="8">
+      <c r="F386" s="5"/>
+      <c r="G386" s="8">
         <v>46143</v>
       </c>
     </row>
-    <row r="387" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="387" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A387" s="4" t="s">
         <v>105</v>
       </c>
@@ -9029,11 +9062,12 @@
       <c r="E387" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="F387" s="9">
+      <c r="F387" s="4"/>
+      <c r="G387" s="9">
         <v>46143</v>
       </c>
     </row>
-    <row r="388" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="388" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A388" s="4" t="s">
         <v>105</v>
       </c>
@@ -9049,11 +9083,12 @@
       <c r="E388" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="F388" s="9">
+      <c r="F388" s="4"/>
+      <c r="G388" s="9">
         <v>46143</v>
       </c>
     </row>
-    <row r="389" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="389" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A389" s="4" t="s">
         <v>105</v>
       </c>
@@ -9069,11 +9104,12 @@
       <c r="E389" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="F389" s="9">
+      <c r="F389" s="4"/>
+      <c r="G389" s="9">
         <v>46143</v>
       </c>
     </row>
-    <row r="390" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="390" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A390" s="5" t="s">
         <v>130</v>
       </c>
@@ -9089,11 +9125,12 @@
       <c r="E390" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="F390" s="8">
+      <c r="F390" s="5"/>
+      <c r="G390" s="8">
         <v>46143</v>
       </c>
     </row>
-    <row r="391" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="391" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A391" s="5" t="s">
         <v>130</v>
       </c>
@@ -9109,11 +9146,12 @@
       <c r="E391" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="F391" s="8">
+      <c r="F391" s="5"/>
+      <c r="G391" s="8">
         <v>46143</v>
       </c>
     </row>
-    <row r="392" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="392" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A392" s="5" t="s">
         <v>130</v>
       </c>
@@ -9129,11 +9167,12 @@
       <c r="E392" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="F392" s="8">
+      <c r="F392" s="5"/>
+      <c r="G392" s="8">
         <v>46143</v>
       </c>
     </row>
-    <row r="393" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="393" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A393" s="1" t="s">
         <v>36</v>
       </c>
@@ -9149,11 +9188,12 @@
       <c r="E393" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="F393" s="7">
+      <c r="F393" s="4"/>
+      <c r="G393" s="7">
         <v>46172</v>
       </c>
     </row>
-    <row r="394" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="394" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A394" s="1" t="s">
         <v>36</v>
       </c>
@@ -9169,11 +9209,12 @@
       <c r="E394" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="F394" s="7">
+      <c r="F394" s="4"/>
+      <c r="G394" s="7">
         <v>46172</v>
       </c>
     </row>
-    <row r="395" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="395" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A395" s="1" t="s">
         <v>36</v>
       </c>
@@ -9189,11 +9230,12 @@
       <c r="E395" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="F395" s="7">
+      <c r="F395" s="4"/>
+      <c r="G395" s="7">
         <v>46172</v>
       </c>
     </row>
-    <row r="396" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="396" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A396" s="3" t="s">
         <v>96</v>
       </c>
@@ -9209,11 +9251,12 @@
       <c r="E396" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="F396" s="6">
+      <c r="F396" s="5"/>
+      <c r="G396" s="6">
         <v>46172</v>
       </c>
     </row>
-    <row r="397" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="397" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A397" s="3" t="s">
         <v>96</v>
       </c>
@@ -9229,11 +9272,12 @@
       <c r="E397" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="F397" s="6">
+      <c r="F397" s="5"/>
+      <c r="G397" s="6">
         <v>46172</v>
       </c>
     </row>
-    <row r="398" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="398" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A398" s="1" t="s">
         <v>20</v>
       </c>
@@ -9249,11 +9293,12 @@
       <c r="E398" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="F398" s="7">
+      <c r="F398" s="4"/>
+      <c r="G398" s="7">
         <v>46172</v>
       </c>
     </row>
-    <row r="399" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="399" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A399" s="1" t="s">
         <v>20</v>
       </c>
@@ -9269,11 +9314,12 @@
       <c r="E399" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="F399" s="7">
+      <c r="F399" s="4"/>
+      <c r="G399" s="7">
         <v>46172</v>
       </c>
     </row>
-    <row r="400" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="400" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A400" s="5" t="s">
         <v>147</v>
       </c>
@@ -9289,11 +9335,12 @@
       <c r="E400" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="F400" s="8">
+      <c r="F400" s="5"/>
+      <c r="G400" s="8">
         <v>46173</v>
       </c>
     </row>
-    <row r="401" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="401" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A401" s="5" t="s">
         <v>147</v>
       </c>
@@ -9309,11 +9356,12 @@
       <c r="E401" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="F401" s="8">
+      <c r="F401" s="5"/>
+      <c r="G401" s="8">
         <v>46173</v>
       </c>
     </row>
-    <row r="402" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="402" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A402" s="4" t="s">
         <v>65</v>
       </c>
@@ -9329,11 +9377,12 @@
       <c r="E402" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="F402" s="9">
+      <c r="F402" s="4"/>
+      <c r="G402" s="9">
         <v>46173</v>
       </c>
     </row>
-    <row r="403" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="403" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A403" s="4" t="s">
         <v>65</v>
       </c>
@@ -9349,11 +9398,12 @@
       <c r="E403" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="F403" s="9">
+      <c r="F403" s="4"/>
+      <c r="G403" s="9">
         <v>46173</v>
       </c>
     </row>
-    <row r="404" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="404" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A404" s="4" t="s">
         <v>65</v>
       </c>
@@ -9369,11 +9419,12 @@
       <c r="E404" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="F404" s="9">
+      <c r="F404" s="4"/>
+      <c r="G404" s="9">
         <v>46173</v>
       </c>
     </row>
-    <row r="405" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="405" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A405" s="5" t="s">
         <v>130</v>
       </c>
@@ -9389,11 +9440,12 @@
       <c r="E405" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="F405" s="8">
+      <c r="F405" s="5"/>
+      <c r="G405" s="8">
         <v>46173</v>
       </c>
     </row>
-    <row r="406" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="406" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A406" s="5" t="s">
         <v>130</v>
       </c>
@@ -9409,11 +9461,12 @@
       <c r="E406" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="F406" s="8">
+      <c r="F406" s="5"/>
+      <c r="G406" s="8">
         <v>46173</v>
       </c>
     </row>
-    <row r="407" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="407" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A407" s="4" t="s">
         <v>100</v>
       </c>
@@ -9429,11 +9482,12 @@
       <c r="E407" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="F407" s="9">
+      <c r="F407" s="4"/>
+      <c r="G407" s="9">
         <v>46173</v>
       </c>
     </row>
-    <row r="408" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="408" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A408" s="4" t="s">
         <v>100</v>
       </c>
@@ -9449,11 +9503,12 @@
       <c r="E408" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="F408" s="9">
+      <c r="F408" s="4"/>
+      <c r="G408" s="9">
         <v>46173</v>
       </c>
     </row>
-    <row r="409" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="409" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A409" s="4" t="s">
         <v>100</v>
       </c>
@@ -9469,11 +9524,12 @@
       <c r="E409" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="F409" s="9">
+      <c r="F409" s="4"/>
+      <c r="G409" s="9">
         <v>46173</v>
       </c>
     </row>
-    <row r="410" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="410" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A410" s="5" t="s">
         <v>94</v>
       </c>
@@ -9489,11 +9545,12 @@
       <c r="E410" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="F410" s="8">
+      <c r="F410" s="5"/>
+      <c r="G410" s="8">
         <v>46174</v>
       </c>
     </row>
-    <row r="411" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="411" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A411" s="5" t="s">
         <v>94</v>
       </c>
@@ -9509,11 +9566,12 @@
       <c r="E411" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="F411" s="8">
+      <c r="F411" s="5"/>
+      <c r="G411" s="8">
         <v>46174</v>
       </c>
     </row>
-    <row r="412" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="412" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A412" s="5" t="s">
         <v>94</v>
       </c>
@@ -9529,11 +9587,12 @@
       <c r="E412" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="F412" s="8">
+      <c r="F412" s="5"/>
+      <c r="G412" s="8">
         <v>46174</v>
       </c>
     </row>
-    <row r="413" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="413" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A413" s="4" t="s">
         <v>25</v>
       </c>
@@ -9549,11 +9608,12 @@
       <c r="E413" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="F413" s="9">
+      <c r="F413" s="4"/>
+      <c r="G413" s="9">
         <v>46175</v>
       </c>
     </row>
-    <row r="414" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="414" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A414" s="4" t="s">
         <v>25</v>
       </c>
@@ -9569,11 +9629,12 @@
       <c r="E414" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="F414" s="9">
+      <c r="F414" s="4"/>
+      <c r="G414" s="9">
         <v>46175</v>
       </c>
     </row>
-    <row r="415" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="415" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A415" s="4" t="s">
         <v>25</v>
       </c>
@@ -9589,11 +9650,12 @@
       <c r="E415" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="F415" s="9">
+      <c r="F415" s="4"/>
+      <c r="G415" s="9">
         <v>46175</v>
       </c>
     </row>
-    <row r="416" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="416" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A416" s="5" t="s">
         <v>28</v>
       </c>
@@ -9609,11 +9671,12 @@
       <c r="E416" s="5" t="s">
         <v>164</v>
       </c>
-      <c r="F416" s="8">
+      <c r="F416" s="5"/>
+      <c r="G416" s="8">
         <v>46175</v>
       </c>
     </row>
-    <row r="417" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="417" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A417" s="4" t="s">
         <v>165</v>
       </c>
@@ -9629,11 +9692,12 @@
       <c r="E417" s="4" t="s">
         <v>164</v>
       </c>
-      <c r="F417" s="9">
+      <c r="F417" s="4"/>
+      <c r="G417" s="9">
         <v>46175</v>
       </c>
     </row>
-    <row r="418" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="418" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A418" s="5" t="s">
         <v>163</v>
       </c>
@@ -9649,11 +9713,12 @@
       <c r="E418" s="5" t="s">
         <v>164</v>
       </c>
-      <c r="F418" s="8">
+      <c r="F418" s="5"/>
+      <c r="G418" s="8">
         <v>46175</v>
       </c>
     </row>
-    <row r="419" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="419" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A419" s="4" t="s">
         <v>28</v>
       </c>
@@ -9669,11 +9734,12 @@
       <c r="E419" s="4" t="s">
         <v>164</v>
       </c>
-      <c r="F419" s="9">
+      <c r="F419" s="4"/>
+      <c r="G419" s="9">
         <v>46175</v>
       </c>
     </row>
-    <row r="420" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="420" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A420" s="5" t="s">
         <v>28</v>
       </c>
@@ -9689,12 +9755,13 @@
       <c r="E420" s="5" t="s">
         <v>164</v>
       </c>
-      <c r="F420" s="8">
+      <c r="F420" s="5"/>
+      <c r="G420" s="8">
         <v>46175</v>
       </c>
-      <c r="G420" s="10"/>
-    </row>
-    <row r="421" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H420" s="10"/>
+    </row>
+    <row r="421" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A421" s="4" t="s">
         <v>94</v>
       </c>
@@ -9710,12 +9777,13 @@
       <c r="E421" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="F421" s="9">
+      <c r="F421" s="4"/>
+      <c r="G421" s="9">
         <v>46176</v>
       </c>
-      <c r="G421" s="10"/>
-    </row>
-    <row r="422" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H421" s="10"/>
+    </row>
+    <row r="422" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A422" s="4" t="s">
         <v>94</v>
       </c>
@@ -9731,12 +9799,13 @@
       <c r="E422" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="F422" s="9">
+      <c r="F422" s="4"/>
+      <c r="G422" s="9">
         <v>46176</v>
       </c>
-      <c r="G422" s="10"/>
-    </row>
-    <row r="423" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H422" s="10"/>
+    </row>
+    <row r="423" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A423" s="4" t="s">
         <v>94</v>
       </c>
@@ -9752,12 +9821,13 @@
       <c r="E423" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="F423" s="9">
+      <c r="F423" s="4"/>
+      <c r="G423" s="9">
         <v>46176</v>
       </c>
-      <c r="G423" s="10"/>
-    </row>
-    <row r="424" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H423" s="10"/>
+    </row>
+    <row r="424" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A424" s="5" t="s">
         <v>33</v>
       </c>
@@ -9773,11 +9843,12 @@
       <c r="E424" s="5" t="s">
         <v>164</v>
       </c>
-      <c r="F424" s="6">
+      <c r="F424" s="5"/>
+      <c r="G424" s="6">
         <v>46183</v>
       </c>
     </row>
-    <row r="425" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="425" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A425" s="4" t="s">
         <v>116</v>
       </c>
@@ -9793,11 +9864,12 @@
       <c r="E425" s="4" t="s">
         <v>164</v>
       </c>
-      <c r="F425" s="7">
+      <c r="F425" s="4"/>
+      <c r="G425" s="7">
         <v>46183</v>
       </c>
     </row>
-    <row r="426" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="426" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A426" s="5" t="s">
         <v>168</v>
       </c>
@@ -9813,11 +9885,12 @@
       <c r="E426" s="5" t="s">
         <v>164</v>
       </c>
-      <c r="F426" s="6">
+      <c r="F426" s="5"/>
+      <c r="G426" s="6">
         <v>46183</v>
       </c>
     </row>
-    <row r="427" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="427" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A427" s="4" t="s">
         <v>33</v>
       </c>
@@ -9833,11 +9906,12 @@
       <c r="E427" s="4" t="s">
         <v>164</v>
       </c>
-      <c r="F427" s="7">
+      <c r="F427" s="4"/>
+      <c r="G427" s="7">
         <v>46183</v>
       </c>
     </row>
-    <row r="428" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="428" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A428" s="5" t="s">
         <v>168</v>
       </c>
@@ -9853,11 +9927,12 @@
       <c r="E428" s="5" t="s">
         <v>164</v>
       </c>
-      <c r="F428" s="6">
+      <c r="F428" s="5"/>
+      <c r="G428" s="6">
         <v>46183</v>
       </c>
     </row>
-    <row r="429" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="429" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A429" s="4" t="s">
         <v>19</v>
       </c>
@@ -9873,11 +9948,12 @@
       <c r="E429" s="4" t="s">
         <v>164</v>
       </c>
-      <c r="F429" s="7">
+      <c r="F429" s="4"/>
+      <c r="G429" s="7">
         <v>46184</v>
       </c>
     </row>
-    <row r="430" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="430" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A430" s="5" t="s">
         <v>11</v>
       </c>
@@ -9893,11 +9969,12 @@
       <c r="E430" s="5" t="s">
         <v>164</v>
       </c>
-      <c r="F430" s="6">
+      <c r="F430" s="5"/>
+      <c r="G430" s="6">
         <v>46184</v>
       </c>
     </row>
-    <row r="431" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="431" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A431" s="4" t="s">
         <v>19</v>
       </c>
@@ -9913,11 +9990,12 @@
       <c r="E431" s="4" t="s">
         <v>164</v>
       </c>
-      <c r="F431" s="7">
+      <c r="F431" s="4"/>
+      <c r="G431" s="7">
         <v>46184</v>
       </c>
     </row>
-    <row r="432" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="432" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A432" s="5" t="s">
         <v>11</v>
       </c>
@@ -9933,11 +10011,12 @@
       <c r="E432" s="5" t="s">
         <v>164</v>
       </c>
-      <c r="F432" s="6">
+      <c r="F432" s="5"/>
+      <c r="G432" s="6">
         <v>46184</v>
       </c>
     </row>
-    <row r="433" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="433" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A433" s="4" t="s">
         <v>19</v>
       </c>
@@ -9953,11 +10032,12 @@
       <c r="E433" s="4" t="s">
         <v>164</v>
       </c>
-      <c r="F433" s="7">
+      <c r="F433" s="4"/>
+      <c r="G433" s="7">
         <v>46184</v>
       </c>
     </row>
-    <row r="434" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="434" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A434" s="3" t="s">
         <v>69</v>
       </c>
@@ -9973,11 +10053,12 @@
       <c r="E434" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F434" s="6">
+      <c r="F434" s="3"/>
+      <c r="G434" s="6">
         <v>46184</v>
       </c>
     </row>
-    <row r="435" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="435" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A435" s="3" t="s">
         <v>69</v>
       </c>
@@ -9993,11 +10074,12 @@
       <c r="E435" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F435" s="6">
+      <c r="F435" s="3"/>
+      <c r="G435" s="6">
         <v>46184</v>
       </c>
     </row>
-    <row r="436" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="436" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A436" s="3" t="s">
         <v>69</v>
       </c>
@@ -10013,11 +10095,12 @@
       <c r="E436" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F436" s="6">
+      <c r="F436" s="3"/>
+      <c r="G436" s="6">
         <v>46184</v>
       </c>
     </row>
-    <row r="437" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="437" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A437" s="3" t="s">
         <v>69</v>
       </c>
@@ -10033,11 +10116,12 @@
       <c r="E437" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F437" s="6">
+      <c r="F437" s="3"/>
+      <c r="G437" s="6">
         <v>46184</v>
       </c>
     </row>
-    <row r="438" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="438" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A438" s="1" t="s">
         <v>171</v>
       </c>
@@ -10053,11 +10137,11 @@
       <c r="E438" s="1" t="s">
         <v>164</v>
       </c>
-      <c r="F438" s="7">
+      <c r="G438" s="7">
         <v>46214</v>
       </c>
     </row>
-    <row r="439" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="439" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A439" s="3" t="s">
         <v>146</v>
       </c>
@@ -10073,11 +10157,12 @@
       <c r="E439" s="3" t="s">
         <v>164</v>
       </c>
-      <c r="F439" s="6">
+      <c r="F439" s="3"/>
+      <c r="G439" s="6">
         <v>46214</v>
       </c>
     </row>
-    <row r="440" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="440" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A440" s="1" t="s">
         <v>172</v>
       </c>
@@ -10093,11 +10178,11 @@
       <c r="E440" s="1" t="s">
         <v>164</v>
       </c>
-      <c r="F440" s="7">
+      <c r="G440" s="7">
         <v>46214</v>
       </c>
     </row>
-    <row r="441" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="441" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A441" s="3" t="s">
         <v>171</v>
       </c>
@@ -10113,11 +10198,12 @@
       <c r="E441" s="3" t="s">
         <v>164</v>
       </c>
-      <c r="F441" s="6">
+      <c r="F441" s="3"/>
+      <c r="G441" s="6">
         <v>46214</v>
       </c>
     </row>
-    <row r="442" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="442" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A442" s="1" t="s">
         <v>173</v>
       </c>
@@ -10133,11 +10219,11 @@
       <c r="E442" s="1" t="s">
         <v>164</v>
       </c>
-      <c r="F442" s="7">
+      <c r="G442" s="7">
         <v>46214</v>
       </c>
     </row>
-    <row r="443" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="443" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A443" s="5" t="s">
         <v>116</v>
       </c>
@@ -10153,11 +10239,12 @@
       <c r="E443" s="5" t="s">
         <v>164</v>
       </c>
-      <c r="F443" s="8">
+      <c r="F443" s="5"/>
+      <c r="G443" s="8">
         <v>46215</v>
       </c>
     </row>
-    <row r="444" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="444" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A444" s="5" t="s">
         <v>116</v>
       </c>
@@ -10173,11 +10260,12 @@
       <c r="E444" s="5" t="s">
         <v>164</v>
       </c>
-      <c r="F444" s="8">
+      <c r="F444" s="5"/>
+      <c r="G444" s="8">
         <v>46215</v>
       </c>
     </row>
-    <row r="445" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="445" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A445" s="4" t="s">
         <v>171</v>
       </c>
@@ -10193,11 +10281,12 @@
       <c r="E445" s="4" t="s">
         <v>164</v>
       </c>
-      <c r="F445" s="9">
+      <c r="F445" s="4"/>
+      <c r="G445" s="9">
         <v>46215</v>
       </c>
     </row>
-    <row r="446" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="446" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A446" s="4" t="s">
         <v>171</v>
       </c>
@@ -10213,11 +10302,12 @@
       <c r="E446" s="4" t="s">
         <v>164</v>
       </c>
-      <c r="F446" s="9">
+      <c r="F446" s="4"/>
+      <c r="G446" s="9">
         <v>46215</v>
       </c>
     </row>
-    <row r="447" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="447" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A447" s="5" t="s">
         <v>146</v>
       </c>
@@ -10233,11 +10323,12 @@
       <c r="E447" s="5" t="s">
         <v>164</v>
       </c>
-      <c r="F447" s="8">
+      <c r="F447" s="5"/>
+      <c r="G447" s="8">
         <v>46215</v>
       </c>
     </row>
-    <row r="448" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="448" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A448" s="5" t="s">
         <v>146</v>
       </c>
@@ -10253,11 +10344,12 @@
       <c r="E448" s="5" t="s">
         <v>164</v>
       </c>
-      <c r="F448" s="8">
+      <c r="F448" s="5"/>
+      <c r="G448" s="8">
         <v>46215</v>
       </c>
     </row>
-    <row r="449" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="449" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A449" s="5" t="s">
         <v>146</v>
       </c>
@@ -10273,11 +10365,12 @@
       <c r="E449" s="5" t="s">
         <v>164</v>
       </c>
-      <c r="F449" s="8">
+      <c r="F449" s="5"/>
+      <c r="G449" s="8">
         <v>46215</v>
       </c>
     </row>
-    <row r="450" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="450" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A450" s="4" t="s">
         <v>28</v>
       </c>
@@ -10293,11 +10386,12 @@
       <c r="E450" s="4" t="s">
         <v>164</v>
       </c>
-      <c r="F450" s="9">
+      <c r="F450" s="4"/>
+      <c r="G450" s="9">
         <v>46215</v>
       </c>
     </row>
-    <row r="451" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="451" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A451" s="4" t="s">
         <v>28</v>
       </c>
@@ -10313,11 +10407,12 @@
       <c r="E451" s="4" t="s">
         <v>164</v>
       </c>
-      <c r="F451" s="9">
+      <c r="F451" s="4"/>
+      <c r="G451" s="9">
         <v>46215</v>
       </c>
     </row>
-    <row r="452" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="452" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A452" s="4" t="s">
         <v>28</v>
       </c>
@@ -10333,11 +10428,12 @@
       <c r="E452" s="4" t="s">
         <v>164</v>
       </c>
-      <c r="F452" s="9">
+      <c r="F452" s="4"/>
+      <c r="G452" s="9">
         <v>46215</v>
       </c>
     </row>
-    <row r="453" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="453" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A453" s="5" t="s">
         <v>116</v>
       </c>
@@ -10353,12 +10449,13 @@
       <c r="E453" s="5" t="s">
         <v>164</v>
       </c>
-      <c r="F453" s="8">
+      <c r="F453" s="5"/>
+      <c r="G453" s="8">
         <v>46216</v>
       </c>
-      <c r="G453" s="10"/>
-    </row>
-    <row r="454" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="H453" s="10"/>
+    </row>
+    <row r="454" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A454" s="5" t="s">
         <v>116</v>
       </c>
@@ -10374,12 +10471,13 @@
       <c r="E454" s="5" t="s">
         <v>164</v>
       </c>
-      <c r="F454" s="8">
+      <c r="F454" s="5"/>
+      <c r="G454" s="8">
         <v>46216</v>
       </c>
-      <c r="G454" s="10"/>
-    </row>
-    <row r="455" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="H454" s="10"/>
+    </row>
+    <row r="455" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A455" s="4" t="s">
         <v>146</v>
       </c>
@@ -10395,11 +10493,12 @@
       <c r="E455" s="4" t="s">
         <v>164</v>
       </c>
-      <c r="F455" s="9">
+      <c r="F455" s="4"/>
+      <c r="G455" s="9">
         <v>46216</v>
       </c>
     </row>
-    <row r="456" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="456" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A456" s="4" t="s">
         <v>146</v>
       </c>
@@ -10415,11 +10514,12 @@
       <c r="E456" s="4" t="s">
         <v>164</v>
       </c>
-      <c r="F456" s="9">
+      <c r="F456" s="4"/>
+      <c r="G456" s="9">
         <v>46216</v>
       </c>
     </row>
-    <row r="457" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="457" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A457" s="5" t="s">
         <v>116</v>
       </c>
@@ -10435,11 +10535,12 @@
       <c r="E457" s="5" t="s">
         <v>164</v>
       </c>
-      <c r="F457" s="8">
+      <c r="F457" s="5"/>
+      <c r="G457" s="8">
         <v>46218</v>
       </c>
     </row>
-    <row r="458" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="458" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A458" s="5" t="s">
         <v>116</v>
       </c>
@@ -10455,11 +10556,12 @@
       <c r="E458" s="5" t="s">
         <v>164</v>
       </c>
-      <c r="F458" s="8">
+      <c r="F458" s="5"/>
+      <c r="G458" s="8">
         <v>46218</v>
       </c>
     </row>
-    <row r="459" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="459" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A459" s="5" t="s">
         <v>116</v>
       </c>
@@ -10475,11 +10577,12 @@
       <c r="E459" s="5" t="s">
         <v>164</v>
       </c>
-      <c r="F459" s="8">
+      <c r="F459" s="5"/>
+      <c r="G459" s="8">
         <v>46218</v>
       </c>
     </row>
-    <row r="460" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="460" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A460" s="4" t="s">
         <v>166</v>
       </c>
@@ -10495,11 +10598,12 @@
       <c r="E460" s="4" t="s">
         <v>164</v>
       </c>
-      <c r="F460" s="9">
+      <c r="F460" s="4"/>
+      <c r="G460" s="9">
         <v>46218</v>
       </c>
     </row>
-    <row r="461" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="461" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A461" s="4" t="s">
         <v>166</v>
       </c>
@@ -10515,11 +10619,12 @@
       <c r="E461" s="4" t="s">
         <v>164</v>
       </c>
-      <c r="F461" s="9">
+      <c r="F461" s="4"/>
+      <c r="G461" s="9">
         <v>46218</v>
       </c>
     </row>
-    <row r="462" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="462" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A462" s="4" t="s">
         <v>166</v>
       </c>
@@ -10535,13 +10640,14 @@
       <c r="E462" s="4" t="s">
         <v>164</v>
       </c>
-      <c r="F462" s="9">
+      <c r="F462" s="4"/>
+      <c r="G462" s="9">
         <v>46218</v>
       </c>
-      <c r="G462" s="10"/>
       <c r="H462" s="10"/>
-    </row>
-    <row r="463" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I462" s="10"/>
+    </row>
+    <row r="463" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A463" s="5" t="s">
         <v>174</v>
       </c>
@@ -10557,13 +10663,14 @@
       <c r="E463" s="5" t="s">
         <v>176</v>
       </c>
-      <c r="F463" s="8">
+      <c r="F463" s="5"/>
+      <c r="G463" s="8">
         <v>46219</v>
       </c>
-      <c r="G463" s="10"/>
       <c r="H463" s="10"/>
-    </row>
-    <row r="464" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I463" s="10"/>
+    </row>
+    <row r="464" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A464" s="5" t="s">
         <v>174</v>
       </c>
@@ -10579,13 +10686,14 @@
       <c r="E464" s="5" t="s">
         <v>176</v>
       </c>
-      <c r="F464" s="8">
+      <c r="F464" s="5"/>
+      <c r="G464" s="8">
         <v>46219</v>
       </c>
-      <c r="G464" s="10"/>
       <c r="H464" s="10"/>
-    </row>
-    <row r="465" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I464" s="10"/>
+    </row>
+    <row r="465" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A465" s="4" t="s">
         <v>177</v>
       </c>
@@ -10599,15 +10707,16 @@
         <v>44</v>
       </c>
       <c r="E465" s="4" t="s">
-        <v>209</v>
-      </c>
-      <c r="F465" s="9">
+        <v>176</v>
+      </c>
+      <c r="F465" s="4"/>
+      <c r="G465" s="9">
         <v>46219</v>
       </c>
-      <c r="G465" s="10"/>
       <c r="H465" s="10"/>
-    </row>
-    <row r="466" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I465" s="10"/>
+    </row>
+    <row r="466" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A466" s="4" t="s">
         <v>177</v>
       </c>
@@ -10621,15 +10730,16 @@
         <v>47</v>
       </c>
       <c r="E466" s="4" t="s">
-        <v>210</v>
-      </c>
-      <c r="F466" s="9">
+        <v>176</v>
+      </c>
+      <c r="F466" s="4"/>
+      <c r="G466" s="9">
         <v>46219</v>
       </c>
-      <c r="G466" s="10"/>
       <c r="H466" s="10"/>
-    </row>
-    <row r="467" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I466" s="10"/>
+    </row>
+    <row r="467" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A467" s="4" t="s">
         <v>177</v>
       </c>
@@ -10643,15 +10753,16 @@
         <v>150</v>
       </c>
       <c r="E467" s="4" t="s">
-        <v>211</v>
-      </c>
-      <c r="F467" s="9">
+        <v>176</v>
+      </c>
+      <c r="F467" s="4"/>
+      <c r="G467" s="9">
         <v>46219</v>
       </c>
-      <c r="G467" s="10"/>
       <c r="H467" s="10"/>
-    </row>
-    <row r="468" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I467" s="10"/>
+    </row>
+    <row r="468" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A468" s="5" t="s">
         <v>179</v>
       </c>
@@ -10665,15 +10776,16 @@
         <v>58</v>
       </c>
       <c r="E468" s="5" t="s">
-        <v>212</v>
-      </c>
-      <c r="F468" s="8">
+        <v>176</v>
+      </c>
+      <c r="F468" s="5"/>
+      <c r="G468" s="8">
         <v>46219</v>
       </c>
-      <c r="G468" s="10"/>
       <c r="H468" s="10"/>
-    </row>
-    <row r="469" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I468" s="10"/>
+    </row>
+    <row r="469" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A469" s="5" t="s">
         <v>179</v>
       </c>
@@ -10687,15 +10799,16 @@
         <v>13</v>
       </c>
       <c r="E469" s="5" t="s">
-        <v>213</v>
-      </c>
-      <c r="F469" s="8">
+        <v>176</v>
+      </c>
+      <c r="F469" s="5"/>
+      <c r="G469" s="8">
         <v>46219</v>
       </c>
-      <c r="G469" s="10"/>
       <c r="H469" s="10"/>
-    </row>
-    <row r="470" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I469" s="10"/>
+    </row>
+    <row r="470" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A470" s="5" t="s">
         <v>179</v>
       </c>
@@ -10709,13 +10822,14 @@
         <v>17</v>
       </c>
       <c r="E470" s="5" t="s">
-        <v>214</v>
-      </c>
-      <c r="F470" s="8">
+        <v>176</v>
+      </c>
+      <c r="F470" s="5"/>
+      <c r="G470" s="8">
         <v>46219</v>
       </c>
     </row>
-    <row r="471" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="471" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A471" s="4" t="s">
         <v>181</v>
       </c>
@@ -10729,13 +10843,14 @@
         <v>29</v>
       </c>
       <c r="E471" s="4" t="s">
-        <v>215</v>
-      </c>
-      <c r="F471" s="9">
+        <v>176</v>
+      </c>
+      <c r="F471" s="4"/>
+      <c r="G471" s="9">
         <v>46219</v>
       </c>
     </row>
-    <row r="472" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="472" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A472" s="4" t="s">
         <v>181</v>
       </c>
@@ -10749,13 +10864,14 @@
         <v>29</v>
       </c>
       <c r="E472" s="4" t="s">
-        <v>216</v>
-      </c>
-      <c r="F472" s="9">
+        <v>176</v>
+      </c>
+      <c r="F472" s="4"/>
+      <c r="G472" s="9">
         <v>46219</v>
       </c>
     </row>
-    <row r="473" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="473" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A473" s="5" t="s">
         <v>183</v>
       </c>
@@ -10769,13 +10885,14 @@
         <v>29</v>
       </c>
       <c r="E473" s="5" t="s">
-        <v>217</v>
-      </c>
-      <c r="F473" s="8">
+        <v>176</v>
+      </c>
+      <c r="F473" s="5"/>
+      <c r="G473" s="8">
         <v>46219</v>
       </c>
     </row>
-    <row r="474" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="474" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A474" s="5" t="s">
         <v>183</v>
       </c>
@@ -10789,13 +10906,14 @@
         <v>154</v>
       </c>
       <c r="E474" s="5" t="s">
-        <v>218</v>
-      </c>
-      <c r="F474" s="8">
+        <v>176</v>
+      </c>
+      <c r="F474" s="5"/>
+      <c r="G474" s="8">
         <v>46219</v>
       </c>
     </row>
-    <row r="475" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="475" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A475" s="4" t="s">
         <v>185</v>
       </c>
@@ -10809,13 +10927,14 @@
         <v>73</v>
       </c>
       <c r="E475" s="4" t="s">
-        <v>219</v>
-      </c>
-      <c r="F475" s="9">
+        <v>176</v>
+      </c>
+      <c r="F475" s="4"/>
+      <c r="G475" s="9">
         <v>46219</v>
       </c>
     </row>
-    <row r="476" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="476" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A476" s="4" t="s">
         <v>185</v>
       </c>
@@ -10829,13 +10948,14 @@
         <v>26</v>
       </c>
       <c r="E476" s="4" t="s">
-        <v>220</v>
-      </c>
-      <c r="F476" s="9">
+        <v>176</v>
+      </c>
+      <c r="F476" s="4"/>
+      <c r="G476" s="9">
         <v>46219</v>
       </c>
     </row>
-    <row r="477" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="477" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A477" s="4" t="s">
         <v>185</v>
       </c>
@@ -10849,13 +10969,14 @@
         <v>58</v>
       </c>
       <c r="E477" s="4" t="s">
-        <v>221</v>
-      </c>
-      <c r="F477" s="9">
+        <v>176</v>
+      </c>
+      <c r="F477" s="4"/>
+      <c r="G477" s="9">
         <v>46219</v>
       </c>
     </row>
-    <row r="478" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="478" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A478" s="5" t="s">
         <v>187</v>
       </c>
@@ -10869,14 +10990,15 @@
         <v>64</v>
       </c>
       <c r="E478" s="5" t="s">
-        <v>222</v>
-      </c>
-      <c r="F478" s="8">
+        <v>176</v>
+      </c>
+      <c r="F478" s="5"/>
+      <c r="G478" s="8">
         <v>46220</v>
       </c>
-      <c r="G478" s="12"/>
-    </row>
-    <row r="479" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="H478" s="12"/>
+    </row>
+    <row r="479" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A479" s="5" t="s">
         <v>187</v>
       </c>
@@ -10890,14 +11012,15 @@
         <v>101</v>
       </c>
       <c r="E479" s="5" t="s">
-        <v>223</v>
-      </c>
-      <c r="F479" s="8">
+        <v>176</v>
+      </c>
+      <c r="F479" s="5"/>
+      <c r="G479" s="8">
         <v>46220</v>
       </c>
-      <c r="G479" s="12"/>
-    </row>
-    <row r="480" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="H479" s="12"/>
+    </row>
+    <row r="480" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A480" s="4" t="s">
         <v>189</v>
       </c>
@@ -10911,14 +11034,15 @@
         <v>101</v>
       </c>
       <c r="E480" s="4" t="s">
-        <v>224</v>
-      </c>
-      <c r="F480" s="9">
+        <v>176</v>
+      </c>
+      <c r="F480" s="4"/>
+      <c r="G480" s="9">
         <v>46220</v>
       </c>
-      <c r="G480" s="12"/>
-    </row>
-    <row r="481" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H480" s="12"/>
+    </row>
+    <row r="481" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A481" s="4" t="s">
         <v>189</v>
       </c>
@@ -10932,14 +11056,15 @@
         <v>13</v>
       </c>
       <c r="E481" s="4" t="s">
-        <v>225</v>
-      </c>
-      <c r="F481" s="9">
+        <v>176</v>
+      </c>
+      <c r="F481" s="4"/>
+      <c r="G481" s="9">
         <v>46220</v>
       </c>
-      <c r="G481" s="12"/>
-    </row>
-    <row r="482" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H481" s="12"/>
+    </row>
+    <row r="482" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A482" s="4" t="s">
         <v>189</v>
       </c>
@@ -10953,14 +11078,15 @@
         <v>73</v>
       </c>
       <c r="E482" s="4" t="s">
-        <v>226</v>
-      </c>
-      <c r="F482" s="9">
+        <v>176</v>
+      </c>
+      <c r="F482" s="4"/>
+      <c r="G482" s="9">
         <v>46220</v>
       </c>
-      <c r="G482" s="12"/>
-    </row>
-    <row r="483" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H482" s="12"/>
+    </row>
+    <row r="483" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A483" s="5" t="s">
         <v>191</v>
       </c>
@@ -10974,14 +11100,15 @@
         <v>149</v>
       </c>
       <c r="E483" s="5" t="s">
-        <v>227</v>
-      </c>
-      <c r="F483" s="8">
+        <v>176</v>
+      </c>
+      <c r="F483" s="5"/>
+      <c r="G483" s="8">
         <v>46220</v>
       </c>
-      <c r="G483" s="12"/>
-    </row>
-    <row r="484" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H483" s="12"/>
+    </row>
+    <row r="484" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A484" s="5" t="s">
         <v>191</v>
       </c>
@@ -10995,14 +11122,15 @@
         <v>152</v>
       </c>
       <c r="E484" s="5" t="s">
-        <v>228</v>
-      </c>
-      <c r="F484" s="8">
+        <v>176</v>
+      </c>
+      <c r="F484" s="5"/>
+      <c r="G484" s="8">
         <v>46220</v>
       </c>
-      <c r="G484" s="12"/>
-    </row>
-    <row r="485" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H484" s="12"/>
+    </row>
+    <row r="485" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A485" s="5" t="s">
         <v>191</v>
       </c>
@@ -11016,14 +11144,15 @@
         <v>73</v>
       </c>
       <c r="E485" s="5" t="s">
-        <v>229</v>
-      </c>
-      <c r="F485" s="8">
+        <v>176</v>
+      </c>
+      <c r="F485" s="5"/>
+      <c r="G485" s="8">
         <v>46220</v>
       </c>
-      <c r="G485" s="12"/>
-    </row>
-    <row r="486" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H485" s="12"/>
+    </row>
+    <row r="486" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A486" s="4" t="s">
         <v>193</v>
       </c>
@@ -11037,14 +11166,15 @@
         <v>101</v>
       </c>
       <c r="E486" s="4" t="s">
-        <v>230</v>
-      </c>
-      <c r="F486" s="9">
+        <v>176</v>
+      </c>
+      <c r="F486" s="4"/>
+      <c r="G486" s="9">
         <v>46220</v>
       </c>
-      <c r="G486" s="12"/>
-    </row>
-    <row r="487" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H486" s="12"/>
+    </row>
+    <row r="487" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A487" s="4" t="s">
         <v>193</v>
       </c>
@@ -11058,14 +11188,15 @@
         <v>38</v>
       </c>
       <c r="E487" s="4" t="s">
-        <v>231</v>
-      </c>
-      <c r="F487" s="9">
+        <v>176</v>
+      </c>
+      <c r="F487" s="4"/>
+      <c r="G487" s="9">
         <v>46220</v>
       </c>
-      <c r="G487" s="12"/>
-    </row>
-    <row r="488" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H487" s="12"/>
+    </row>
+    <row r="488" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A488" s="4" t="s">
         <v>193</v>
       </c>
@@ -11079,14 +11210,15 @@
         <v>38</v>
       </c>
       <c r="E488" s="4" t="s">
-        <v>232</v>
-      </c>
-      <c r="F488" s="9">
+        <v>176</v>
+      </c>
+      <c r="F488" s="4"/>
+      <c r="G488" s="9">
         <v>46220</v>
       </c>
-      <c r="G488" s="12"/>
-    </row>
-    <row r="489" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H488" s="12"/>
+    </row>
+    <row r="489" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A489" s="5" t="s">
         <v>195</v>
       </c>
@@ -11100,14 +11232,15 @@
         <v>38</v>
       </c>
       <c r="E489" s="5" t="s">
-        <v>233</v>
-      </c>
-      <c r="F489" s="8">
+        <v>176</v>
+      </c>
+      <c r="F489" s="5"/>
+      <c r="G489" s="8">
         <v>46220</v>
       </c>
-      <c r="G489" s="12"/>
-    </row>
-    <row r="490" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H489" s="12"/>
+    </row>
+    <row r="490" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A490" s="5" t="s">
         <v>195</v>
       </c>
@@ -11121,14 +11254,15 @@
         <v>90</v>
       </c>
       <c r="E490" s="5" t="s">
-        <v>234</v>
-      </c>
-      <c r="F490" s="8">
+        <v>176</v>
+      </c>
+      <c r="F490" s="5"/>
+      <c r="G490" s="8">
         <v>46220</v>
       </c>
-      <c r="G490" s="12"/>
-    </row>
-    <row r="491" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H490" s="12"/>
+    </row>
+    <row r="491" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A491" s="5" t="s">
         <v>195</v>
       </c>
@@ -11142,14 +11276,15 @@
         <v>73</v>
       </c>
       <c r="E491" s="5" t="s">
-        <v>235</v>
-      </c>
-      <c r="F491" s="8">
+        <v>176</v>
+      </c>
+      <c r="F491" s="5"/>
+      <c r="G491" s="8">
         <v>46220</v>
       </c>
-      <c r="G491" s="12"/>
-    </row>
-    <row r="492" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H491" s="12"/>
+    </row>
+    <row r="492" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A492" s="4" t="s">
         <v>197</v>
       </c>
@@ -11163,14 +11298,15 @@
         <v>73</v>
       </c>
       <c r="E492" s="4" t="s">
-        <v>236</v>
-      </c>
-      <c r="F492" s="9">
+        <v>176</v>
+      </c>
+      <c r="F492" s="4"/>
+      <c r="G492" s="9">
         <v>46220</v>
       </c>
-      <c r="G492" s="12"/>
-    </row>
-    <row r="493" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H492" s="12"/>
+    </row>
+    <row r="493" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A493" s="4" t="s">
         <v>197</v>
       </c>
@@ -11184,14 +11320,15 @@
         <v>38</v>
       </c>
       <c r="E493" s="4" t="s">
-        <v>237</v>
-      </c>
-      <c r="F493" s="9">
+        <v>176</v>
+      </c>
+      <c r="F493" s="4"/>
+      <c r="G493" s="9">
         <v>46220</v>
       </c>
-      <c r="G493" s="12"/>
-    </row>
-    <row r="494" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H493" s="12"/>
+    </row>
+    <row r="494" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A494" s="5" t="s">
         <v>199</v>
       </c>
@@ -11205,14 +11342,15 @@
         <v>47</v>
       </c>
       <c r="E494" s="5" t="s">
-        <v>238</v>
-      </c>
-      <c r="F494" s="8">
+        <v>176</v>
+      </c>
+      <c r="F494" s="5"/>
+      <c r="G494" s="8">
         <v>46220</v>
       </c>
-      <c r="G494" s="12"/>
-    </row>
-    <row r="495" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H494" s="12"/>
+    </row>
+    <row r="495" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A495" s="5" t="s">
         <v>199</v>
       </c>
@@ -11226,14 +11364,15 @@
         <v>29</v>
       </c>
       <c r="E495" s="5" t="s">
-        <v>239</v>
-      </c>
-      <c r="F495" s="8">
+        <v>176</v>
+      </c>
+      <c r="F495" s="5"/>
+      <c r="G495" s="8">
         <v>46220</v>
       </c>
-      <c r="G495" s="12"/>
-    </row>
-    <row r="496" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H495" s="12"/>
+    </row>
+    <row r="496" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A496" s="5" t="s">
         <v>199</v>
       </c>
@@ -11247,14 +11386,15 @@
         <v>202</v>
       </c>
       <c r="E496" s="5" t="s">
-        <v>240</v>
-      </c>
-      <c r="F496" s="8">
+        <v>176</v>
+      </c>
+      <c r="F496" s="5"/>
+      <c r="G496" s="8">
         <v>46220</v>
       </c>
-      <c r="G496" s="12"/>
-    </row>
-    <row r="497" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H496" s="12"/>
+    </row>
+    <row r="497" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A497" s="4" t="s">
         <v>203</v>
       </c>
@@ -11268,14 +11408,15 @@
         <v>38</v>
       </c>
       <c r="E497" s="4" t="s">
-        <v>241</v>
-      </c>
-      <c r="F497" s="9">
+        <v>176</v>
+      </c>
+      <c r="F497" s="4"/>
+      <c r="G497" s="9">
         <v>46221</v>
       </c>
-      <c r="G497" s="12"/>
-    </row>
-    <row r="498" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H497" s="12"/>
+    </row>
+    <row r="498" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A498" s="4" t="s">
         <v>203</v>
       </c>
@@ -11289,14 +11430,15 @@
         <v>76</v>
       </c>
       <c r="E498" s="4" t="s">
-        <v>242</v>
-      </c>
-      <c r="F498" s="9">
+        <v>176</v>
+      </c>
+      <c r="F498" s="4"/>
+      <c r="G498" s="9">
         <v>46221</v>
       </c>
-      <c r="G498" s="12"/>
-    </row>
-    <row r="499" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H498" s="12"/>
+    </row>
+    <row r="499" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A499" s="5" t="s">
         <v>205</v>
       </c>
@@ -11310,14 +11452,15 @@
         <v>101</v>
       </c>
       <c r="E499" s="5" t="s">
-        <v>243</v>
-      </c>
-      <c r="F499" s="8">
+        <v>176</v>
+      </c>
+      <c r="F499" s="5"/>
+      <c r="G499" s="8">
         <v>46221</v>
       </c>
-      <c r="G499" s="12"/>
-    </row>
-    <row r="500" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H499" s="12"/>
+    </row>
+    <row r="500" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A500" s="5" t="s">
         <v>205</v>
       </c>
@@ -11331,14 +11474,15 @@
         <v>58</v>
       </c>
       <c r="E500" s="5" t="s">
-        <v>244</v>
-      </c>
-      <c r="F500" s="8">
+        <v>176</v>
+      </c>
+      <c r="F500" s="5"/>
+      <c r="G500" s="8">
         <v>46221</v>
       </c>
-      <c r="G500" s="12"/>
-    </row>
-    <row r="501" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H500" s="12"/>
+    </row>
+    <row r="501" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A501" s="4" t="s">
         <v>207</v>
       </c>
@@ -11352,14 +11496,15 @@
         <v>47</v>
       </c>
       <c r="E501" s="4" t="s">
-        <v>245</v>
-      </c>
-      <c r="F501" s="9">
+        <v>176</v>
+      </c>
+      <c r="F501" s="4"/>
+      <c r="G501" s="9">
         <v>46221</v>
       </c>
-      <c r="G501" s="12"/>
-    </row>
-    <row r="502" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H501" s="12"/>
+    </row>
+    <row r="502" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A502" s="4" t="s">
         <v>207</v>
       </c>
@@ -11373,14 +11518,15 @@
         <v>64</v>
       </c>
       <c r="E502" s="4" t="s">
-        <v>246</v>
-      </c>
-      <c r="F502" s="9">
+        <v>176</v>
+      </c>
+      <c r="F502" s="4"/>
+      <c r="G502" s="9">
         <v>46221</v>
       </c>
-      <c r="G502" s="12"/>
-    </row>
-    <row r="503" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H502" s="12"/>
+    </row>
+    <row r="503" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A503" s="5" t="s">
         <v>177</v>
       </c>
@@ -11394,14 +11540,15 @@
         <v>150</v>
       </c>
       <c r="E503" s="5" t="s">
-        <v>248</v>
-      </c>
-      <c r="F503" s="8">
+        <v>176</v>
+      </c>
+      <c r="F503" s="5"/>
+      <c r="G503" s="8">
         <v>46225</v>
       </c>
-      <c r="G503" s="12"/>
-    </row>
-    <row r="504" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H503" s="12"/>
+    </row>
+    <row r="504" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A504" s="5" t="s">
         <v>177</v>
       </c>
@@ -11412,17 +11559,18 @@
         <v>162</v>
       </c>
       <c r="D504" s="5" t="s">
-        <v>247</v>
+        <v>209</v>
       </c>
       <c r="E504" s="5" t="s">
-        <v>249</v>
-      </c>
-      <c r="F504" s="8">
+        <v>176</v>
+      </c>
+      <c r="F504" s="5"/>
+      <c r="G504" s="8">
         <v>46225</v>
       </c>
-      <c r="G504" s="12"/>
-    </row>
-    <row r="505" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H504" s="12"/>
+    </row>
+    <row r="505" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A505" s="4" t="s">
         <v>195</v>
       </c>
@@ -11436,14 +11584,15 @@
         <v>90</v>
       </c>
       <c r="E505" s="4" t="s">
-        <v>250</v>
-      </c>
-      <c r="F505" s="9">
+        <v>176</v>
+      </c>
+      <c r="F505" s="4"/>
+      <c r="G505" s="9">
         <v>46225</v>
       </c>
-      <c r="G505" s="12"/>
-    </row>
-    <row r="506" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H505" s="12"/>
+    </row>
+    <row r="506" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A506" s="4" t="s">
         <v>195</v>
       </c>
@@ -11457,14 +11606,15 @@
         <v>29</v>
       </c>
       <c r="E506" s="4" t="s">
-        <v>251</v>
-      </c>
-      <c r="F506" s="9">
+        <v>176</v>
+      </c>
+      <c r="F506" s="4"/>
+      <c r="G506" s="9">
         <v>46225</v>
       </c>
-      <c r="G506" s="12"/>
-    </row>
-    <row r="507" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H506" s="12"/>
+    </row>
+    <row r="507" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A507" s="4" t="s">
         <v>195</v>
       </c>
@@ -11478,14 +11628,15 @@
         <v>61</v>
       </c>
       <c r="E507" s="4" t="s">
-        <v>252</v>
-      </c>
-      <c r="F507" s="9">
+        <v>176</v>
+      </c>
+      <c r="F507" s="4"/>
+      <c r="G507" s="9">
         <v>46225</v>
       </c>
-      <c r="G507" s="12"/>
-    </row>
-    <row r="508" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H507" s="12"/>
+    </row>
+    <row r="508" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A508" s="5" t="s">
         <v>203</v>
       </c>
@@ -11499,14 +11650,15 @@
         <v>90</v>
       </c>
       <c r="E508" s="5" t="s">
-        <v>253</v>
-      </c>
-      <c r="F508" s="8">
+        <v>176</v>
+      </c>
+      <c r="F508" s="5"/>
+      <c r="G508" s="8">
         <v>46226</v>
       </c>
-      <c r="G508" s="12"/>
-    </row>
-    <row r="509" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H508" s="12"/>
+    </row>
+    <row r="509" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A509" s="5" t="s">
         <v>203</v>
       </c>
@@ -11520,14 +11672,15 @@
         <v>35</v>
       </c>
       <c r="E509" s="5" t="s">
-        <v>254</v>
-      </c>
-      <c r="F509" s="8">
+        <v>176</v>
+      </c>
+      <c r="F509" s="5"/>
+      <c r="G509" s="8">
         <v>46226</v>
       </c>
-      <c r="G509" s="12"/>
-    </row>
-    <row r="510" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H509" s="12"/>
+    </row>
+    <row r="510" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A510" s="4" t="s">
         <v>197</v>
       </c>
@@ -11541,14 +11694,15 @@
         <v>90</v>
       </c>
       <c r="E510" s="4" t="s">
-        <v>255</v>
-      </c>
-      <c r="F510" s="9">
+        <v>176</v>
+      </c>
+      <c r="F510" s="4"/>
+      <c r="G510" s="9">
         <v>46226</v>
       </c>
-      <c r="G510" s="12"/>
-    </row>
-    <row r="511" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H510" s="12"/>
+    </row>
+    <row r="511" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A511" s="4" t="s">
         <v>197</v>
       </c>
@@ -11562,14 +11716,15 @@
         <v>35</v>
       </c>
       <c r="E511" s="4" t="s">
-        <v>256</v>
-      </c>
-      <c r="F511" s="9">
+        <v>176</v>
+      </c>
+      <c r="F511" s="4"/>
+      <c r="G511" s="9">
         <v>46226</v>
       </c>
-      <c r="G511" s="12"/>
-    </row>
-    <row r="512" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H511" s="12"/>
+    </row>
+    <row r="512" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A512" s="5" t="s">
         <v>208</v>
       </c>
@@ -11583,14 +11738,15 @@
         <v>44</v>
       </c>
       <c r="E512" s="5" t="s">
-        <v>257</v>
-      </c>
-      <c r="F512" s="8">
+        <v>176</v>
+      </c>
+      <c r="F512" s="5"/>
+      <c r="G512" s="8">
         <v>46226</v>
       </c>
-      <c r="G512" s="12"/>
-    </row>
-    <row r="513" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H512" s="12"/>
+    </row>
+    <row r="513" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A513" s="5" t="s">
         <v>208</v>
       </c>
@@ -11604,14 +11760,15 @@
         <v>106</v>
       </c>
       <c r="E513" s="5" t="s">
-        <v>258</v>
-      </c>
-      <c r="F513" s="8">
+        <v>176</v>
+      </c>
+      <c r="F513" s="5"/>
+      <c r="G513" s="8">
         <v>46226</v>
       </c>
-      <c r="G513" s="12"/>
-    </row>
-    <row r="514" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H513" s="12"/>
+    </row>
+    <row r="514" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A514" s="5" t="s">
         <v>208</v>
       </c>
@@ -11625,14 +11782,15 @@
         <v>150</v>
       </c>
       <c r="E514" s="5" t="s">
-        <v>259</v>
-      </c>
-      <c r="F514" s="8">
+        <v>176</v>
+      </c>
+      <c r="F514" s="5"/>
+      <c r="G514" s="8">
         <v>46226</v>
       </c>
-      <c r="G514" s="12"/>
-    </row>
-    <row r="515" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H514" s="12"/>
+    </row>
+    <row r="515" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A515" s="4" t="s">
         <v>189</v>
       </c>
@@ -11646,14 +11804,15 @@
         <v>73</v>
       </c>
       <c r="E515" s="4" t="s">
-        <v>260</v>
-      </c>
-      <c r="F515" s="9">
+        <v>176</v>
+      </c>
+      <c r="F515" s="4"/>
+      <c r="G515" s="9">
         <v>46227</v>
       </c>
-      <c r="G515" s="12"/>
-    </row>
-    <row r="516" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H515" s="12"/>
+    </row>
+    <row r="516" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A516" s="4" t="s">
         <v>189</v>
       </c>
@@ -11667,14 +11826,15 @@
         <v>17</v>
       </c>
       <c r="E516" s="4" t="s">
-        <v>261</v>
-      </c>
-      <c r="F516" s="9">
+        <v>176</v>
+      </c>
+      <c r="F516" s="4"/>
+      <c r="G516" s="9">
         <v>46227</v>
       </c>
-      <c r="G516" s="12"/>
-    </row>
-    <row r="517" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H516" s="12"/>
+    </row>
+    <row r="517" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A517" s="5" t="s">
         <v>193</v>
       </c>
@@ -11688,14 +11848,15 @@
         <v>44</v>
       </c>
       <c r="E517" s="5" t="s">
-        <v>262</v>
-      </c>
-      <c r="F517" s="8">
+        <v>176</v>
+      </c>
+      <c r="F517" s="5"/>
+      <c r="G517" s="8">
         <v>46227</v>
       </c>
-      <c r="G517" s="12"/>
-    </row>
-    <row r="518" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H517" s="12"/>
+    </row>
+    <row r="518" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A518" s="5" t="s">
         <v>193</v>
       </c>
@@ -11709,14 +11870,15 @@
         <v>29</v>
       </c>
       <c r="E518" s="5" t="s">
-        <v>263</v>
-      </c>
-      <c r="F518" s="8">
+        <v>176</v>
+      </c>
+      <c r="F518" s="5"/>
+      <c r="G518" s="8">
         <v>46227</v>
       </c>
-      <c r="G518" s="12"/>
-    </row>
-    <row r="519" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H518" s="12"/>
+    </row>
+    <row r="519" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A519" s="4" t="s">
         <v>200</v>
       </c>
@@ -11730,14 +11892,15 @@
         <v>90</v>
       </c>
       <c r="E519" s="4" t="s">
-        <v>264</v>
-      </c>
-      <c r="F519" s="9">
+        <v>176</v>
+      </c>
+      <c r="F519" s="4"/>
+      <c r="G519" s="9">
         <v>46227</v>
       </c>
-      <c r="G519" s="12"/>
-    </row>
-    <row r="520" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H519" s="12"/>
+    </row>
+    <row r="520" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A520" s="4" t="s">
         <v>200</v>
       </c>
@@ -11751,13 +11914,14 @@
         <v>90</v>
       </c>
       <c r="E520" s="4" t="s">
-        <v>265</v>
-      </c>
-      <c r="F520" s="9">
+        <v>176</v>
+      </c>
+      <c r="F520" s="4"/>
+      <c r="G520" s="9">
         <v>46227</v>
       </c>
     </row>
-    <row r="521" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="521" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A521" s="5" t="s">
         <v>72</v>
       </c>
@@ -11771,13 +11935,14 @@
         <v>90</v>
       </c>
       <c r="E521" s="5" t="s">
-        <v>266</v>
-      </c>
-      <c r="F521" s="8">
+        <v>210</v>
+      </c>
+      <c r="F521" s="5"/>
+      <c r="G521" s="8">
         <v>46235</v>
       </c>
     </row>
-    <row r="522" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="522" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A522" s="5" t="s">
         <v>72</v>
       </c>
@@ -11791,13 +11956,14 @@
         <v>23</v>
       </c>
       <c r="E522" s="5" t="s">
-        <v>266</v>
-      </c>
-      <c r="F522" s="8">
+        <v>210</v>
+      </c>
+      <c r="F522" s="5"/>
+      <c r="G522" s="8">
         <v>46235</v>
       </c>
     </row>
-    <row r="523" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="523" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A523" s="5" t="s">
         <v>72</v>
       </c>
@@ -11811,13 +11977,14 @@
         <v>38</v>
       </c>
       <c r="E523" s="5" t="s">
-        <v>266</v>
-      </c>
-      <c r="F523" s="8">
+        <v>210</v>
+      </c>
+      <c r="F523" s="5"/>
+      <c r="G523" s="8">
         <v>46235</v>
       </c>
     </row>
-    <row r="524" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="524" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A524" s="4" t="s">
         <v>104</v>
       </c>
@@ -11831,13 +11998,14 @@
         <v>73</v>
       </c>
       <c r="E524" s="4" t="s">
-        <v>266</v>
-      </c>
-      <c r="F524" s="9">
+        <v>210</v>
+      </c>
+      <c r="F524" s="4"/>
+      <c r="G524" s="9">
         <v>46235</v>
       </c>
     </row>
-    <row r="525" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="525" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A525" s="4" t="s">
         <v>104</v>
       </c>
@@ -11851,13 +12019,14 @@
         <v>76</v>
       </c>
       <c r="E525" s="4" t="s">
-        <v>266</v>
-      </c>
-      <c r="F525" s="9">
+        <v>210</v>
+      </c>
+      <c r="F525" s="4"/>
+      <c r="G525" s="9">
         <v>46235</v>
       </c>
     </row>
-    <row r="526" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="526" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A526" s="5" t="s">
         <v>95</v>
       </c>
@@ -11871,13 +12040,14 @@
         <v>151</v>
       </c>
       <c r="E526" s="5" t="s">
-        <v>266</v>
-      </c>
-      <c r="F526" s="8">
+        <v>210</v>
+      </c>
+      <c r="F526" s="5"/>
+      <c r="G526" s="8">
         <v>46236</v>
       </c>
     </row>
-    <row r="527" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="527" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A527" s="5" t="s">
         <v>95</v>
       </c>
@@ -11891,13 +12061,14 @@
         <v>73</v>
       </c>
       <c r="E527" s="5" t="s">
-        <v>266</v>
-      </c>
-      <c r="F527" s="8">
+        <v>210</v>
+      </c>
+      <c r="F527" s="5"/>
+      <c r="G527" s="8">
         <v>46236</v>
       </c>
     </row>
-    <row r="528" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="528" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A528" s="5" t="s">
         <v>95</v>
       </c>
@@ -11911,13 +12082,14 @@
         <v>13</v>
       </c>
       <c r="E528" s="5" t="s">
-        <v>266</v>
-      </c>
-      <c r="F528" s="8">
+        <v>210</v>
+      </c>
+      <c r="F528" s="5"/>
+      <c r="G528" s="8">
         <v>46236</v>
       </c>
     </row>
-    <row r="529" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="529" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A529" s="4" t="s">
         <v>21</v>
       </c>
@@ -11931,13 +12103,14 @@
         <v>38</v>
       </c>
       <c r="E529" s="4" t="s">
-        <v>266</v>
-      </c>
-      <c r="F529" s="9">
+        <v>210</v>
+      </c>
+      <c r="F529" s="4"/>
+      <c r="G529" s="9">
         <v>46236</v>
       </c>
     </row>
-    <row r="530" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="530" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A530" s="4" t="s">
         <v>21</v>
       </c>
@@ -11951,13 +12124,14 @@
         <v>76</v>
       </c>
       <c r="E530" s="4" t="s">
-        <v>266</v>
-      </c>
-      <c r="F530" s="9">
+        <v>210</v>
+      </c>
+      <c r="F530" s="4"/>
+      <c r="G530" s="9">
         <v>46236</v>
       </c>
     </row>
-    <row r="531" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="531" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A531" s="5" t="s">
         <v>114</v>
       </c>
@@ -11971,13 +12145,14 @@
         <v>58</v>
       </c>
       <c r="E531" s="5" t="s">
-        <v>266</v>
-      </c>
-      <c r="F531" s="8">
+        <v>210</v>
+      </c>
+      <c r="F531" s="5"/>
+      <c r="G531" s="8">
         <v>46237</v>
       </c>
     </row>
-    <row r="532" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="532" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A532" s="5" t="s">
         <v>114</v>
       </c>
@@ -11991,13 +12166,14 @@
         <v>35</v>
       </c>
       <c r="E532" s="5" t="s">
-        <v>266</v>
-      </c>
-      <c r="F532" s="8">
+        <v>210</v>
+      </c>
+      <c r="F532" s="5"/>
+      <c r="G532" s="8">
         <v>46237</v>
       </c>
     </row>
-    <row r="533" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="533" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A533" s="4" t="s">
         <v>30</v>
       </c>
@@ -12011,13 +12187,14 @@
         <v>17</v>
       </c>
       <c r="E533" s="4" t="s">
-        <v>266</v>
-      </c>
-      <c r="F533" s="9">
+        <v>210</v>
+      </c>
+      <c r="F533" s="4"/>
+      <c r="G533" s="9">
         <v>46237</v>
       </c>
     </row>
-    <row r="534" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="534" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A534" s="4" t="s">
         <v>30</v>
       </c>
@@ -12031,13 +12208,14 @@
         <v>13</v>
       </c>
       <c r="E534" s="4" t="s">
-        <v>266</v>
-      </c>
-      <c r="F534" s="9">
+        <v>210</v>
+      </c>
+      <c r="F534" s="4"/>
+      <c r="G534" s="9">
         <v>46237</v>
       </c>
     </row>
-    <row r="535" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="535" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A535" s="5" t="s">
         <v>110</v>
       </c>
@@ -12051,13 +12229,14 @@
         <v>26</v>
       </c>
       <c r="E535" s="5" t="s">
-        <v>266</v>
-      </c>
-      <c r="F535" s="8">
+        <v>210</v>
+      </c>
+      <c r="F535" s="5"/>
+      <c r="G535" s="8">
         <v>46238</v>
       </c>
     </row>
-    <row r="536" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="536" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A536" s="5" t="s">
         <v>110</v>
       </c>
@@ -12071,13 +12250,14 @@
         <v>90</v>
       </c>
       <c r="E536" s="5" t="s">
-        <v>266</v>
-      </c>
-      <c r="F536" s="8">
+        <v>210</v>
+      </c>
+      <c r="F536" s="5"/>
+      <c r="G536" s="8">
         <v>46238</v>
       </c>
     </row>
-    <row r="537" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="537" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A537" s="4" t="s">
         <v>99</v>
       </c>
@@ -12091,13 +12271,14 @@
         <v>64</v>
       </c>
       <c r="E537" s="4" t="s">
-        <v>266</v>
-      </c>
-      <c r="F537" s="9">
+        <v>210</v>
+      </c>
+      <c r="F537" s="4"/>
+      <c r="G537" s="9">
         <v>46238</v>
       </c>
     </row>
-    <row r="538" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="538" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A538" s="4" t="s">
         <v>99</v>
       </c>
@@ -12111,13 +12292,14 @@
         <v>13</v>
       </c>
       <c r="E538" s="4" t="s">
-        <v>266</v>
-      </c>
-      <c r="F538" s="9">
+        <v>210</v>
+      </c>
+      <c r="F538" s="4"/>
+      <c r="G538" s="9">
         <v>46238</v>
       </c>
     </row>
-    <row r="539" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="539" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A539" s="4" t="s">
         <v>99</v>
       </c>
@@ -12131,13 +12313,14 @@
         <v>73</v>
       </c>
       <c r="E539" s="4" t="s">
-        <v>266</v>
-      </c>
-      <c r="F539" s="9">
+        <v>210</v>
+      </c>
+      <c r="F539" s="4"/>
+      <c r="G539" s="9">
         <v>46238</v>
       </c>
     </row>
-    <row r="540" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="540" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A540" s="5" t="s">
         <v>52</v>
       </c>
@@ -12151,13 +12334,14 @@
         <v>64</v>
       </c>
       <c r="E540" s="5" t="s">
-        <v>266</v>
-      </c>
-      <c r="F540" s="8">
+        <v>210</v>
+      </c>
+      <c r="F540" s="5"/>
+      <c r="G540" s="8">
         <v>46239</v>
       </c>
     </row>
-    <row r="541" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="541" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A541" s="5" t="s">
         <v>52</v>
       </c>
@@ -12171,13 +12355,14 @@
         <v>64</v>
       </c>
       <c r="E541" s="5" t="s">
-        <v>266</v>
-      </c>
-      <c r="F541" s="8">
+        <v>210</v>
+      </c>
+      <c r="F541" s="5"/>
+      <c r="G541" s="8">
         <v>46239</v>
       </c>
     </row>
-    <row r="542" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="542" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A542" s="4" t="s">
         <v>18</v>
       </c>
@@ -12191,13 +12376,14 @@
         <v>64</v>
       </c>
       <c r="E542" s="4" t="s">
-        <v>266</v>
-      </c>
-      <c r="F542" s="9">
+        <v>210</v>
+      </c>
+      <c r="F542" s="4"/>
+      <c r="G542" s="9">
         <v>46239</v>
       </c>
     </row>
-    <row r="543" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="543" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A543" s="4" t="s">
         <v>18</v>
       </c>
@@ -12211,13 +12397,14 @@
         <v>13</v>
       </c>
       <c r="E543" s="4" t="s">
-        <v>266</v>
-      </c>
-      <c r="F543" s="9">
+        <v>210</v>
+      </c>
+      <c r="F543" s="4"/>
+      <c r="G543" s="9">
         <v>46239</v>
       </c>
     </row>
-    <row r="544" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="544" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A544" s="4" t="s">
         <v>18</v>
       </c>
@@ -12231,13 +12418,14 @@
         <v>73</v>
       </c>
       <c r="E544" s="4" t="s">
-        <v>266</v>
-      </c>
-      <c r="F544" s="9">
+        <v>210</v>
+      </c>
+      <c r="F544" s="4"/>
+      <c r="G544" s="9">
         <v>46239</v>
       </c>
     </row>
-    <row r="545" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="545" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A545" s="5" t="s">
         <v>86</v>
       </c>
@@ -12251,13 +12439,14 @@
         <v>41</v>
       </c>
       <c r="E545" s="5" t="s">
-        <v>266</v>
-      </c>
-      <c r="F545" s="8">
+        <v>210</v>
+      </c>
+      <c r="F545" s="5"/>
+      <c r="G545" s="8">
         <v>46240</v>
       </c>
     </row>
-    <row r="546" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="546" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A546" s="5" t="s">
         <v>86</v>
       </c>
@@ -12271,13 +12460,14 @@
         <v>106</v>
       </c>
       <c r="E546" s="5" t="s">
-        <v>266</v>
-      </c>
-      <c r="F546" s="8">
+        <v>210</v>
+      </c>
+      <c r="F546" s="5"/>
+      <c r="G546" s="8">
         <v>46240</v>
       </c>
     </row>
-    <row r="547" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="547" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A547" s="4" t="s">
         <v>82</v>
       </c>
@@ -12291,13 +12481,14 @@
         <v>73</v>
       </c>
       <c r="E547" s="4" t="s">
-        <v>266</v>
-      </c>
-      <c r="F547" s="9">
+        <v>210</v>
+      </c>
+      <c r="F547" s="4"/>
+      <c r="G547" s="9">
         <v>46240</v>
       </c>
     </row>
-    <row r="548" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="548" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A548" s="4" t="s">
         <v>82</v>
       </c>
@@ -12311,13 +12502,14 @@
         <v>151</v>
       </c>
       <c r="E548" s="4" t="s">
-        <v>266</v>
-      </c>
-      <c r="F548" s="9">
+        <v>210</v>
+      </c>
+      <c r="F548" s="4"/>
+      <c r="G548" s="9">
         <v>46240</v>
       </c>
     </row>
-    <row r="549" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="549" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A549" s="4" t="s">
         <v>82</v>
       </c>
@@ -12331,13 +12523,14 @@
         <v>38</v>
       </c>
       <c r="E549" s="4" t="s">
-        <v>266</v>
-      </c>
-      <c r="F549" s="9">
+        <v>210</v>
+      </c>
+      <c r="F549" s="4"/>
+      <c r="G549" s="9">
         <v>46240</v>
       </c>
     </row>
-    <row r="550" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="550" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A550" s="5" t="s">
         <v>165</v>
       </c>
@@ -12351,13 +12544,14 @@
         <v>58</v>
       </c>
       <c r="E550" s="5" t="s">
-        <v>266</v>
-      </c>
-      <c r="F550" s="8">
+        <v>210</v>
+      </c>
+      <c r="F550" s="5"/>
+      <c r="G550" s="8">
         <v>46241</v>
       </c>
     </row>
-    <row r="551" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="551" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A551" s="5" t="s">
         <v>165</v>
       </c>
@@ -12371,13 +12565,14 @@
         <v>90</v>
       </c>
       <c r="E551" s="5" t="s">
-        <v>266</v>
-      </c>
-      <c r="F551" s="8">
+        <v>210</v>
+      </c>
+      <c r="F551" s="5"/>
+      <c r="G551" s="8">
         <v>46241</v>
       </c>
     </row>
-    <row r="552" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="552" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A552" s="4" t="s">
         <v>168</v>
       </c>
@@ -12391,13 +12586,14 @@
         <v>106</v>
       </c>
       <c r="E552" s="4" t="s">
-        <v>266</v>
-      </c>
-      <c r="F552" s="9">
+        <v>210</v>
+      </c>
+      <c r="F552" s="4"/>
+      <c r="G552" s="9">
         <v>46241</v>
       </c>
     </row>
-    <row r="553" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="553" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A553" s="4" t="s">
         <v>168</v>
       </c>
@@ -12411,13 +12607,14 @@
         <v>58</v>
       </c>
       <c r="E553" s="4" t="s">
-        <v>266</v>
-      </c>
-      <c r="F553" s="9">
+        <v>210</v>
+      </c>
+      <c r="F553" s="4"/>
+      <c r="G553" s="9">
         <v>46241</v>
       </c>
     </row>
-    <row r="554" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="554" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A554" s="5" t="s">
         <v>83</v>
       </c>
@@ -12431,13 +12628,14 @@
         <v>155</v>
       </c>
       <c r="E554" s="5" t="s">
-        <v>266</v>
-      </c>
-      <c r="F554" s="8">
+        <v>210</v>
+      </c>
+      <c r="F554" s="5"/>
+      <c r="G554" s="8">
         <v>46242</v>
       </c>
     </row>
-    <row r="555" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="555" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A555" s="5" t="s">
         <v>83</v>
       </c>
@@ -12451,18 +12649,19 @@
         <v>73</v>
       </c>
       <c r="E555" s="5" t="s">
-        <v>266</v>
-      </c>
-      <c r="F555" s="8">
+        <v>210</v>
+      </c>
+      <c r="F555" s="5"/>
+      <c r="G555" s="8">
         <v>46242</v>
       </c>
     </row>
-    <row r="556" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="556" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A556" s="4" t="s">
         <v>167</v>
       </c>
       <c r="B556" s="4" t="s">
-        <v>267</v>
+        <v>211</v>
       </c>
       <c r="C556" s="4" t="s">
         <v>16</v>
@@ -12471,18 +12670,19 @@
         <v>58</v>
       </c>
       <c r="E556" s="4" t="s">
-        <v>266</v>
-      </c>
-      <c r="F556" s="9">
+        <v>210</v>
+      </c>
+      <c r="F556" s="4"/>
+      <c r="G556" s="9">
         <v>46242</v>
       </c>
     </row>
-    <row r="557" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="557" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A557" s="4" t="s">
         <v>167</v>
       </c>
       <c r="B557" s="4" t="s">
-        <v>267</v>
+        <v>211</v>
       </c>
       <c r="C557" s="4" t="s">
         <v>54</v>
@@ -12491,13 +12691,14 @@
         <v>149</v>
       </c>
       <c r="E557" s="4" t="s">
-        <v>266</v>
-      </c>
-      <c r="F557" s="9">
+        <v>210</v>
+      </c>
+      <c r="F557" s="4"/>
+      <c r="G557" s="9">
         <v>46242</v>
       </c>
     </row>
-    <row r="558" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="558" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A558" s="5" t="s">
         <v>136</v>
       </c>
@@ -12511,13 +12712,14 @@
         <v>151</v>
       </c>
       <c r="E558" s="5" t="s">
-        <v>266</v>
-      </c>
-      <c r="F558" s="8">
+        <v>210</v>
+      </c>
+      <c r="F558" s="5"/>
+      <c r="G558" s="8">
         <v>46246</v>
       </c>
     </row>
-    <row r="559" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="559" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A559" s="5" t="s">
         <v>136</v>
       </c>
@@ -12531,13 +12733,14 @@
         <v>58</v>
       </c>
       <c r="E559" s="5" t="s">
-        <v>266</v>
-      </c>
-      <c r="F559" s="8">
+        <v>210</v>
+      </c>
+      <c r="F559" s="5"/>
+      <c r="G559" s="8">
         <v>46246</v>
       </c>
     </row>
-    <row r="560" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="560" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A560" s="4" t="s">
         <v>72</v>
       </c>
@@ -12551,13 +12754,14 @@
         <v>58</v>
       </c>
       <c r="E560" s="4" t="s">
-        <v>266</v>
-      </c>
-      <c r="F560" s="9">
+        <v>210</v>
+      </c>
+      <c r="F560" s="4"/>
+      <c r="G560" s="9">
         <v>46246</v>
       </c>
     </row>
-    <row r="561" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="561" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A561" s="4" t="s">
         <v>72</v>
       </c>
@@ -12571,13 +12775,14 @@
         <v>29</v>
       </c>
       <c r="E561" s="4" t="s">
-        <v>266</v>
-      </c>
-      <c r="F561" s="9">
+        <v>210</v>
+      </c>
+      <c r="F561" s="4"/>
+      <c r="G561" s="9">
         <v>46246</v>
       </c>
     </row>
-    <row r="562" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="562" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A562" s="4" t="s">
         <v>72</v>
       </c>
@@ -12591,13 +12796,14 @@
         <v>64</v>
       </c>
       <c r="E562" s="4" t="s">
-        <v>266</v>
-      </c>
-      <c r="F562" s="9">
+        <v>210</v>
+      </c>
+      <c r="F562" s="4"/>
+      <c r="G562" s="9">
         <v>46246</v>
       </c>
     </row>
-    <row r="563" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="563" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A563" s="5" t="s">
         <v>95</v>
       </c>
@@ -12611,13 +12817,14 @@
         <v>101</v>
       </c>
       <c r="E563" s="5" t="s">
-        <v>266</v>
-      </c>
-      <c r="F563" s="8">
+        <v>210</v>
+      </c>
+      <c r="F563" s="5"/>
+      <c r="G563" s="8">
         <v>46246</v>
       </c>
     </row>
-    <row r="564" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="564" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A564" s="5" t="s">
         <v>95</v>
       </c>
@@ -12631,13 +12838,14 @@
         <v>38</v>
       </c>
       <c r="E564" s="5" t="s">
-        <v>266</v>
-      </c>
-      <c r="F564" s="8">
+        <v>210</v>
+      </c>
+      <c r="F564" s="5"/>
+      <c r="G564" s="8">
         <v>46246</v>
       </c>
     </row>
-    <row r="565" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="565" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A565" s="5" t="s">
         <v>95</v>
       </c>
@@ -12651,13 +12859,14 @@
         <v>58</v>
       </c>
       <c r="E565" s="5" t="s">
-        <v>266</v>
-      </c>
-      <c r="F565" s="8">
+        <v>210</v>
+      </c>
+      <c r="F565" s="5"/>
+      <c r="G565" s="8">
         <v>46246</v>
       </c>
     </row>
-    <row r="566" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="566" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A566" s="4" t="s">
         <v>57</v>
       </c>
@@ -12671,13 +12880,14 @@
         <v>101</v>
       </c>
       <c r="E566" s="4" t="s">
-        <v>266</v>
-      </c>
-      <c r="F566" s="9">
+        <v>210</v>
+      </c>
+      <c r="F566" s="4"/>
+      <c r="G566" s="9">
         <v>46246</v>
       </c>
     </row>
-    <row r="567" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="567" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A567" s="4" t="s">
         <v>57</v>
       </c>
@@ -12691,13 +12901,14 @@
         <v>64</v>
       </c>
       <c r="E567" s="4" t="s">
-        <v>266</v>
-      </c>
-      <c r="F567" s="9">
+        <v>210</v>
+      </c>
+      <c r="F567" s="4"/>
+      <c r="G567" s="9">
         <v>46246</v>
       </c>
     </row>
-    <row r="568" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="568" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A568" s="5" t="s">
         <v>104</v>
       </c>
@@ -12711,13 +12922,14 @@
         <v>13</v>
       </c>
       <c r="E568" s="5" t="s">
-        <v>266</v>
-      </c>
-      <c r="F568" s="8">
+        <v>210</v>
+      </c>
+      <c r="F568" s="5"/>
+      <c r="G568" s="8">
         <v>46247</v>
       </c>
     </row>
-    <row r="569" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="569" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A569" s="5" t="s">
         <v>104</v>
       </c>
@@ -12731,13 +12943,14 @@
         <v>150</v>
       </c>
       <c r="E569" s="5" t="s">
-        <v>266</v>
-      </c>
-      <c r="F569" s="8">
+        <v>210</v>
+      </c>
+      <c r="F569" s="5"/>
+      <c r="G569" s="8">
         <v>46247</v>
       </c>
     </row>
-    <row r="570" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="570" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A570" s="4" t="s">
         <v>81</v>
       </c>
@@ -12751,13 +12964,14 @@
         <v>35</v>
       </c>
       <c r="E570" s="4" t="s">
-        <v>266</v>
-      </c>
-      <c r="F570" s="9">
+        <v>210</v>
+      </c>
+      <c r="F570" s="4"/>
+      <c r="G570" s="9">
         <v>46247</v>
       </c>
     </row>
-    <row r="571" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="571" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A571" s="4" t="s">
         <v>81</v>
       </c>
@@ -12771,13 +12985,14 @@
         <v>106</v>
       </c>
       <c r="E571" s="4" t="s">
-        <v>266</v>
-      </c>
-      <c r="F571" s="9">
+        <v>210</v>
+      </c>
+      <c r="F571" s="4"/>
+      <c r="G571" s="9">
         <v>46247</v>
       </c>
     </row>
-    <row r="572" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="572" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A572" s="5" t="s">
         <v>119</v>
       </c>
@@ -12791,13 +13006,14 @@
         <v>47</v>
       </c>
       <c r="E572" s="5" t="s">
-        <v>266</v>
-      </c>
-      <c r="F572" s="8">
+        <v>210</v>
+      </c>
+      <c r="F572" s="5"/>
+      <c r="G572" s="8">
         <v>46247</v>
       </c>
     </row>
-    <row r="573" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="573" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A573" s="5" t="s">
         <v>119</v>
       </c>
@@ -12811,15 +13027,16 @@
         <v>35</v>
       </c>
       <c r="E573" s="5" t="s">
-        <v>266</v>
-      </c>
-      <c r="F573" s="8">
+        <v>210</v>
+      </c>
+      <c r="F573" s="5"/>
+      <c r="G573" s="8">
         <v>46247</v>
       </c>
     </row>
-    <row r="574" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="574" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A574" s="4" t="s">
-        <v>267</v>
+        <v>211</v>
       </c>
       <c r="B574" s="4" t="s">
         <v>83</v>
@@ -12831,15 +13048,16 @@
         <v>23</v>
       </c>
       <c r="E574" s="4" t="s">
-        <v>266</v>
-      </c>
-      <c r="F574" s="9">
+        <v>210</v>
+      </c>
+      <c r="F574" s="4"/>
+      <c r="G574" s="9">
         <v>46247</v>
       </c>
     </row>
-    <row r="575" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="575" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A575" s="4" t="s">
-        <v>267</v>
+        <v>211</v>
       </c>
       <c r="B575" s="4" t="s">
         <v>83</v>
@@ -12851,259 +13069,291 @@
         <v>51</v>
       </c>
       <c r="E575" s="4" t="s">
-        <v>266</v>
-      </c>
-      <c r="F575" s="9">
+        <v>210</v>
+      </c>
+      <c r="F575" s="4"/>
+      <c r="G575" s="9">
         <v>46247</v>
       </c>
     </row>
-    <row r="576" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="576" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A576" s="11"/>
       <c r="B576" s="11"/>
       <c r="C576" s="11"/>
       <c r="D576" s="11"/>
       <c r="E576" s="11"/>
       <c r="F576" s="11"/>
-    </row>
-    <row r="577" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G576" s="11"/>
+    </row>
+    <row r="577" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A577" s="11"/>
       <c r="B577" s="11"/>
       <c r="C577" s="11"/>
       <c r="D577" s="11"/>
       <c r="E577" s="11"/>
       <c r="F577" s="11"/>
-    </row>
-    <row r="578" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G577" s="11"/>
+    </row>
+    <row r="578" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A578" s="11"/>
       <c r="B578" s="11"/>
       <c r="C578" s="11"/>
       <c r="D578" s="11"/>
       <c r="E578" s="11"/>
       <c r="F578" s="11"/>
-    </row>
-    <row r="579" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G578" s="11"/>
+    </row>
+    <row r="579" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A579" s="11"/>
       <c r="B579" s="11"/>
       <c r="C579" s="11"/>
       <c r="D579" s="11"/>
       <c r="E579" s="11"/>
       <c r="F579" s="11"/>
-    </row>
-    <row r="580" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G579" s="11"/>
+    </row>
+    <row r="580" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A580" s="11"/>
       <c r="B580" s="11"/>
       <c r="C580" s="11"/>
       <c r="D580" s="11"/>
       <c r="E580" s="11"/>
       <c r="F580" s="11"/>
-    </row>
-    <row r="581" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G580" s="11"/>
+    </row>
+    <row r="581" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A581" s="11"/>
       <c r="B581" s="11"/>
       <c r="C581" s="11"/>
       <c r="D581" s="11"/>
       <c r="E581" s="11"/>
       <c r="F581" s="11"/>
-    </row>
-    <row r="582" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G581" s="11"/>
+    </row>
+    <row r="582" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A582" s="11"/>
       <c r="B582" s="11"/>
       <c r="C582" s="11"/>
       <c r="D582" s="11"/>
       <c r="E582" s="11"/>
       <c r="F582" s="11"/>
-    </row>
-    <row r="583" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G582" s="11"/>
+    </row>
+    <row r="583" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A583" s="11"/>
       <c r="B583" s="11"/>
       <c r="C583" s="11"/>
       <c r="D583" s="11"/>
       <c r="E583" s="11"/>
       <c r="F583" s="11"/>
-    </row>
-    <row r="584" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G583" s="11"/>
+    </row>
+    <row r="584" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A584" s="11"/>
       <c r="B584" s="11"/>
       <c r="C584" s="11"/>
       <c r="D584" s="11"/>
       <c r="E584" s="11"/>
       <c r="F584" s="11"/>
-    </row>
-    <row r="585" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G584" s="11"/>
+    </row>
+    <row r="585" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A585" s="11"/>
       <c r="B585" s="11"/>
       <c r="C585" s="11"/>
       <c r="D585" s="11"/>
       <c r="E585" s="11"/>
       <c r="F585" s="11"/>
-    </row>
-    <row r="586" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G585" s="11"/>
+    </row>
+    <row r="586" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A586" s="11"/>
       <c r="B586" s="11"/>
       <c r="C586" s="11"/>
       <c r="D586" s="11"/>
       <c r="E586" s="11"/>
       <c r="F586" s="11"/>
-    </row>
-    <row r="587" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G586" s="11"/>
+    </row>
+    <row r="587" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A587" s="11"/>
       <c r="B587" s="11"/>
       <c r="C587" s="11"/>
       <c r="D587" s="11"/>
       <c r="E587" s="11"/>
       <c r="F587" s="11"/>
-    </row>
-    <row r="588" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G587" s="11"/>
+    </row>
+    <row r="588" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A588" s="11"/>
       <c r="B588" s="11"/>
       <c r="C588" s="11"/>
       <c r="D588" s="11"/>
       <c r="E588" s="11"/>
       <c r="F588" s="11"/>
-    </row>
-    <row r="589" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G588" s="11"/>
+    </row>
+    <row r="589" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A589" s="11"/>
       <c r="B589" s="11"/>
       <c r="C589" s="11"/>
       <c r="D589" s="11"/>
       <c r="E589" s="11"/>
       <c r="F589" s="11"/>
-    </row>
-    <row r="590" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G589" s="11"/>
+    </row>
+    <row r="590" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A590" s="11"/>
       <c r="B590" s="11"/>
       <c r="C590" s="11"/>
       <c r="D590" s="11"/>
       <c r="E590" s="11"/>
       <c r="F590" s="11"/>
-    </row>
-    <row r="591" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G590" s="11"/>
+    </row>
+    <row r="591" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A591" s="11"/>
       <c r="B591" s="11"/>
       <c r="C591" s="11"/>
       <c r="D591" s="11"/>
       <c r="E591" s="11"/>
       <c r="F591" s="11"/>
-    </row>
-    <row r="592" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G591" s="11"/>
+    </row>
+    <row r="592" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A592" s="11"/>
       <c r="B592" s="11"/>
       <c r="C592" s="11"/>
       <c r="D592" s="11"/>
       <c r="E592" s="11"/>
       <c r="F592" s="11"/>
-    </row>
-    <row r="593" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G592" s="11"/>
+    </row>
+    <row r="593" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A593" s="11"/>
       <c r="B593" s="11"/>
       <c r="C593" s="11"/>
       <c r="D593" s="11"/>
       <c r="E593" s="11"/>
       <c r="F593" s="11"/>
-    </row>
-    <row r="594" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G593" s="11"/>
+    </row>
+    <row r="594" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A594" s="11"/>
       <c r="B594" s="11"/>
       <c r="C594" s="11"/>
       <c r="D594" s="11"/>
       <c r="E594" s="11"/>
       <c r="F594" s="11"/>
-    </row>
-    <row r="595" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G594" s="11"/>
+    </row>
+    <row r="595" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A595" s="11"/>
       <c r="B595" s="11"/>
       <c r="C595" s="11"/>
       <c r="D595" s="11"/>
       <c r="E595" s="11"/>
       <c r="F595" s="11"/>
-    </row>
-    <row r="596" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G595" s="11"/>
+    </row>
+    <row r="596" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A596" s="11"/>
       <c r="B596" s="11"/>
       <c r="C596" s="11"/>
       <c r="D596" s="11"/>
       <c r="E596" s="11"/>
       <c r="F596" s="11"/>
-    </row>
-    <row r="597" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G596" s="11"/>
+    </row>
+    <row r="597" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A597" s="11"/>
       <c r="B597" s="11"/>
       <c r="C597" s="11"/>
       <c r="D597" s="11"/>
       <c r="E597" s="11"/>
       <c r="F597" s="11"/>
-    </row>
-    <row r="598" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G597" s="11"/>
+    </row>
+    <row r="598" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A598" s="11"/>
       <c r="B598" s="11"/>
       <c r="C598" s="11"/>
       <c r="D598" s="11"/>
       <c r="E598" s="11"/>
       <c r="F598" s="11"/>
-    </row>
-    <row r="599" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G598" s="11"/>
+    </row>
+    <row r="599" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A599" s="11"/>
       <c r="B599" s="11"/>
       <c r="C599" s="11"/>
       <c r="D599" s="11"/>
       <c r="E599" s="11"/>
       <c r="F599" s="11"/>
-    </row>
-    <row r="600" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G599" s="11"/>
+    </row>
+    <row r="600" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A600" s="11"/>
       <c r="B600" s="11"/>
       <c r="C600" s="11"/>
       <c r="D600" s="11"/>
       <c r="E600" s="11"/>
       <c r="F600" s="11"/>
-    </row>
-    <row r="601" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G600" s="11"/>
+    </row>
+    <row r="601" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A601" s="11"/>
       <c r="B601" s="11"/>
       <c r="C601" s="11"/>
       <c r="D601" s="11"/>
       <c r="E601" s="11"/>
       <c r="F601" s="11"/>
-    </row>
-    <row r="602" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G601" s="11"/>
+    </row>
+    <row r="602" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A602" s="11"/>
       <c r="B602" s="11"/>
       <c r="C602" s="11"/>
       <c r="D602" s="11"/>
       <c r="E602" s="11"/>
       <c r="F602" s="11"/>
-    </row>
-    <row r="603" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G602" s="11"/>
+    </row>
+    <row r="603" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A603" s="11"/>
       <c r="B603" s="11"/>
       <c r="C603" s="11"/>
       <c r="D603" s="11"/>
       <c r="E603" s="11"/>
       <c r="F603" s="11"/>
-    </row>
-    <row r="604" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G603" s="11"/>
+    </row>
+    <row r="604" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A604" s="11"/>
       <c r="B604" s="11"/>
       <c r="C604" s="11"/>
       <c r="D604" s="11"/>
       <c r="E604" s="11"/>
       <c r="F604" s="11"/>
-    </row>
-    <row r="605" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G604" s="11"/>
+    </row>
+    <row r="605" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A605" s="11"/>
       <c r="B605" s="11"/>
       <c r="C605" s="11"/>
       <c r="D605" s="11"/>
       <c r="E605" s="11"/>
       <c r="F605" s="11"/>
-    </row>
-    <row r="606" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G605" s="11"/>
+    </row>
+    <row r="606" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A606" s="11"/>
       <c r="B606" s="11"/>
       <c r="C606" s="11"/>
       <c r="D606" s="11"/>
       <c r="E606" s="11"/>
       <c r="F606" s="11"/>
+      <c r="G606" s="11"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
